--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A039439C-5075-4A23-9F6F-6FBC541E2182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35253DEE-FC8A-421D-A6FA-8B231EB76485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{604AECDA-6046-4CDC-AD03-6629280F8074}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F6166B1B-3DE9-46BF-87DC-ACE00B969080}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,33 +81,33 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w785319805-500</t>
+  </si>
+  <si>
+    <t>e_w241822631-500</t>
+  </si>
+  <si>
+    <t>e_w104391636-500</t>
+  </si>
+  <si>
+    <t>e_w187988970-500</t>
+  </si>
+  <si>
+    <t>e_w170247312-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275</t>
+  </si>
+  <si>
+    <t>e_w151379730-500</t>
+  </si>
+  <si>
     <t>e_w150065045-500</t>
   </si>
   <si>
     <t>e_w106076988-500</t>
   </si>
   <si>
-    <t>e_JP7-275</t>
-  </si>
-  <si>
-    <t>e_w151379730-500</t>
-  </si>
-  <si>
-    <t>e_w170247312-500</t>
-  </si>
-  <si>
-    <t>e_w785319805-500</t>
-  </si>
-  <si>
-    <t>e_w187988970-500</t>
-  </si>
-  <si>
-    <t>e_w241822631-500</t>
-  </si>
-  <si>
-    <t>e_w104391636-500</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200026</t>
   </si>
   <si>
@@ -1269,81 +1269,81 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_JP29-500</t>
+  </si>
+  <si>
+    <t>e_w832823487-500</t>
+  </si>
+  <si>
+    <t>e_w250540807-1000</t>
+  </si>
+  <si>
+    <t>e_w142662111-500</t>
+  </si>
+  <si>
+    <t>e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_w256682313-500</t>
+  </si>
+  <si>
+    <t>e_JP30-500</t>
+  </si>
+  <si>
+    <t>e_r13768299-500</t>
+  </si>
+  <si>
+    <t>e_w459476442-500</t>
+  </si>
+  <si>
+    <t>e_JP74-500</t>
+  </si>
+  <si>
+    <t>e_JP76-500</t>
+  </si>
+  <si>
+    <t>e_w170366035-500</t>
+  </si>
+  <si>
+    <t>e_JP95-500</t>
+  </si>
+  <si>
+    <t>e_JP34-500</t>
+  </si>
+  <si>
+    <t>e_w241828221-500</t>
+  </si>
+  <si>
+    <t>e_JP57-500</t>
+  </si>
+  <si>
     <t>e_JP37-500</t>
   </si>
   <si>
-    <t>e_JP29-500</t>
-  </si>
-  <si>
-    <t>e_JP76-500</t>
-  </si>
-  <si>
-    <t>e_JP74-500</t>
-  </si>
-  <si>
-    <t>e_r13768299-500</t>
+    <t>e_w161870227-500</t>
+  </si>
+  <si>
+    <t>e_w116559939-500</t>
+  </si>
+  <si>
+    <t>e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_w170850727-500</t>
+  </si>
+  <si>
+    <t>e_JP155-500</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500</t>
   </si>
   <si>
     <t>e_JP137-500</t>
   </si>
   <si>
-    <t>e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_JP34-500</t>
-  </si>
-  <si>
-    <t>e_JP95-500</t>
-  </si>
-  <si>
-    <t>e_w170366035-500</t>
-  </si>
-  <si>
-    <t>e_JP57-500</t>
-  </si>
-  <si>
-    <t>e_w241828221-500</t>
-  </si>
-  <si>
     <t>e_w209429410-500</t>
   </si>
   <si>
-    <t>e_w116559939-500</t>
-  </si>
-  <si>
-    <t>e_w250540807-1000</t>
-  </si>
-  <si>
-    <t>e_w142662111-500</t>
-  </si>
-  <si>
-    <t>e_w256682313-500</t>
-  </si>
-  <si>
-    <t>e_w216953915-500</t>
-  </si>
-  <si>
-    <t>e_w161870227-500</t>
-  </si>
-  <si>
-    <t>e_w459476442-500</t>
-  </si>
-  <si>
-    <t>e_w832823487-500</t>
-  </si>
-  <si>
-    <t>e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_w170850727-500</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>e_JP155-500</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602267</t>
   </si>
   <si>
@@ -2028,12 +2028,12 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv_024</t>
+  </si>
+  <si>
     <t>elc_spv_026</t>
   </si>
   <si>
-    <t>elc_spv_024</t>
-  </si>
-  <si>
     <t>elc_spv_013</t>
   </si>
   <si>
@@ -2406,45 +2406,45 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/785319805-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/104391636-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/187988970-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/150065045-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/106076988-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/170247312-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
+    <t>Aggregated Plant - EMBER Gap - way/241822631-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - JP7-275_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/104391636-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/785319805-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/151379730-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/241822631-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/106076988-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/150065045-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/187988970-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Sendai-ko power station_1</t>
   </si>
   <si>
@@ -2988,111 +2988,111 @@
     <t>Yanatsu Nishiyama geothermal power plant_--</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - JP30-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP7-275_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP21-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/241828221-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/170974371-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/170850727-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/216502300-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP74-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/185029969-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - relation/17013811-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/832823487-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - JP95-500_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - JP1-275_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/161870227-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1038584990-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/171066843-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP29-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP137-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP34-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1030329139-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116559939-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP76-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/459476442-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/256682313-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP155-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/142662111-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/216953915-500_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/142662111-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/170850727-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP74-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/170974371-500_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/170366035-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP296-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/315662839-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP57-500_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - relation/13768299-500_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - JP57-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/161870227-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP29-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1038584990-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/171066843-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP30-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP21-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/241828221-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP7-275_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP34-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP1-275_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/256682313-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/170366035-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/315662839-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP155-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - way/209429410-500_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - JP37-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/250540807-1000_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - JP37-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/832823487-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/185029969-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - relation/17013811-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/216502300-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/116559939-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP76-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/459476442-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1030329139-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP137-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP296-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Akimoto hydroelectric plant_</t>
   </si>
   <si>
@@ -3579,10 +3579,10 @@
     <t>Aggregated Plant - IRENA Gap - JPN_248_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - JPN_211_Missing Onshore wind energy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - JPN_285_Missing Onshore wind energy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JPN_211_Missing Onshore wind energy Capacity</t>
   </si>
   <si>
     <t>AF</t>
@@ -5051,7 +5051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7824EA7C-BCF7-49CA-9CE8-E0DD2D85793E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88002BBA-011E-44A7-822C-696A6E076A2F}">
   <dimension ref="B9:T380"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5351,7 +5351,7 @@
         <v>163</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E15">
         <v>0.29791792799999994</v>
@@ -6583,7 +6583,7 @@
         <v>163</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E37">
         <v>9.2775936000000031E-2</v>
@@ -6639,7 +6639,7 @@
         <v>163</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E38">
         <v>9.2775936000000031E-2</v>
@@ -6975,7 +6975,7 @@
         <v>163</v>
       </c>
       <c r="D44" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E44">
         <v>9.0047232000000033E-2</v>
@@ -7031,7 +7031,7 @@
         <v>163</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E45">
         <v>9.0047232000000033E-2</v>
@@ -7087,7 +7087,7 @@
         <v>163</v>
       </c>
       <c r="D46" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E46">
         <v>9.0047232000000033E-2</v>
@@ -7255,7 +7255,7 @@
         <v>163</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E49">
         <v>9.2775936000000031E-2</v>
@@ -7311,7 +7311,7 @@
         <v>163</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E50">
         <v>9.2775936000000031E-2</v>
@@ -7367,7 +7367,7 @@
         <v>163</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E51">
         <v>9.2775936000000031E-2</v>
@@ -9439,7 +9439,7 @@
         <v>163</v>
       </c>
       <c r="D88" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E88">
         <v>9.2775936000000031E-2</v>
@@ -9495,7 +9495,7 @@
         <v>163</v>
       </c>
       <c r="D89" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E89">
         <v>9.2775936000000031E-2</v>
@@ -9551,7 +9551,7 @@
         <v>163</v>
       </c>
       <c r="D90" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E90">
         <v>9.2775936000000031E-2</v>
@@ -9607,7 +9607,7 @@
         <v>163</v>
       </c>
       <c r="D91" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E91">
         <v>9.2775936000000031E-2</v>
@@ -9663,7 +9663,7 @@
         <v>163</v>
       </c>
       <c r="D92" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E92">
         <v>9.2775936000000031E-2</v>
@@ -9719,7 +9719,7 @@
         <v>163</v>
       </c>
       <c r="D93" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E93">
         <v>9.2775936000000031E-2</v>
@@ -9775,7 +9775,7 @@
         <v>163</v>
       </c>
       <c r="D94" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E94">
         <v>9.2775936000000031E-2</v>
@@ -9831,7 +9831,7 @@
         <v>163</v>
       </c>
       <c r="D95" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E95">
         <v>9.2775936000000031E-2</v>
@@ -10279,7 +10279,7 @@
         <v>163</v>
       </c>
       <c r="D103" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E103">
         <v>9.2775936000000031E-2</v>
@@ -10335,7 +10335,7 @@
         <v>163</v>
       </c>
       <c r="D104" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E104">
         <v>9.2775936000000031E-2</v>
@@ -10391,7 +10391,7 @@
         <v>163</v>
       </c>
       <c r="D105" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E105">
         <v>9.2775936000000031E-2</v>
@@ -11455,7 +11455,7 @@
         <v>163</v>
       </c>
       <c r="D124" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E124">
         <v>9.2775936000000031E-2</v>
@@ -11959,7 +11959,7 @@
         <v>163</v>
       </c>
       <c r="D133" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E133">
         <v>0.24244176000000003</v>
@@ -12015,7 +12015,7 @@
         <v>163</v>
       </c>
       <c r="D134" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E134">
         <v>0.24244176000000003</v>
@@ -12631,7 +12631,7 @@
         <v>163</v>
       </c>
       <c r="D145" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E145">
         <v>0.24244176000000003</v>
@@ -12743,7 +12743,7 @@
         <v>163</v>
       </c>
       <c r="D147" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E147">
         <v>0.10778380800000002</v>
@@ -14591,7 +14591,7 @@
         <v>163</v>
       </c>
       <c r="D180" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E180">
         <v>0.31855824000000005</v>
@@ -15039,7 +15039,7 @@
         <v>288</v>
       </c>
       <c r="D188" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E188">
         <v>0.45553200000000005</v>
@@ -15095,7 +15095,7 @@
         <v>288</v>
       </c>
       <c r="D189" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E189">
         <v>0.45553200000000005</v>
@@ -15151,7 +15151,7 @@
         <v>288</v>
       </c>
       <c r="D190" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E190">
         <v>0.45553200000000005</v>
@@ -15711,7 +15711,7 @@
         <v>288</v>
       </c>
       <c r="D200" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E200">
         <v>0.47124000000000005</v>
@@ -15767,7 +15767,7 @@
         <v>288</v>
       </c>
       <c r="D201" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E201">
         <v>0.47124000000000005</v>
@@ -15823,7 +15823,7 @@
         <v>288</v>
       </c>
       <c r="D202" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E202">
         <v>0.47124000000000005</v>
@@ -17279,7 +17279,7 @@
         <v>288</v>
       </c>
       <c r="D228" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E228">
         <v>0.45553200000000005</v>
@@ -17335,7 +17335,7 @@
         <v>288</v>
       </c>
       <c r="D229" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E229">
         <v>0.45553200000000005</v>
@@ -18518,7 +18518,7 @@
         <v>288</v>
       </c>
       <c r="D255" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E255">
         <v>0.43982399999999999</v>
@@ -18553,7 +18553,7 @@
         <v>288</v>
       </c>
       <c r="D256" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E256">
         <v>0.43982399999999999</v>
@@ -18588,7 +18588,7 @@
         <v>288</v>
       </c>
       <c r="D257" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E257">
         <v>0.43982399999999999</v>
@@ -18623,7 +18623,7 @@
         <v>288</v>
       </c>
       <c r="D258" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E258">
         <v>0.43982399999999999</v>
@@ -18658,7 +18658,7 @@
         <v>288</v>
       </c>
       <c r="D259" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E259">
         <v>0.43982399999999999</v>
@@ -18693,7 +18693,7 @@
         <v>288</v>
       </c>
       <c r="D260" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E260">
         <v>0.43982399999999999</v>
@@ -18728,7 +18728,7 @@
         <v>288</v>
       </c>
       <c r="D261" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E261">
         <v>0.43982399999999999</v>
@@ -20408,7 +20408,7 @@
         <v>288</v>
       </c>
       <c r="D309" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E309">
         <v>0.42804300000000006</v>
@@ -20898,7 +20898,7 @@
         <v>288</v>
       </c>
       <c r="D323" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E323">
         <v>0.25918200000000002</v>
@@ -20933,7 +20933,7 @@
         <v>288</v>
       </c>
       <c r="D324" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E324">
         <v>0.26703600000000005</v>
@@ -21318,7 +21318,7 @@
         <v>288</v>
       </c>
       <c r="D335" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E335">
         <v>0.25132800000000005</v>
@@ -21353,7 +21353,7 @@
         <v>288</v>
       </c>
       <c r="D336" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E336">
         <v>0.26703600000000005</v>
@@ -21388,7 +21388,7 @@
         <v>288</v>
       </c>
       <c r="D337" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E337">
         <v>0.26703600000000005</v>
@@ -21423,7 +21423,7 @@
         <v>288</v>
       </c>
       <c r="D338" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E338">
         <v>0.26703600000000005</v>
@@ -21458,7 +21458,7 @@
         <v>288</v>
       </c>
       <c r="D339" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E339">
         <v>0.26703600000000005</v>
@@ -21493,7 +21493,7 @@
         <v>288</v>
       </c>
       <c r="D340" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E340">
         <v>0.26703600000000005</v>
@@ -21948,7 +21948,7 @@
         <v>636</v>
       </c>
       <c r="D353" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E353">
         <v>0.172788</v>
@@ -22123,7 +22123,7 @@
         <v>636</v>
       </c>
       <c r="D358" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E358">
         <v>0.25918200000000002</v>
@@ -22158,7 +22158,7 @@
         <v>636</v>
       </c>
       <c r="D359" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E359">
         <v>0.25918200000000002</v>
@@ -22613,7 +22613,7 @@
         <v>636</v>
       </c>
       <c r="D372" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E372">
         <v>0.23562000000000002</v>
@@ -22926,7 +22926,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A7A9AA-B03D-411E-B77F-989B55C46708}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE8D958-774D-408B-AD63-08A5B6DEF519}">
   <dimension ref="B9:T1231"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23008,7 +23008,7 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>6.7648321797158462E-2</v>
+        <v>5.9113253159199221E-2</v>
       </c>
       <c r="G11">
         <v>0.29620800000000003</v>
@@ -23061,7 +23061,7 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>9.2621300404520698E-2</v>
+        <v>9.6414664243613696E-2</v>
       </c>
       <c r="G12">
         <v>0.29620800000000003</v>
@@ -23114,7 +23114,7 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>6.1768607846564322E-2</v>
+        <v>5.9113253159199221E-2</v>
       </c>
       <c r="G13">
         <v>0.29620800000000003</v>
@@ -23167,13 +23167,13 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>5.5288277954780453E-2</v>
+        <v>0.12233598381074919</v>
       </c>
       <c r="G14">
         <v>0.29620800000000003</v>
       </c>
       <c r="H14">
-        <v>4829.9999999999982</v>
+        <v>4829.9999999999991</v>
       </c>
       <c r="I14">
         <v>164.45</v>
@@ -23273,7 +23273,7 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>5.9113253159199221E-2</v>
+        <v>6.1768607846564322E-2</v>
       </c>
       <c r="G16">
         <v>0.29620800000000003</v>
@@ -23326,13 +23326,13 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.12233598381074919</v>
+        <v>5.5288277954780453E-2</v>
       </c>
       <c r="G17">
         <v>0.29620800000000003</v>
       </c>
       <c r="H17">
-        <v>4829.9999999999991</v>
+        <v>4829.9999999999982</v>
       </c>
       <c r="I17">
         <v>164.45</v>
@@ -23379,7 +23379,7 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>9.6414664243613696E-2</v>
+        <v>6.7648321797158462E-2</v>
       </c>
       <c r="G18">
         <v>0.29620800000000003</v>
@@ -23432,7 +23432,7 @@
         <v>2022</v>
       </c>
       <c r="F19">
-        <v>5.9113253159199221E-2</v>
+        <v>9.2621300404520698E-2</v>
       </c>
       <c r="G19">
         <v>0.29620800000000003</v>
@@ -23479,7 +23479,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E20">
         <v>2025</v>
@@ -23956,7 +23956,7 @@
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E29">
         <v>2021</v>
@@ -24062,7 +24062,7 @@
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E31">
         <v>2020</v>
@@ -24274,7 +24274,7 @@
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E35">
         <v>2023</v>
@@ -24486,7 +24486,7 @@
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E39">
         <v>2021</v>
@@ -24592,7 +24592,7 @@
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E41">
         <v>2023</v>
@@ -24804,7 +24804,7 @@
         <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E45">
         <v>2024</v>
@@ -24963,7 +24963,7 @@
         <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E48">
         <v>1982</v>
@@ -25016,7 +25016,7 @@
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E49">
         <v>2024</v>
@@ -25069,7 +25069,7 @@
         <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E50">
         <v>2022</v>
@@ -25387,7 +25387,7 @@
         <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E56">
         <v>2023</v>
@@ -25546,7 +25546,7 @@
         <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E59">
         <v>2022</v>
@@ -25705,7 +25705,7 @@
         <v>13</v>
       </c>
       <c r="D62" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E62">
         <v>2023</v>
@@ -25758,7 +25758,7 @@
         <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E63">
         <v>2015</v>
@@ -25917,7 +25917,7 @@
         <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E66">
         <v>2018</v>
@@ -25970,7 +25970,7 @@
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E67">
         <v>2015</v>
@@ -26023,7 +26023,7 @@
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E68">
         <v>2022</v>
@@ -26129,7 +26129,7 @@
         <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E70">
         <v>2013</v>
@@ -26235,7 +26235,7 @@
         <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E72">
         <v>2023</v>
@@ -26288,7 +26288,7 @@
         <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E73">
         <v>2026</v>
@@ -26341,7 +26341,7 @@
         <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E74">
         <v>2020</v>
@@ -26447,7 +26447,7 @@
         <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E76">
         <v>2016</v>
@@ -27348,7 +27348,7 @@
         <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E93">
         <v>2013</v>
@@ -27878,7 +27878,7 @@
         <v>13</v>
       </c>
       <c r="D103" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E103">
         <v>2018</v>
@@ -27931,7 +27931,7 @@
         <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E104">
         <v>2013</v>
@@ -28991,7 +28991,7 @@
         <v>13</v>
       </c>
       <c r="D124" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E124">
         <v>2021</v>
@@ -29839,7 +29839,7 @@
         <v>163</v>
       </c>
       <c r="D140" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E140">
         <v>2021</v>
@@ -31005,7 +31005,7 @@
         <v>163</v>
       </c>
       <c r="D162" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E162">
         <v>1980</v>
@@ -31058,7 +31058,7 @@
         <v>163</v>
       </c>
       <c r="D163" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E163">
         <v>2022</v>
@@ -31376,7 +31376,7 @@
         <v>163</v>
       </c>
       <c r="D169" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E169">
         <v>1970</v>
@@ -31429,7 +31429,7 @@
         <v>163</v>
       </c>
       <c r="D170" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E170">
         <v>2006</v>
@@ -31482,7 +31482,7 @@
         <v>163</v>
       </c>
       <c r="D171" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E171">
         <v>2022</v>
@@ -31641,7 +31641,7 @@
         <v>163</v>
       </c>
       <c r="D174" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E174">
         <v>1977</v>
@@ -31694,7 +31694,7 @@
         <v>163</v>
       </c>
       <c r="D175" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E175">
         <v>1978</v>
@@ -31747,7 +31747,7 @@
         <v>163</v>
       </c>
       <c r="D176" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E176">
         <v>1987</v>
@@ -33708,7 +33708,7 @@
         <v>163</v>
       </c>
       <c r="D213" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E213">
         <v>1991</v>
@@ -33761,7 +33761,7 @@
         <v>163</v>
       </c>
       <c r="D214" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E214">
         <v>1999</v>
@@ -33814,7 +33814,7 @@
         <v>163</v>
       </c>
       <c r="D215" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E215">
         <v>2004</v>
@@ -33867,7 +33867,7 @@
         <v>163</v>
       </c>
       <c r="D216" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E216">
         <v>2007</v>
@@ -33920,7 +33920,7 @@
         <v>163</v>
       </c>
       <c r="D217" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E217">
         <v>2010</v>
@@ -33973,7 +33973,7 @@
         <v>163</v>
       </c>
       <c r="D218" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E218">
         <v>2018</v>
@@ -34026,7 +34026,7 @@
         <v>163</v>
       </c>
       <c r="D219" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E219">
         <v>2022</v>
@@ -34079,7 +34079,7 @@
         <v>163</v>
       </c>
       <c r="D220" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E220">
         <v>2019</v>
@@ -34503,7 +34503,7 @@
         <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E228">
         <v>1996</v>
@@ -34556,7 +34556,7 @@
         <v>163</v>
       </c>
       <c r="D229" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E229">
         <v>1997</v>
@@ -34609,7 +34609,7 @@
         <v>163</v>
       </c>
       <c r="D230" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E230">
         <v>1999</v>
@@ -35616,7 +35616,7 @@
         <v>163</v>
       </c>
       <c r="D249" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E249">
         <v>2017</v>
@@ -36093,7 +36093,7 @@
         <v>163</v>
       </c>
       <c r="D258" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E258">
         <v>1983</v>
@@ -36146,7 +36146,7 @@
         <v>163</v>
       </c>
       <c r="D259" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E259">
         <v>1983</v>
@@ -36729,7 +36729,7 @@
         <v>163</v>
       </c>
       <c r="D270" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E270">
         <v>1985</v>
@@ -36835,7 +36835,7 @@
         <v>163</v>
       </c>
       <c r="D272" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E272">
         <v>2001</v>
@@ -38584,7 +38584,7 @@
         <v>163</v>
       </c>
       <c r="D305" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E305">
         <v>2002</v>
@@ -39008,7 +39008,7 @@
         <v>288</v>
       </c>
       <c r="D313" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E313">
         <v>2014</v>
@@ -39061,7 +39061,7 @@
         <v>288</v>
       </c>
       <c r="D314" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E314">
         <v>2014</v>
@@ -39114,7 +39114,7 @@
         <v>288</v>
       </c>
       <c r="D315" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E315">
         <v>2014</v>
@@ -39644,7 +39644,7 @@
         <v>288</v>
       </c>
       <c r="D325" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E325">
         <v>2024</v>
@@ -39697,7 +39697,7 @@
         <v>288</v>
       </c>
       <c r="D326" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E326">
         <v>2025</v>
@@ -39750,7 +39750,7 @@
         <v>288</v>
       </c>
       <c r="D327" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E327">
         <v>2025</v>
@@ -41128,7 +41128,7 @@
         <v>288</v>
       </c>
       <c r="D353" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E353">
         <v>2015</v>
@@ -41181,7 +41181,7 @@
         <v>288</v>
       </c>
       <c r="D354" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E354">
         <v>2016</v>
@@ -42559,7 +42559,7 @@
         <v>288</v>
       </c>
       <c r="D380" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E380">
         <v>1998</v>
@@ -42612,7 +42612,7 @@
         <v>288</v>
       </c>
       <c r="D381" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E381">
         <v>1999</v>
@@ -42665,7 +42665,7 @@
         <v>288</v>
       </c>
       <c r="D382" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E382">
         <v>2000</v>
@@ -42718,7 +42718,7 @@
         <v>288</v>
       </c>
       <c r="D383" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E383">
         <v>2002</v>
@@ -42771,7 +42771,7 @@
         <v>288</v>
       </c>
       <c r="D384" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E384">
         <v>2004</v>
@@ -42824,7 +42824,7 @@
         <v>288</v>
       </c>
       <c r="D385" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E385">
         <v>2015</v>
@@ -42877,7 +42877,7 @@
         <v>288</v>
       </c>
       <c r="D386" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -45421,7 +45421,7 @@
         <v>288</v>
       </c>
       <c r="D434" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E434">
         <v>2010</v>
@@ -46163,7 +46163,7 @@
         <v>288</v>
       </c>
       <c r="D448" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E448">
         <v>1978</v>
@@ -46216,7 +46216,7 @@
         <v>288</v>
       </c>
       <c r="D449" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E449">
         <v>1983</v>
@@ -46799,7 +46799,7 @@
         <v>288</v>
       </c>
       <c r="D460" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E460">
         <v>1984</v>
@@ -46852,7 +46852,7 @@
         <v>288</v>
       </c>
       <c r="D461" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E461">
         <v>1971</v>
@@ -46905,7 +46905,7 @@
         <v>288</v>
       </c>
       <c r="D462" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E462">
         <v>1972</v>
@@ -46958,7 +46958,7 @@
         <v>288</v>
       </c>
       <c r="D463" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E463">
         <v>1978</v>
@@ -47011,7 +47011,7 @@
         <v>288</v>
       </c>
       <c r="D464" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E464">
         <v>1999</v>
@@ -47064,7 +47064,7 @@
         <v>288</v>
       </c>
       <c r="D465" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E465">
         <v>2010</v>
@@ -47965,7 +47965,7 @@
         <v>393</v>
       </c>
       <c r="D482" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E482">
         <v>1975</v>
@@ -48018,7 +48018,7 @@
         <v>393</v>
       </c>
       <c r="D483" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E483">
         <v>1994</v>
@@ -48071,7 +48071,7 @@
         <v>393</v>
       </c>
       <c r="D484" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E484">
         <v>2019</v>
@@ -48124,7 +48124,7 @@
         <v>393</v>
       </c>
       <c r="D485" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E485">
         <v>2027</v>
@@ -49290,25 +49290,25 @@
         <v>409</v>
       </c>
       <c r="D507" t="s">
-        <v>410</v>
+        <v>19</v>
       </c>
       <c r="E507">
         <v>2022</v>
       </c>
       <c r="F507">
-        <v>0.36108635902240982</v>
+        <v>0.13713305223705793</v>
       </c>
       <c r="G507">
         <v>1</v>
       </c>
       <c r="H507">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I507">
-        <v>57.499999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J507">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K507">
         <v>100</v>
@@ -49343,7 +49343,7 @@
         <v>409</v>
       </c>
       <c r="D508" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E508">
         <v>2022</v>
@@ -49396,25 +49396,25 @@
         <v>409</v>
       </c>
       <c r="D509" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E509">
         <v>2022</v>
       </c>
       <c r="F509">
-        <v>0.28837823065511065</v>
+        <v>0.52767080502850028</v>
       </c>
       <c r="G509">
         <v>1</v>
       </c>
       <c r="H509">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I509">
-        <v>63.25</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J509">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K509">
         <v>100</v>
@@ -49449,25 +49449,25 @@
         <v>409</v>
       </c>
       <c r="D510" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E510">
         <v>2022</v>
       </c>
       <c r="F510">
-        <v>0.12762270633247449</v>
+        <v>0.40495666432419791</v>
       </c>
       <c r="G510">
         <v>1</v>
       </c>
       <c r="H510">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I510">
-        <v>63.25</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J510">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K510">
         <v>100</v>
@@ -49502,13 +49502,13 @@
         <v>409</v>
       </c>
       <c r="D511" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="E511">
         <v>2022</v>
       </c>
       <c r="F511">
-        <v>1.0955304911376598</v>
+        <v>0.46079159834465555</v>
       </c>
       <c r="G511">
         <v>1</v>
@@ -49555,13 +49555,13 @@
         <v>409</v>
       </c>
       <c r="D512" t="s">
-        <v>414</v>
+        <v>86</v>
       </c>
       <c r="E512">
         <v>2022</v>
       </c>
       <c r="F512">
-        <v>7.6696337940188999E-2</v>
+        <v>0.18867299133286491</v>
       </c>
       <c r="G512">
         <v>1</v>
@@ -49570,7 +49570,7 @@
         <v>3450</v>
       </c>
       <c r="I512">
-        <v>63.249999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J512">
         <v>2.3100000000000005</v>
@@ -49608,13 +49608,13 @@
         <v>409</v>
       </c>
       <c r="D513" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E513">
         <v>2022</v>
       </c>
       <c r="F513">
-        <v>0.59270929960178054</v>
+        <v>0.42336378542984326</v>
       </c>
       <c r="G513">
         <v>1</v>
@@ -49661,13 +49661,13 @@
         <v>409</v>
       </c>
       <c r="D514" t="s">
-        <v>31</v>
+        <v>415</v>
       </c>
       <c r="E514">
         <v>2022</v>
       </c>
       <c r="F514">
-        <v>7.9150620754275036E-2</v>
+        <v>0.10338666354337477</v>
       </c>
       <c r="G514">
         <v>1</v>
@@ -49676,7 +49676,7 @@
         <v>3450</v>
       </c>
       <c r="I514">
-        <v>63.250000000000007</v>
+        <v>63.25</v>
       </c>
       <c r="J514">
         <v>2.3100000000000005</v>
@@ -49720,19 +49720,19 @@
         <v>2022</v>
       </c>
       <c r="F515">
-        <v>0.1840712110564536</v>
+        <v>0.48318692902319071</v>
       </c>
       <c r="G515">
         <v>1</v>
       </c>
       <c r="H515">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I515">
-        <v>63.25</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J515">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K515">
         <v>100</v>
@@ -49773,19 +49773,19 @@
         <v>2022</v>
       </c>
       <c r="F516">
-        <v>0.94673959553369302</v>
+        <v>7.6696337940188999E-2</v>
       </c>
       <c r="G516">
         <v>1</v>
       </c>
       <c r="H516">
-        <v>3000.0000000000005</v>
+        <v>3450</v>
       </c>
       <c r="I516">
-        <v>57.499999999999993</v>
+        <v>63.249999999999993</v>
       </c>
       <c r="J516">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K516">
         <v>100</v>
@@ -49820,13 +49820,13 @@
         <v>409</v>
       </c>
       <c r="D517" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="E517">
         <v>2022</v>
       </c>
       <c r="F517">
-        <v>0.36814242211290721</v>
+        <v>1.0955304911376598</v>
       </c>
       <c r="G517">
         <v>1</v>
@@ -49873,13 +49873,13 @@
         <v>409</v>
       </c>
       <c r="D518" t="s">
-        <v>419</v>
+        <v>142</v>
       </c>
       <c r="E518">
         <v>2022</v>
       </c>
       <c r="F518">
-        <v>0.10860201452330762</v>
+        <v>0.1840712110564536</v>
       </c>
       <c r="G518">
         <v>1</v>
@@ -49926,13 +49926,13 @@
         <v>409</v>
       </c>
       <c r="D519" t="s">
-        <v>25</v>
+        <v>418</v>
       </c>
       <c r="E519">
         <v>2022</v>
       </c>
       <c r="F519">
-        <v>0.11995307253845558</v>
+        <v>8.6513469196533188E-2</v>
       </c>
       <c r="G519">
         <v>1</v>
@@ -49979,13 +49979,13 @@
         <v>409</v>
       </c>
       <c r="D520" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E520">
         <v>2022</v>
       </c>
       <c r="F520">
-        <v>0.28500359178574231</v>
+        <v>0.12762270633247449</v>
       </c>
       <c r="G520">
         <v>1</v>
@@ -50032,25 +50032,25 @@
         <v>409</v>
       </c>
       <c r="D521" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="E521">
         <v>2022</v>
       </c>
       <c r="F521">
-        <v>0.92955961583509072</v>
+        <v>0.28837823065511065</v>
       </c>
       <c r="G521">
         <v>1</v>
       </c>
       <c r="H521">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I521">
-        <v>57.499999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J521">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K521">
         <v>100</v>
@@ -50085,13 +50085,13 @@
         <v>409</v>
       </c>
       <c r="D522" t="s">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="E522">
         <v>2022</v>
       </c>
       <c r="F522">
-        <v>0.1840712110564536</v>
+        <v>0.12915663309127828</v>
       </c>
       <c r="G522">
         <v>1</v>
@@ -50138,13 +50138,13 @@
         <v>409</v>
       </c>
       <c r="D523" t="s">
-        <v>16</v>
+        <v>421</v>
       </c>
       <c r="E523">
         <v>2022</v>
       </c>
       <c r="F523">
-        <v>0.13713305223705793</v>
+        <v>0.10860201452330762</v>
       </c>
       <c r="G523">
         <v>1</v>
@@ -50191,25 +50191,25 @@
         <v>409</v>
       </c>
       <c r="D524" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E524">
         <v>2022</v>
       </c>
       <c r="F524">
-        <v>9.2955961583509064E-2</v>
+        <v>0.36814242211290721</v>
       </c>
       <c r="G524">
         <v>1</v>
       </c>
       <c r="H524">
-        <v>3450.0000000000005</v>
+        <v>3000</v>
       </c>
       <c r="I524">
-        <v>63.249999999999993</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J524">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K524">
         <v>100</v>
@@ -50244,25 +50244,25 @@
         <v>409</v>
       </c>
       <c r="D525" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E525">
         <v>2022</v>
       </c>
       <c r="F525">
-        <v>7.1480986960256149E-2</v>
+        <v>0.94673959553369302</v>
       </c>
       <c r="G525">
         <v>1</v>
       </c>
       <c r="H525">
-        <v>3450</v>
+        <v>3000.0000000000005</v>
       </c>
       <c r="I525">
-        <v>63.249999999999993</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J525">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K525">
         <v>100</v>
@@ -50297,22 +50297,22 @@
         <v>409</v>
       </c>
       <c r="D526" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E526">
         <v>2022</v>
       </c>
       <c r="F526">
-        <v>0.14664339814164137</v>
+        <v>9.2955961583509064E-2</v>
       </c>
       <c r="G526">
         <v>1</v>
       </c>
       <c r="H526">
-        <v>3450</v>
+        <v>3450.0000000000005</v>
       </c>
       <c r="I526">
-        <v>63.25</v>
+        <v>63.249999999999993</v>
       </c>
       <c r="J526">
         <v>2.3100000000000005</v>
@@ -50350,13 +50350,13 @@
         <v>409</v>
       </c>
       <c r="D527" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="E527">
         <v>2022</v>
       </c>
       <c r="F527">
-        <v>0.40495666432419791</v>
+        <v>0.92955961583509072</v>
       </c>
       <c r="G527">
         <v>1</v>
@@ -50409,19 +50409,19 @@
         <v>2022</v>
       </c>
       <c r="F528">
-        <v>0.46079159834465555</v>
+        <v>0.28500359178574231</v>
       </c>
       <c r="G528">
         <v>1</v>
       </c>
       <c r="H528">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I528">
-        <v>57.499999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J528">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K528">
         <v>100</v>
@@ -50456,13 +50456,13 @@
         <v>409</v>
       </c>
       <c r="D529" t="s">
-        <v>426</v>
+        <v>25</v>
       </c>
       <c r="E529">
         <v>2022</v>
       </c>
       <c r="F529">
-        <v>0.10338666354337477</v>
+        <v>0.11995307253845558</v>
       </c>
       <c r="G529">
         <v>1</v>
@@ -50509,13 +50509,13 @@
         <v>409</v>
       </c>
       <c r="D530" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E530">
         <v>2022</v>
       </c>
       <c r="F530">
-        <v>0.42336378542984326</v>
+        <v>0.36108635902240982</v>
       </c>
       <c r="G530">
         <v>1</v>
@@ -50668,7 +50668,7 @@
         <v>409</v>
       </c>
       <c r="D533" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E533">
         <v>2022</v>
@@ -50721,13 +50721,13 @@
         <v>409</v>
       </c>
       <c r="D534" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E534">
         <v>2022</v>
       </c>
       <c r="F534">
-        <v>8.6513469196533188E-2</v>
+        <v>0.14664339814164137</v>
       </c>
       <c r="G534">
         <v>1</v>
@@ -50774,25 +50774,25 @@
         <v>409</v>
       </c>
       <c r="D535" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E535">
         <v>2022</v>
       </c>
       <c r="F535">
-        <v>0.52767080502850028</v>
+        <v>0.1840712110564536</v>
       </c>
       <c r="G535">
         <v>1</v>
       </c>
       <c r="H535">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I535">
-        <v>57.499999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J535">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K535">
         <v>100</v>
@@ -50827,13 +50827,13 @@
         <v>409</v>
       </c>
       <c r="D536" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E536">
         <v>2022</v>
       </c>
       <c r="F536">
-        <v>0.48318692902319071</v>
+        <v>0.37305098774107925</v>
       </c>
       <c r="G536">
         <v>1</v>
@@ -50842,7 +50842,7 @@
         <v>3000</v>
       </c>
       <c r="I536">
-        <v>57.499999999999993</v>
+        <v>57.499999999999986</v>
       </c>
       <c r="J536">
         <v>2.1</v>
@@ -50880,13 +50880,13 @@
         <v>409</v>
       </c>
       <c r="D537" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E537">
         <v>2022</v>
       </c>
       <c r="F537">
-        <v>0.37305098774107925</v>
+        <v>0.39268525025376771</v>
       </c>
       <c r="G537">
         <v>1</v>
@@ -50895,7 +50895,7 @@
         <v>3000</v>
       </c>
       <c r="I537">
-        <v>57.499999999999986</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J537">
         <v>2.1</v>
@@ -50933,7 +50933,7 @@
         <v>409</v>
       </c>
       <c r="D538" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E538">
         <v>2022</v>
@@ -50986,25 +50986,25 @@
         <v>409</v>
       </c>
       <c r="D539" t="s">
-        <v>434</v>
+        <v>31</v>
       </c>
       <c r="E539">
         <v>2022</v>
       </c>
       <c r="F539">
-        <v>0.39268525025376771</v>
+        <v>7.9150620754275036E-2</v>
       </c>
       <c r="G539">
         <v>1</v>
       </c>
       <c r="H539">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I539">
-        <v>57.499999999999993</v>
+        <v>63.250000000000007</v>
       </c>
       <c r="J539">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K539">
         <v>100</v>
@@ -51039,25 +51039,25 @@
         <v>409</v>
       </c>
       <c r="D540" t="s">
-        <v>86</v>
+        <v>433</v>
       </c>
       <c r="E540">
         <v>2022</v>
       </c>
       <c r="F540">
-        <v>0.18867299133286491</v>
+        <v>0.59270929960178054</v>
       </c>
       <c r="G540">
         <v>1</v>
       </c>
       <c r="H540">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I540">
-        <v>63.25</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J540">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K540">
         <v>100</v>
@@ -51092,13 +51092,13 @@
         <v>409</v>
       </c>
       <c r="D541" t="s">
-        <v>35</v>
+        <v>434</v>
       </c>
       <c r="E541">
         <v>2022</v>
       </c>
       <c r="F541">
-        <v>0.12915663309127828</v>
+        <v>7.1480986960256149E-2</v>
       </c>
       <c r="G541">
         <v>1</v>
@@ -51107,7 +51107,7 @@
         <v>3450</v>
       </c>
       <c r="I541">
-        <v>63.25</v>
+        <v>63.249999999999993</v>
       </c>
       <c r="J541">
         <v>2.3100000000000005</v>
@@ -51198,7 +51198,7 @@
         <v>409</v>
       </c>
       <c r="D543" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E543">
         <v>1964</v>
@@ -51251,7 +51251,7 @@
         <v>409</v>
       </c>
       <c r="D544" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E544">
         <v>1981</v>
@@ -51357,7 +51357,7 @@
         <v>409</v>
       </c>
       <c r="D546" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="E546">
         <v>1961</v>
@@ -51410,7 +51410,7 @@
         <v>409</v>
       </c>
       <c r="D547" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="E547">
         <v>1952</v>
@@ -51463,7 +51463,7 @@
         <v>409</v>
       </c>
       <c r="D548" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="E548">
         <v>1963</v>
@@ -51622,7 +51622,7 @@
         <v>409</v>
       </c>
       <c r="D551" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E551">
         <v>1954</v>
@@ -51728,7 +51728,7 @@
         <v>409</v>
       </c>
       <c r="D553" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="E553">
         <v>1963</v>
@@ -51781,7 +51781,7 @@
         <v>409</v>
       </c>
       <c r="D554" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E554">
         <v>1970</v>
@@ -51834,7 +51834,7 @@
         <v>409</v>
       </c>
       <c r="D555" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="E555">
         <v>1968</v>
@@ -52099,7 +52099,7 @@
         <v>409</v>
       </c>
       <c r="D560" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E560">
         <v>1976</v>
@@ -52152,7 +52152,7 @@
         <v>409</v>
       </c>
       <c r="D561" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="E561">
         <v>1961</v>
@@ -52258,7 +52258,7 @@
         <v>409</v>
       </c>
       <c r="D563" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="E563">
         <v>1968</v>
@@ -52364,7 +52364,7 @@
         <v>409</v>
       </c>
       <c r="D565" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E565">
         <v>1965</v>
@@ -52523,7 +52523,7 @@
         <v>409</v>
       </c>
       <c r="D568" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="E568">
         <v>1956</v>
@@ -52576,7 +52576,7 @@
         <v>409</v>
       </c>
       <c r="D569" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="E569">
         <v>1994</v>
@@ -52629,7 +52629,7 @@
         <v>409</v>
       </c>
       <c r="D570" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E570">
         <v>1960</v>
@@ -52682,7 +52682,7 @@
         <v>409</v>
       </c>
       <c r="D571" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E571">
         <v>1978</v>
@@ -52735,7 +52735,7 @@
         <v>409</v>
       </c>
       <c r="D572" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E572">
         <v>1963</v>
@@ -52894,7 +52894,7 @@
         <v>409</v>
       </c>
       <c r="D575" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E575">
         <v>1956</v>
@@ -53053,7 +53053,7 @@
         <v>409</v>
       </c>
       <c r="D578" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="E578">
         <v>1973</v>
@@ -53265,7 +53265,7 @@
         <v>409</v>
       </c>
       <c r="D582" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E582">
         <v>1959</v>
@@ -53371,7 +53371,7 @@
         <v>409</v>
       </c>
       <c r="D584" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="E584">
         <v>1979</v>
@@ -53424,7 +53424,7 @@
         <v>409</v>
       </c>
       <c r="D585" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="E585">
         <v>1979</v>
@@ -53530,7 +53530,7 @@
         <v>409</v>
       </c>
       <c r="D587" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E587">
         <v>1960</v>
@@ -53583,7 +53583,7 @@
         <v>409</v>
       </c>
       <c r="D588" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E588">
         <v>1959</v>
@@ -53689,7 +53689,7 @@
         <v>409</v>
       </c>
       <c r="D590" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="E590">
         <v>1923</v>
@@ -53742,7 +53742,7 @@
         <v>409</v>
       </c>
       <c r="D591" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="E591">
         <v>1957</v>
@@ -53795,7 +53795,7 @@
         <v>409</v>
       </c>
       <c r="D592" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E592">
         <v>1976</v>
@@ -53848,7 +53848,7 @@
         <v>409</v>
       </c>
       <c r="D593" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E593">
         <v>1989</v>
@@ -53901,7 +53901,7 @@
         <v>409</v>
       </c>
       <c r="D594" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E594">
         <v>1970</v>
@@ -54060,7 +54060,7 @@
         <v>409</v>
       </c>
       <c r="D597" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E597">
         <v>1967</v>
@@ -54537,7 +54537,7 @@
         <v>409</v>
       </c>
       <c r="D606" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="E606">
         <v>1936</v>
@@ -54696,7 +54696,7 @@
         <v>409</v>
       </c>
       <c r="D609" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E609">
         <v>1959</v>
@@ -54749,7 +54749,7 @@
         <v>409</v>
       </c>
       <c r="D610" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E610">
         <v>1975</v>
@@ -55279,7 +55279,7 @@
         <v>409</v>
       </c>
       <c r="D620" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E620">
         <v>1955</v>
@@ -55385,7 +55385,7 @@
         <v>409</v>
       </c>
       <c r="D622" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E622">
         <v>1930</v>
@@ -55438,7 +55438,7 @@
         <v>409</v>
       </c>
       <c r="D623" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E623">
         <v>1942</v>
@@ -55491,7 +55491,7 @@
         <v>409</v>
       </c>
       <c r="D624" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E624">
         <v>1975</v>
@@ -55544,7 +55544,7 @@
         <v>409</v>
       </c>
       <c r="D625" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E625">
         <v>1980</v>
@@ -55597,7 +55597,7 @@
         <v>409</v>
       </c>
       <c r="D626" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E626">
         <v>1966</v>
@@ -55650,7 +55650,7 @@
         <v>409</v>
       </c>
       <c r="D627" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="E627">
         <v>1963</v>
@@ -56127,7 +56127,7 @@
         <v>409</v>
       </c>
       <c r="D636" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E636">
         <v>1962</v>
@@ -56180,7 +56180,7 @@
         <v>409</v>
       </c>
       <c r="D637" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E637">
         <v>1958</v>
@@ -56233,7 +56233,7 @@
         <v>409</v>
       </c>
       <c r="D638" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E638">
         <v>1991</v>
@@ -56286,7 +56286,7 @@
         <v>409</v>
       </c>
       <c r="D639" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="E639">
         <v>1936</v>
@@ -56339,7 +56339,7 @@
         <v>409</v>
       </c>
       <c r="D640" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="E640">
         <v>1969</v>
@@ -56530,7 +56530,7 @@
         <v>409</v>
       </c>
       <c r="D644" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E644">
         <v>2022</v>
@@ -56562,7 +56562,7 @@
         <v>409</v>
       </c>
       <c r="D645" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E645">
         <v>1972</v>
@@ -56594,7 +56594,7 @@
         <v>409</v>
       </c>
       <c r="D646" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E646">
         <v>2022</v>
@@ -56690,7 +56690,7 @@
         <v>409</v>
       </c>
       <c r="D649" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E649">
         <v>1924</v>
@@ -57138,7 +57138,7 @@
         <v>409</v>
       </c>
       <c r="D663" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="E663">
         <v>1960</v>
@@ -57298,7 +57298,7 @@
         <v>551</v>
       </c>
       <c r="D668" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="E668">
         <v>1962</v>
@@ -57362,7 +57362,7 @@
         <v>551</v>
       </c>
       <c r="D670" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E670">
         <v>1964</v>
@@ -57394,7 +57394,7 @@
         <v>551</v>
       </c>
       <c r="D671" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="E671">
         <v>1988</v>
@@ -57426,7 +57426,7 @@
         <v>551</v>
       </c>
       <c r="D672" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="E672">
         <v>2005</v>
@@ -57458,7 +57458,7 @@
         <v>551</v>
       </c>
       <c r="D673" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E673">
         <v>1999</v>
@@ -57490,7 +57490,7 @@
         <v>551</v>
       </c>
       <c r="D674" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="E674">
         <v>2014</v>
@@ -57522,7 +57522,7 @@
         <v>551</v>
       </c>
       <c r="D675" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="E675">
         <v>2033</v>
@@ -57554,7 +57554,7 @@
         <v>551</v>
       </c>
       <c r="D676" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="E676">
         <v>1986</v>
@@ -57650,7 +57650,7 @@
         <v>551</v>
       </c>
       <c r="D679" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E679">
         <v>1974</v>
@@ -57682,7 +57682,7 @@
         <v>551</v>
       </c>
       <c r="D680" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="E680">
         <v>1973</v>
@@ -57746,7 +57746,7 @@
         <v>551</v>
       </c>
       <c r="D682" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E682">
         <v>1992</v>
@@ -57778,7 +57778,7 @@
         <v>551</v>
       </c>
       <c r="D683" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E683">
         <v>1996</v>
@@ -57810,7 +57810,7 @@
         <v>551</v>
       </c>
       <c r="D684" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E684">
         <v>1978</v>
@@ -57842,7 +57842,7 @@
         <v>551</v>
       </c>
       <c r="D685" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E685">
         <v>1980</v>
@@ -57874,7 +57874,7 @@
         <v>551</v>
       </c>
       <c r="D686" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E686">
         <v>1980</v>
@@ -57906,7 +57906,7 @@
         <v>551</v>
       </c>
       <c r="D687" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="E687">
         <v>1974</v>
@@ -57938,7 +57938,7 @@
         <v>551</v>
       </c>
       <c r="D688" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="E688">
         <v>2007</v>
@@ -58002,7 +58002,7 @@
         <v>551</v>
       </c>
       <c r="D690" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E690">
         <v>1968</v>
@@ -58066,7 +58066,7 @@
         <v>551</v>
       </c>
       <c r="D692" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="E692">
         <v>1973</v>
@@ -58098,7 +58098,7 @@
         <v>551</v>
       </c>
       <c r="D693" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="E693">
         <v>1994</v>
@@ -58130,7 +58130,7 @@
         <v>551</v>
       </c>
       <c r="D694" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E694">
         <v>1965</v>
@@ -58162,7 +58162,7 @@
         <v>551</v>
       </c>
       <c r="D695" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E695">
         <v>1983</v>
@@ -58226,7 +58226,7 @@
         <v>551</v>
       </c>
       <c r="D697" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E697">
         <v>1982</v>
@@ -58290,7 +58290,7 @@
         <v>551</v>
       </c>
       <c r="D699" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E699">
         <v>1965</v>
@@ -58354,7 +58354,7 @@
         <v>409</v>
       </c>
       <c r="D701" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="E701">
         <v>1981</v>
@@ -58418,7 +58418,7 @@
         <v>409</v>
       </c>
       <c r="D703" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E703">
         <v>1925</v>
@@ -58450,7 +58450,7 @@
         <v>409</v>
       </c>
       <c r="D704" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E704">
         <v>1943</v>
@@ -59442,7 +59442,7 @@
         <v>592</v>
       </c>
       <c r="D735" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E735">
         <v>1995</v>
@@ -59474,7 +59474,7 @@
         <v>592</v>
       </c>
       <c r="D736" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E736">
         <v>2002</v>
@@ -59666,7 +59666,7 @@
         <v>636</v>
       </c>
       <c r="D742" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E742">
         <v>1978</v>
@@ -59826,7 +59826,7 @@
         <v>636</v>
       </c>
       <c r="D747" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E747">
         <v>1987</v>
@@ -59858,7 +59858,7 @@
         <v>636</v>
       </c>
       <c r="D748" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E748">
         <v>1987</v>
@@ -60274,7 +60274,7 @@
         <v>636</v>
       </c>
       <c r="D761" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E761">
         <v>1973</v>
@@ -60568,7 +60568,7 @@
         <v>2022</v>
       </c>
       <c r="F770">
-        <v>18.698663529818063</v>
+        <v>17.631312619735244</v>
       </c>
       <c r="G770">
         <v>1</v>
@@ -60603,7 +60603,7 @@
         <v>2022</v>
       </c>
       <c r="F771">
-        <v>17.631312619735244</v>
+        <v>18.698663529818063</v>
       </c>
       <c r="G771">
         <v>1</v>
@@ -67807,7 +67807,7 @@
         <v>662</v>
       </c>
       <c r="D977" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E977">
         <v>2013</v>
@@ -67842,7 +67842,7 @@
         <v>662</v>
       </c>
       <c r="D978" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E978">
         <v>2014</v>
@@ -67877,7 +67877,7 @@
         <v>662</v>
       </c>
       <c r="D979" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E979">
         <v>2015</v>
@@ -67912,7 +67912,7 @@
         <v>662</v>
       </c>
       <c r="D980" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E980">
         <v>2016</v>
@@ -67947,7 +67947,7 @@
         <v>662</v>
       </c>
       <c r="D981" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E981">
         <v>2017</v>
@@ -67982,7 +67982,7 @@
         <v>662</v>
       </c>
       <c r="D982" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E982">
         <v>2018</v>
@@ -68017,7 +68017,7 @@
         <v>662</v>
       </c>
       <c r="D983" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E983">
         <v>2019</v>
@@ -68052,7 +68052,7 @@
         <v>662</v>
       </c>
       <c r="D984" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E984">
         <v>2020</v>
@@ -68087,7 +68087,7 @@
         <v>662</v>
       </c>
       <c r="D985" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E985">
         <v>2021</v>
@@ -68122,7 +68122,7 @@
         <v>662</v>
       </c>
       <c r="D986" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E986">
         <v>2022</v>
@@ -68157,7 +68157,7 @@
         <v>662</v>
       </c>
       <c r="D987" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E987">
         <v>2023</v>
@@ -68192,7 +68192,7 @@
         <v>662</v>
       </c>
       <c r="D988" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E988">
         <v>2024</v>
@@ -68227,7 +68227,7 @@
         <v>662</v>
       </c>
       <c r="D989" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E989">
         <v>2028</v>
@@ -68682,7 +68682,7 @@
         <v>662</v>
       </c>
       <c r="D1002" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1002">
         <v>2013</v>
@@ -68717,7 +68717,7 @@
         <v>662</v>
       </c>
       <c r="D1003" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1003">
         <v>2014</v>
@@ -68752,7 +68752,7 @@
         <v>662</v>
       </c>
       <c r="D1004" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1004">
         <v>2015</v>
@@ -68787,7 +68787,7 @@
         <v>662</v>
       </c>
       <c r="D1005" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1005">
         <v>2016</v>
@@ -68822,7 +68822,7 @@
         <v>662</v>
       </c>
       <c r="D1006" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1006">
         <v>2017</v>
@@ -68857,7 +68857,7 @@
         <v>662</v>
       </c>
       <c r="D1007" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1007">
         <v>2018</v>
@@ -68892,7 +68892,7 @@
         <v>662</v>
       </c>
       <c r="D1008" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1008">
         <v>2019</v>
@@ -68927,7 +68927,7 @@
         <v>662</v>
       </c>
       <c r="D1009" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1009">
         <v>2020</v>
@@ -68962,7 +68962,7 @@
         <v>662</v>
       </c>
       <c r="D1010" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1010">
         <v>2021</v>
@@ -68997,7 +68997,7 @@
         <v>662</v>
       </c>
       <c r="D1011" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1011">
         <v>2022</v>
@@ -69032,7 +69032,7 @@
         <v>662</v>
       </c>
       <c r="D1012" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1012">
         <v>2023</v>
@@ -69067,7 +69067,7 @@
         <v>662</v>
       </c>
       <c r="D1013" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1013">
         <v>2024</v>
@@ -69102,7 +69102,7 @@
         <v>662</v>
       </c>
       <c r="D1014" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1014">
         <v>2028</v>
@@ -71132,13 +71132,13 @@
         <v>662</v>
       </c>
       <c r="D1072" t="s">
-        <v>33</v>
+        <v>605</v>
       </c>
       <c r="E1072">
         <v>2013</v>
       </c>
       <c r="F1072">
-        <v>3.5000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="G1072">
         <v>1</v>
@@ -71147,7 +71147,7 @@
         <v>1458</v>
       </c>
       <c r="I1072">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1072">
         <v>0</v>
@@ -71156,7 +71156,7 @@
         <v>42</v>
       </c>
       <c r="L1072">
-        <v>0.19855392263260624</v>
+        <v>0.1921131304391373</v>
       </c>
     </row>
     <row r="1073" spans="2:12" x14ac:dyDescent="0.45">
@@ -71167,13 +71167,13 @@
         <v>662</v>
       </c>
       <c r="D1073" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="E1073">
         <v>2013</v>
       </c>
       <c r="F1073">
-        <v>1.9E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G1073">
         <v>1</v>
@@ -71191,7 +71191,7 @@
         <v>42</v>
       </c>
       <c r="L1073">
-        <v>0.18013391841854179</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1074" spans="2:12" x14ac:dyDescent="0.45">
@@ -71202,13 +71202,13 @@
         <v>662</v>
       </c>
       <c r="D1074" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="E1074">
         <v>2013</v>
       </c>
       <c r="F1074">
-        <v>1.4E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1074">
         <v>1</v>
@@ -71226,7 +71226,7 @@
         <v>42</v>
       </c>
       <c r="L1074">
-        <v>0.1885335384832984</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1075" spans="2:12" x14ac:dyDescent="0.45">
@@ -71237,13 +71237,13 @@
         <v>662</v>
       </c>
       <c r="D1075" t="s">
-        <v>605</v>
+        <v>33</v>
       </c>
       <c r="E1075">
         <v>2013</v>
       </c>
       <c r="F1075">
-        <v>2E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1075">
         <v>1</v>
@@ -71252,7 +71252,7 @@
         <v>1458</v>
       </c>
       <c r="I1075">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1075">
         <v>0</v>
@@ -71261,7 +71261,7 @@
         <v>42</v>
       </c>
       <c r="L1075">
-        <v>0.1921131304391373</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1076" spans="2:12" x14ac:dyDescent="0.45">
@@ -71272,13 +71272,13 @@
         <v>662</v>
       </c>
       <c r="D1076" t="s">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="E1076">
         <v>2014</v>
       </c>
       <c r="F1076">
-        <v>2.5000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="G1076">
         <v>1</v>
@@ -71342,13 +71342,13 @@
         <v>662</v>
       </c>
       <c r="D1078" t="s">
-        <v>224</v>
+        <v>77</v>
       </c>
       <c r="E1078">
         <v>2014</v>
       </c>
       <c r="F1078">
-        <v>3.8999999999999998E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1078">
         <v>1</v>
@@ -71377,22 +71377,22 @@
         <v>662</v>
       </c>
       <c r="D1079" t="s">
-        <v>33</v>
+        <v>600</v>
       </c>
       <c r="E1079">
         <v>2015</v>
       </c>
       <c r="F1079">
-        <v>9.6999999999999986E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1079">
         <v>1</v>
       </c>
       <c r="H1079">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1079">
-        <v>22.425000000000001</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1079">
         <v>0</v>
@@ -71401,7 +71401,7 @@
         <v>40</v>
       </c>
       <c r="L1079">
-        <v>0.19855392263260621</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1080" spans="2:12" x14ac:dyDescent="0.45">
@@ -71412,13 +71412,13 @@
         <v>662</v>
       </c>
       <c r="D1080" t="s">
-        <v>725</v>
+        <v>33</v>
       </c>
       <c r="E1080">
         <v>2015</v>
       </c>
       <c r="F1080">
-        <v>1E-3</v>
+        <v>9.6999999999999986E-3</v>
       </c>
       <c r="G1080">
         <v>1</v>
@@ -71427,7 +71427,7 @@
         <v>1458</v>
       </c>
       <c r="I1080">
-        <v>22.424999999999997</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J1080">
         <v>0</v>
@@ -71436,7 +71436,7 @@
         <v>40</v>
       </c>
       <c r="L1080">
-        <v>0.17907908788454549</v>
+        <v>0.19855392263260621</v>
       </c>
     </row>
     <row r="1081" spans="2:12" x14ac:dyDescent="0.45">
@@ -71447,13 +71447,13 @@
         <v>662</v>
       </c>
       <c r="D1081" t="s">
-        <v>224</v>
+        <v>725</v>
       </c>
       <c r="E1081">
         <v>2015</v>
       </c>
       <c r="F1081">
-        <v>6.4000000000000003E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1081">
         <v>1</v>
@@ -71471,7 +71471,7 @@
         <v>40</v>
       </c>
       <c r="L1081">
-        <v>0.1885335384832984</v>
+        <v>0.17907908788454549</v>
       </c>
     </row>
     <row r="1082" spans="2:12" x14ac:dyDescent="0.45">
@@ -71482,19 +71482,19 @@
         <v>662</v>
       </c>
       <c r="D1082" t="s">
-        <v>600</v>
+        <v>77</v>
       </c>
       <c r="E1082">
         <v>2015</v>
       </c>
       <c r="F1082">
-        <v>4.9000000000000007E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1082">
         <v>1</v>
       </c>
       <c r="H1082">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1082">
         <v>22.424999999999997</v>
@@ -71506,7 +71506,7 @@
         <v>40</v>
       </c>
       <c r="L1082">
-        <v>0.18956968490584708</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1083" spans="2:12" x14ac:dyDescent="0.45">
@@ -71517,13 +71517,13 @@
         <v>662</v>
       </c>
       <c r="D1083" t="s">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="E1083">
         <v>2015</v>
       </c>
       <c r="F1083">
-        <v>1E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="G1083">
         <v>1</v>
@@ -71622,13 +71622,13 @@
         <v>662</v>
       </c>
       <c r="D1086" t="s">
-        <v>52</v>
+        <v>224</v>
       </c>
       <c r="E1086">
         <v>2017</v>
       </c>
       <c r="F1086">
-        <v>1.5699999999999999E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="G1086">
         <v>1</v>
@@ -71657,13 +71657,13 @@
         <v>662</v>
       </c>
       <c r="D1087" t="s">
-        <v>224</v>
+        <v>52</v>
       </c>
       <c r="E1087">
         <v>2017</v>
       </c>
       <c r="F1087">
-        <v>4.4999999999999997E-3</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="G1087">
         <v>1</v>
@@ -72028,7 +72028,7 @@
         <v>730</v>
       </c>
       <c r="D1100" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1100">
         <v>2025</v>
@@ -72080,7 +72080,7 @@
         <v>2022</v>
       </c>
       <c r="F1102">
-        <v>0.23444585931601827</v>
+        <v>0.2581233858557071</v>
       </c>
       <c r="G1102">
         <v>0.33123000000000002</v>
@@ -72126,7 +72126,7 @@
         <v>2022</v>
       </c>
       <c r="F1104">
-        <v>0.2581233858557071</v>
+        <v>0.23444585931601827</v>
       </c>
       <c r="G1104">
         <v>0.33123000000000002</v>

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35253DEE-FC8A-421D-A6FA-8B231EB76485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D149594F-6B3B-41FE-B8C3-544852A5B898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F6166B1B-3DE9-46BF-87DC-ACE00B969080}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{89C15E15-B730-4B2F-9FBC-1C97EC7DA0E1}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,33 +81,33 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w170247312-500</t>
+  </si>
+  <si>
+    <t>e_w104391636-500</t>
+  </si>
+  <si>
+    <t>e_w150065045-500</t>
+  </si>
+  <si>
+    <t>e_JP7-275</t>
+  </si>
+  <si>
+    <t>e_w151379730-500</t>
+  </si>
+  <si>
+    <t>e_w187988970-500</t>
+  </si>
+  <si>
+    <t>e_w106076988-500</t>
+  </si>
+  <si>
     <t>e_w785319805-500</t>
   </si>
   <si>
     <t>e_w241822631-500</t>
   </si>
   <si>
-    <t>e_w104391636-500</t>
-  </si>
-  <si>
-    <t>e_w187988970-500</t>
-  </si>
-  <si>
-    <t>e_w170247312-500</t>
-  </si>
-  <si>
-    <t>e_JP7-275</t>
-  </si>
-  <si>
-    <t>e_w151379730-500</t>
-  </si>
-  <si>
-    <t>e_w150065045-500</t>
-  </si>
-  <si>
-    <t>e_w106076988-500</t>
-  </si>
-  <si>
     <t>ep_bioenergy_G100000200026</t>
   </si>
   <si>
@@ -1269,81 +1269,81 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w170366035-500</t>
+  </si>
+  <si>
+    <t>e_w216953915-500</t>
+  </si>
+  <si>
+    <t>e_JP95-500</t>
+  </si>
+  <si>
+    <t>e_JP34-500</t>
+  </si>
+  <si>
+    <t>e_w170850727-500</t>
+  </si>
+  <si>
+    <t>e_JP76-500</t>
+  </si>
+  <si>
+    <t>e_w1038584990-500</t>
+  </si>
+  <si>
+    <t>e_w116559939-500</t>
+  </si>
+  <si>
+    <t>e_w832823487-500</t>
+  </si>
+  <si>
+    <t>e_w241828221-500</t>
+  </si>
+  <si>
+    <t>e_JP37-500</t>
+  </si>
+  <si>
+    <t>e_JP1-275</t>
+  </si>
+  <si>
+    <t>e_JP155-500</t>
+  </si>
+  <si>
+    <t>e_w209429410-500</t>
+  </si>
+  <si>
+    <t>e_w459476442-500</t>
+  </si>
+  <si>
+    <t>e_JP74-500</t>
+  </si>
+  <si>
+    <t>e_JP57-500</t>
+  </si>
+  <si>
+    <t>e_r13768299-500</t>
+  </si>
+  <si>
+    <t>e_JP137-500</t>
+  </si>
+  <si>
+    <t>e_w250540807-1000</t>
+  </si>
+  <si>
+    <t>e_JP30-500</t>
+  </si>
+  <si>
     <t>e_JP29-500</t>
   </si>
   <si>
-    <t>e_w832823487-500</t>
-  </si>
-  <si>
-    <t>e_w250540807-1000</t>
+    <t>e_w161870227-500</t>
   </si>
   <si>
     <t>e_w142662111-500</t>
   </si>
   <si>
-    <t>e_w216953915-500</t>
-  </si>
-  <si>
     <t>e_w256682313-500</t>
   </si>
   <si>
-    <t>e_JP30-500</t>
-  </si>
-  <si>
-    <t>e_r13768299-500</t>
-  </si>
-  <si>
-    <t>e_w459476442-500</t>
-  </si>
-  <si>
-    <t>e_JP74-500</t>
-  </si>
-  <si>
-    <t>e_JP76-500</t>
-  </si>
-  <si>
-    <t>e_w170366035-500</t>
-  </si>
-  <si>
-    <t>e_JP95-500</t>
-  </si>
-  <si>
-    <t>e_JP34-500</t>
-  </si>
-  <si>
-    <t>e_w241828221-500</t>
-  </si>
-  <si>
-    <t>e_JP57-500</t>
-  </si>
-  <si>
-    <t>e_JP37-500</t>
-  </si>
-  <si>
-    <t>e_w161870227-500</t>
-  </si>
-  <si>
-    <t>e_w116559939-500</t>
-  </si>
-  <si>
-    <t>e_JP1-275</t>
-  </si>
-  <si>
-    <t>e_w170850727-500</t>
-  </si>
-  <si>
-    <t>e_JP155-500</t>
-  </si>
-  <si>
-    <t>e_w1038584990-500</t>
-  </si>
-  <si>
-    <t>e_JP137-500</t>
-  </si>
-  <si>
-    <t>e_w209429410-500</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_G100000602267</t>
   </si>
   <si>
@@ -2028,12 +2028,12 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv_026</t>
+  </si>
+  <si>
     <t>elc_spv_024</t>
   </si>
   <si>
-    <t>elc_spv_026</t>
-  </si>
-  <si>
     <t>elc_spv_013</t>
   </si>
   <si>
@@ -2250,12 +2250,12 @@
     <t>windon</t>
   </si>
   <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
     <t>elc_won_026</t>
   </si>
   <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
     <t>ep_windon_wind_001</t>
   </si>
   <si>
@@ -2406,45 +2406,45 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/150065045-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/187988970-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - JP7-275_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/241822631-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/785319805-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/104391636-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/187988970-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/150065045-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/106076988-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/151379730-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/170247312-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/241822631-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - JP7-275_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/151379730-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Sendai-ko power station_1</t>
   </si>
   <si>
@@ -2988,46 +2988,94 @@
     <t>Yanatsu Nishiyama geothermal power plant_--</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/209429410-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/250540807-1000_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP37-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/161870227-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/315662839-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP95-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP1-275_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/170366035-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP137-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/116559939-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP34-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/216502300-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP74-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/170850727-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/170974371-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP296-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/241828221-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - JP30-500_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - JP21-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - JP7-275_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - JP21-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/241828221-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/170974371-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/170850727-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/216502300-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP74-500_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - relation/17013811-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/832823487-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP76-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1030329139-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/459476442-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP155-500_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/185029969-500_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - relation/17013811-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/832823487-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP95-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP1-275_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/161870227-500_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - way/142662111-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/216953915-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JP29-500_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/1038584990-500_Missing Hydro Capacity</t>
@@ -3036,63 +3084,15 @@
     <t>Aggregated Plant - IRENA Gap - way/171066843-500_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - JP29-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP137-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP34-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/1030329139-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/116559939-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP76-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/459476442-500_Missing Hydro Capacity</t>
+    <t>Aggregated Plant - IRENA Gap - JP57-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - relation/13768299-500_Missing Hydro Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - way/256682313-500_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - JP155-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/142662111-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/216953915-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/170366035-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP296-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/315662839-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP57-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - relation/13768299-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/209429410-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JP37-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/250540807-1000_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Akimoto hydroelectric plant_</t>
   </si>
   <si>
@@ -3549,16 +3549,16 @@
     <t>Gobo power station_1</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - JPN_216_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - JPN_217_Missing Solar Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - JPN_156_Missing Solar Capacity</t>
-  </si>
-  <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JPN_216_Missing Solar Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - JPN_217_Missing Solar Capacity</t>
   </si>
   <si>
     <t>Pacifico Energy Sakuto Mega-Solar Project_--</t>
@@ -5051,7 +5051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88002BBA-011E-44A7-822C-696A6E076A2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BF3F5FF-96CC-4667-9127-084CFB5AEA2D}">
   <dimension ref="B9:T380"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5351,7 +5351,7 @@
         <v>163</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15">
         <v>0.29791792799999994</v>
@@ -6583,7 +6583,7 @@
         <v>163</v>
       </c>
       <c r="D37" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E37">
         <v>9.2775936000000031E-2</v>
@@ -6639,7 +6639,7 @@
         <v>163</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E38">
         <v>9.2775936000000031E-2</v>
@@ -6975,7 +6975,7 @@
         <v>163</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E44">
         <v>9.0047232000000033E-2</v>
@@ -7031,7 +7031,7 @@
         <v>163</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E45">
         <v>9.0047232000000033E-2</v>
@@ -7087,7 +7087,7 @@
         <v>163</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E46">
         <v>9.0047232000000033E-2</v>
@@ -7255,7 +7255,7 @@
         <v>163</v>
       </c>
       <c r="D49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E49">
         <v>9.2775936000000031E-2</v>
@@ -7311,7 +7311,7 @@
         <v>163</v>
       </c>
       <c r="D50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E50">
         <v>9.2775936000000031E-2</v>
@@ -7367,7 +7367,7 @@
         <v>163</v>
       </c>
       <c r="D51" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E51">
         <v>9.2775936000000031E-2</v>
@@ -9439,7 +9439,7 @@
         <v>163</v>
       </c>
       <c r="D88" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E88">
         <v>9.2775936000000031E-2</v>
@@ -9495,7 +9495,7 @@
         <v>163</v>
       </c>
       <c r="D89" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E89">
         <v>9.2775936000000031E-2</v>
@@ -9551,7 +9551,7 @@
         <v>163</v>
       </c>
       <c r="D90" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E90">
         <v>9.2775936000000031E-2</v>
@@ -9607,7 +9607,7 @@
         <v>163</v>
       </c>
       <c r="D91" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E91">
         <v>9.2775936000000031E-2</v>
@@ -9663,7 +9663,7 @@
         <v>163</v>
       </c>
       <c r="D92" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E92">
         <v>9.2775936000000031E-2</v>
@@ -9719,7 +9719,7 @@
         <v>163</v>
       </c>
       <c r="D93" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E93">
         <v>9.2775936000000031E-2</v>
@@ -9775,7 +9775,7 @@
         <v>163</v>
       </c>
       <c r="D94" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E94">
         <v>9.2775936000000031E-2</v>
@@ -9831,7 +9831,7 @@
         <v>163</v>
       </c>
       <c r="D95" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E95">
         <v>9.2775936000000031E-2</v>
@@ -10279,7 +10279,7 @@
         <v>163</v>
       </c>
       <c r="D103" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E103">
         <v>9.2775936000000031E-2</v>
@@ -10335,7 +10335,7 @@
         <v>163</v>
       </c>
       <c r="D104" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E104">
         <v>9.2775936000000031E-2</v>
@@ -10391,7 +10391,7 @@
         <v>163</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E105">
         <v>9.2775936000000031E-2</v>
@@ -11455,7 +11455,7 @@
         <v>163</v>
       </c>
       <c r="D124" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E124">
         <v>9.2775936000000031E-2</v>
@@ -11959,7 +11959,7 @@
         <v>163</v>
       </c>
       <c r="D133" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E133">
         <v>0.24244176000000003</v>
@@ -12015,7 +12015,7 @@
         <v>163</v>
       </c>
       <c r="D134" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E134">
         <v>0.24244176000000003</v>
@@ -12631,7 +12631,7 @@
         <v>163</v>
       </c>
       <c r="D145" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E145">
         <v>0.24244176000000003</v>
@@ -12743,7 +12743,7 @@
         <v>163</v>
       </c>
       <c r="D147" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E147">
         <v>0.10778380800000002</v>
@@ -14591,7 +14591,7 @@
         <v>163</v>
       </c>
       <c r="D180" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E180">
         <v>0.31855824000000005</v>
@@ -15039,7 +15039,7 @@
         <v>288</v>
       </c>
       <c r="D188" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E188">
         <v>0.45553200000000005</v>
@@ -15095,7 +15095,7 @@
         <v>288</v>
       </c>
       <c r="D189" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E189">
         <v>0.45553200000000005</v>
@@ -15151,7 +15151,7 @@
         <v>288</v>
       </c>
       <c r="D190" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E190">
         <v>0.45553200000000005</v>
@@ -15711,7 +15711,7 @@
         <v>288</v>
       </c>
       <c r="D200" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E200">
         <v>0.47124000000000005</v>
@@ -15767,7 +15767,7 @@
         <v>288</v>
       </c>
       <c r="D201" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E201">
         <v>0.47124000000000005</v>
@@ -15823,7 +15823,7 @@
         <v>288</v>
       </c>
       <c r="D202" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E202">
         <v>0.47124000000000005</v>
@@ -17279,7 +17279,7 @@
         <v>288</v>
       </c>
       <c r="D228" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E228">
         <v>0.45553200000000005</v>
@@ -17335,7 +17335,7 @@
         <v>288</v>
       </c>
       <c r="D229" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E229">
         <v>0.45553200000000005</v>
@@ -18518,7 +18518,7 @@
         <v>288</v>
       </c>
       <c r="D255" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E255">
         <v>0.43982399999999999</v>
@@ -18553,7 +18553,7 @@
         <v>288</v>
       </c>
       <c r="D256" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E256">
         <v>0.43982399999999999</v>
@@ -18588,7 +18588,7 @@
         <v>288</v>
       </c>
       <c r="D257" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E257">
         <v>0.43982399999999999</v>
@@ -18623,7 +18623,7 @@
         <v>288</v>
       </c>
       <c r="D258" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E258">
         <v>0.43982399999999999</v>
@@ -18658,7 +18658,7 @@
         <v>288</v>
       </c>
       <c r="D259" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E259">
         <v>0.43982399999999999</v>
@@ -18693,7 +18693,7 @@
         <v>288</v>
       </c>
       <c r="D260" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E260">
         <v>0.43982399999999999</v>
@@ -18728,7 +18728,7 @@
         <v>288</v>
       </c>
       <c r="D261" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E261">
         <v>0.43982399999999999</v>
@@ -20408,7 +20408,7 @@
         <v>288</v>
       </c>
       <c r="D309" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E309">
         <v>0.42804300000000006</v>
@@ -20898,7 +20898,7 @@
         <v>288</v>
       </c>
       <c r="D323" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E323">
         <v>0.25918200000000002</v>
@@ -20933,7 +20933,7 @@
         <v>288</v>
       </c>
       <c r="D324" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E324">
         <v>0.26703600000000005</v>
@@ -21318,7 +21318,7 @@
         <v>288</v>
       </c>
       <c r="D335" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E335">
         <v>0.25132800000000005</v>
@@ -21353,7 +21353,7 @@
         <v>288</v>
       </c>
       <c r="D336" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E336">
         <v>0.26703600000000005</v>
@@ -21388,7 +21388,7 @@
         <v>288</v>
       </c>
       <c r="D337" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E337">
         <v>0.26703600000000005</v>
@@ -21423,7 +21423,7 @@
         <v>288</v>
       </c>
       <c r="D338" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E338">
         <v>0.26703600000000005</v>
@@ -21458,7 +21458,7 @@
         <v>288</v>
       </c>
       <c r="D339" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E339">
         <v>0.26703600000000005</v>
@@ -21493,7 +21493,7 @@
         <v>288</v>
       </c>
       <c r="D340" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E340">
         <v>0.26703600000000005</v>
@@ -21948,7 +21948,7 @@
         <v>636</v>
       </c>
       <c r="D353" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E353">
         <v>0.172788</v>
@@ -22053,7 +22053,7 @@
         <v>636</v>
       </c>
       <c r="D356" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E356">
         <v>0.25918200000000002</v>
@@ -22088,7 +22088,7 @@
         <v>636</v>
       </c>
       <c r="D357" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E357">
         <v>0.25918200000000002</v>
@@ -22123,7 +22123,7 @@
         <v>636</v>
       </c>
       <c r="D358" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E358">
         <v>0.25918200000000002</v>
@@ -22158,7 +22158,7 @@
         <v>636</v>
       </c>
       <c r="D359" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E359">
         <v>0.25918200000000002</v>
@@ -22613,7 +22613,7 @@
         <v>636</v>
       </c>
       <c r="D372" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E372">
         <v>0.23562000000000002</v>
@@ -22926,7 +22926,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE8D958-774D-408B-AD63-08A5B6DEF519}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40BA4C2-C7CB-487B-A45F-13387F69FED7}">
   <dimension ref="B9:T1231"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23008,7 +23008,7 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>5.9113253159199221E-2</v>
+        <v>0.10653030114786169</v>
       </c>
       <c r="G11">
         <v>0.29620800000000003</v>
@@ -23061,7 +23061,7 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>9.6414664243613696E-2</v>
+        <v>5.9113253159199221E-2</v>
       </c>
       <c r="G12">
         <v>0.29620800000000003</v>
@@ -23114,7 +23114,7 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>5.9113253159199221E-2</v>
+        <v>6.7648321797158462E-2</v>
       </c>
       <c r="G13">
         <v>0.29620800000000003</v>
@@ -23167,7 +23167,7 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.12233598381074919</v>
+        <v>6.1768607846564322E-2</v>
       </c>
       <c r="G14">
         <v>0.29620800000000003</v>
@@ -23220,13 +23220,13 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.10653030114786169</v>
+        <v>5.5288277954780453E-2</v>
       </c>
       <c r="G15">
         <v>0.29620800000000003</v>
       </c>
       <c r="H15">
-        <v>4829.9999999999991</v>
+        <v>4829.9999999999982</v>
       </c>
       <c r="I15">
         <v>164.45</v>
@@ -23273,7 +23273,7 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>6.1768607846564322E-2</v>
+        <v>0.12233598381074919</v>
       </c>
       <c r="G16">
         <v>0.29620800000000003</v>
@@ -23326,13 +23326,13 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>5.5288277954780453E-2</v>
+        <v>9.2621300404520698E-2</v>
       </c>
       <c r="G17">
         <v>0.29620800000000003</v>
       </c>
       <c r="H17">
-        <v>4829.9999999999982</v>
+        <v>4829.9999999999991</v>
       </c>
       <c r="I17">
         <v>164.45</v>
@@ -23379,7 +23379,7 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>6.7648321797158462E-2</v>
+        <v>5.9113253159199221E-2</v>
       </c>
       <c r="G18">
         <v>0.29620800000000003</v>
@@ -23432,7 +23432,7 @@
         <v>2022</v>
       </c>
       <c r="F19">
-        <v>9.2621300404520698E-2</v>
+        <v>9.6414664243613696E-2</v>
       </c>
       <c r="G19">
         <v>0.29620800000000003</v>
@@ -23479,7 +23479,7 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E20">
         <v>2025</v>
@@ -23956,7 +23956,7 @@
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E29">
         <v>2021</v>
@@ -24062,7 +24062,7 @@
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E31">
         <v>2020</v>
@@ -24115,7 +24115,7 @@
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E32">
         <v>2023</v>
@@ -24221,7 +24221,7 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E34">
         <v>2025</v>
@@ -24274,7 +24274,7 @@
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E35">
         <v>2023</v>
@@ -24433,7 +24433,7 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E38">
         <v>2025</v>
@@ -24486,7 +24486,7 @@
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E39">
         <v>2021</v>
@@ -24592,7 +24592,7 @@
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E41">
         <v>2023</v>
@@ -24804,7 +24804,7 @@
         <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E45">
         <v>2024</v>
@@ -24910,7 +24910,7 @@
         <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E47">
         <v>2024</v>
@@ -24963,7 +24963,7 @@
         <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E48">
         <v>1982</v>
@@ -25016,7 +25016,7 @@
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E49">
         <v>2024</v>
@@ -25069,7 +25069,7 @@
         <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E50">
         <v>2022</v>
@@ -25387,7 +25387,7 @@
         <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E56">
         <v>2023</v>
@@ -25546,7 +25546,7 @@
         <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E59">
         <v>2022</v>
@@ -25705,7 +25705,7 @@
         <v>13</v>
       </c>
       <c r="D62" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E62">
         <v>2023</v>
@@ -25758,7 +25758,7 @@
         <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E63">
         <v>2015</v>
@@ -25917,7 +25917,7 @@
         <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E66">
         <v>2018</v>
@@ -25970,7 +25970,7 @@
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E67">
         <v>2015</v>
@@ -26023,7 +26023,7 @@
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E68">
         <v>2022</v>
@@ -26129,7 +26129,7 @@
         <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E70">
         <v>2013</v>
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E71">
         <v>2025</v>
@@ -26235,7 +26235,7 @@
         <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E72">
         <v>2023</v>
@@ -26288,7 +26288,7 @@
         <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E73">
         <v>2026</v>
@@ -26341,7 +26341,7 @@
         <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E74">
         <v>2020</v>
@@ -26447,7 +26447,7 @@
         <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E76">
         <v>2016</v>
@@ -27348,7 +27348,7 @@
         <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E93">
         <v>2013</v>
@@ -27878,7 +27878,7 @@
         <v>13</v>
       </c>
       <c r="D103" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E103">
         <v>2018</v>
@@ -27931,7 +27931,7 @@
         <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E104">
         <v>2013</v>
@@ -28991,7 +28991,7 @@
         <v>13</v>
       </c>
       <c r="D124" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E124">
         <v>2021</v>
@@ -29839,7 +29839,7 @@
         <v>163</v>
       </c>
       <c r="D140" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E140">
         <v>2021</v>
@@ -31005,7 +31005,7 @@
         <v>163</v>
       </c>
       <c r="D162" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E162">
         <v>1980</v>
@@ -31058,7 +31058,7 @@
         <v>163</v>
       </c>
       <c r="D163" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E163">
         <v>2022</v>
@@ -31376,7 +31376,7 @@
         <v>163</v>
       </c>
       <c r="D169" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E169">
         <v>1970</v>
@@ -31429,7 +31429,7 @@
         <v>163</v>
       </c>
       <c r="D170" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E170">
         <v>2006</v>
@@ -31482,7 +31482,7 @@
         <v>163</v>
       </c>
       <c r="D171" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E171">
         <v>2022</v>
@@ -31641,7 +31641,7 @@
         <v>163</v>
       </c>
       <c r="D174" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E174">
         <v>1977</v>
@@ -31694,7 +31694,7 @@
         <v>163</v>
       </c>
       <c r="D175" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E175">
         <v>1978</v>
@@ -31747,7 +31747,7 @@
         <v>163</v>
       </c>
       <c r="D176" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E176">
         <v>1987</v>
@@ -33708,7 +33708,7 @@
         <v>163</v>
       </c>
       <c r="D213" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E213">
         <v>1991</v>
@@ -33761,7 +33761,7 @@
         <v>163</v>
       </c>
       <c r="D214" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E214">
         <v>1999</v>
@@ -33814,7 +33814,7 @@
         <v>163</v>
       </c>
       <c r="D215" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E215">
         <v>2004</v>
@@ -33867,7 +33867,7 @@
         <v>163</v>
       </c>
       <c r="D216" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E216">
         <v>2007</v>
@@ -33920,7 +33920,7 @@
         <v>163</v>
       </c>
       <c r="D217" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E217">
         <v>2010</v>
@@ -33973,7 +33973,7 @@
         <v>163</v>
       </c>
       <c r="D218" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E218">
         <v>2018</v>
@@ -34026,7 +34026,7 @@
         <v>163</v>
       </c>
       <c r="D219" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E219">
         <v>2022</v>
@@ -34079,7 +34079,7 @@
         <v>163</v>
       </c>
       <c r="D220" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E220">
         <v>2019</v>
@@ -34503,7 +34503,7 @@
         <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E228">
         <v>1996</v>
@@ -34556,7 +34556,7 @@
         <v>163</v>
       </c>
       <c r="D229" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E229">
         <v>1997</v>
@@ -34609,7 +34609,7 @@
         <v>163</v>
       </c>
       <c r="D230" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E230">
         <v>1999</v>
@@ -35616,7 +35616,7 @@
         <v>163</v>
       </c>
       <c r="D249" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E249">
         <v>2017</v>
@@ -36093,7 +36093,7 @@
         <v>163</v>
       </c>
       <c r="D258" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E258">
         <v>1983</v>
@@ -36146,7 +36146,7 @@
         <v>163</v>
       </c>
       <c r="D259" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E259">
         <v>1983</v>
@@ -36729,7 +36729,7 @@
         <v>163</v>
       </c>
       <c r="D270" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E270">
         <v>1985</v>
@@ -36835,7 +36835,7 @@
         <v>163</v>
       </c>
       <c r="D272" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E272">
         <v>2001</v>
@@ -38584,7 +38584,7 @@
         <v>163</v>
       </c>
       <c r="D305" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E305">
         <v>2002</v>
@@ -39008,7 +39008,7 @@
         <v>288</v>
       </c>
       <c r="D313" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E313">
         <v>2014</v>
@@ -39061,7 +39061,7 @@
         <v>288</v>
       </c>
       <c r="D314" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E314">
         <v>2014</v>
@@ -39114,7 +39114,7 @@
         <v>288</v>
       </c>
       <c r="D315" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E315">
         <v>2014</v>
@@ -39644,7 +39644,7 @@
         <v>288</v>
       </c>
       <c r="D325" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E325">
         <v>2024</v>
@@ -39697,7 +39697,7 @@
         <v>288</v>
       </c>
       <c r="D326" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E326">
         <v>2025</v>
@@ -39750,7 +39750,7 @@
         <v>288</v>
       </c>
       <c r="D327" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E327">
         <v>2025</v>
@@ -41128,7 +41128,7 @@
         <v>288</v>
       </c>
       <c r="D353" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E353">
         <v>2015</v>
@@ -41181,7 +41181,7 @@
         <v>288</v>
       </c>
       <c r="D354" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E354">
         <v>2016</v>
@@ -42559,7 +42559,7 @@
         <v>288</v>
       </c>
       <c r="D380" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E380">
         <v>1998</v>
@@ -42612,7 +42612,7 @@
         <v>288</v>
       </c>
       <c r="D381" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E381">
         <v>1999</v>
@@ -42665,7 +42665,7 @@
         <v>288</v>
       </c>
       <c r="D382" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E382">
         <v>2000</v>
@@ -42718,7 +42718,7 @@
         <v>288</v>
       </c>
       <c r="D383" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E383">
         <v>2002</v>
@@ -42771,7 +42771,7 @@
         <v>288</v>
       </c>
       <c r="D384" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E384">
         <v>2004</v>
@@ -42824,7 +42824,7 @@
         <v>288</v>
       </c>
       <c r="D385" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E385">
         <v>2015</v>
@@ -42877,7 +42877,7 @@
         <v>288</v>
       </c>
       <c r="D386" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E386">
         <v>2022</v>
@@ -45421,7 +45421,7 @@
         <v>288</v>
       </c>
       <c r="D434" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E434">
         <v>2010</v>
@@ -46163,7 +46163,7 @@
         <v>288</v>
       </c>
       <c r="D448" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E448">
         <v>1978</v>
@@ -46216,7 +46216,7 @@
         <v>288</v>
       </c>
       <c r="D449" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E449">
         <v>1983</v>
@@ -46799,7 +46799,7 @@
         <v>288</v>
       </c>
       <c r="D460" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E460">
         <v>1984</v>
@@ -46852,7 +46852,7 @@
         <v>288</v>
       </c>
       <c r="D461" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E461">
         <v>1971</v>
@@ -46905,7 +46905,7 @@
         <v>288</v>
       </c>
       <c r="D462" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E462">
         <v>1972</v>
@@ -46958,7 +46958,7 @@
         <v>288</v>
       </c>
       <c r="D463" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E463">
         <v>1978</v>
@@ -47011,7 +47011,7 @@
         <v>288</v>
       </c>
       <c r="D464" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E464">
         <v>1999</v>
@@ -47064,7 +47064,7 @@
         <v>288</v>
       </c>
       <c r="D465" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E465">
         <v>2010</v>
@@ -47965,7 +47965,7 @@
         <v>393</v>
       </c>
       <c r="D482" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E482">
         <v>1975</v>
@@ -48018,7 +48018,7 @@
         <v>393</v>
       </c>
       <c r="D483" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E483">
         <v>1994</v>
@@ -48071,7 +48071,7 @@
         <v>393</v>
       </c>
       <c r="D484" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E484">
         <v>2019</v>
@@ -48124,7 +48124,7 @@
         <v>393</v>
       </c>
       <c r="D485" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E485">
         <v>2027</v>
@@ -49290,13 +49290,13 @@
         <v>409</v>
       </c>
       <c r="D507" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E507">
         <v>2022</v>
       </c>
       <c r="F507">
-        <v>0.13713305223705793</v>
+        <v>0.12915663309127828</v>
       </c>
       <c r="G507">
         <v>1</v>
@@ -49349,19 +49349,19 @@
         <v>2022</v>
       </c>
       <c r="F508">
-        <v>0.37028991957523255</v>
+        <v>0.10860201452330762</v>
       </c>
       <c r="G508">
         <v>1</v>
       </c>
       <c r="H508">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I508">
-        <v>57.499999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J508">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K508">
         <v>100</v>
@@ -49402,7 +49402,7 @@
         <v>2022</v>
       </c>
       <c r="F509">
-        <v>0.52767080502850028</v>
+        <v>0.42336378542984326</v>
       </c>
       <c r="G509">
         <v>1</v>
@@ -49455,7 +49455,7 @@
         <v>2022</v>
       </c>
       <c r="F510">
-        <v>0.40495666432419791</v>
+        <v>0.36814242211290721</v>
       </c>
       <c r="G510">
         <v>1</v>
@@ -49508,13 +49508,13 @@
         <v>2022</v>
       </c>
       <c r="F511">
-        <v>0.46079159834465555</v>
+        <v>0.94673959553369302</v>
       </c>
       <c r="G511">
         <v>1</v>
       </c>
       <c r="H511">
-        <v>3000</v>
+        <v>3000.0000000000005</v>
       </c>
       <c r="I511">
         <v>57.499999999999993</v>
@@ -49555,25 +49555,25 @@
         <v>409</v>
       </c>
       <c r="D512" t="s">
-        <v>86</v>
+        <v>414</v>
       </c>
       <c r="E512">
         <v>2022</v>
       </c>
       <c r="F512">
-        <v>0.18867299133286491</v>
+        <v>0.37305098774107925</v>
       </c>
       <c r="G512">
         <v>1</v>
       </c>
       <c r="H512">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I512">
-        <v>63.25</v>
+        <v>57.499999999999986</v>
       </c>
       <c r="J512">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K512">
         <v>100</v>
@@ -49608,25 +49608,25 @@
         <v>409</v>
       </c>
       <c r="D513" t="s">
-        <v>414</v>
+        <v>66</v>
       </c>
       <c r="E513">
         <v>2022</v>
       </c>
       <c r="F513">
-        <v>0.42336378542984326</v>
+        <v>0.153392675880378</v>
       </c>
       <c r="G513">
         <v>1</v>
       </c>
       <c r="H513">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I513">
-        <v>57.499999999999993</v>
+        <v>63.249999999999993</v>
       </c>
       <c r="J513">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K513">
         <v>100</v>
@@ -49667,7 +49667,7 @@
         <v>2022</v>
       </c>
       <c r="F514">
-        <v>0.10338666354337477</v>
+        <v>0.28837823065511065</v>
       </c>
       <c r="G514">
         <v>1</v>
@@ -49720,7 +49720,7 @@
         <v>2022</v>
       </c>
       <c r="F515">
-        <v>0.48318692902319071</v>
+        <v>0.54331685796829887</v>
       </c>
       <c r="G515">
         <v>1</v>
@@ -49773,7 +49773,7 @@
         <v>2022</v>
       </c>
       <c r="F516">
-        <v>7.6696337940188999E-2</v>
+        <v>0.14664339814164137</v>
       </c>
       <c r="G516">
         <v>1</v>
@@ -49782,7 +49782,7 @@
         <v>3450</v>
       </c>
       <c r="I516">
-        <v>63.249999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J516">
         <v>2.3100000000000005</v>
@@ -49820,25 +49820,25 @@
         <v>409</v>
       </c>
       <c r="D517" t="s">
-        <v>404</v>
+        <v>86</v>
       </c>
       <c r="E517">
         <v>2022</v>
       </c>
       <c r="F517">
-        <v>1.0955304911376598</v>
+        <v>0.18867299133286491</v>
       </c>
       <c r="G517">
         <v>1</v>
       </c>
       <c r="H517">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I517">
-        <v>57.499999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J517">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K517">
         <v>100</v>
@@ -49873,25 +49873,25 @@
         <v>409</v>
       </c>
       <c r="D518" t="s">
-        <v>142</v>
+        <v>418</v>
       </c>
       <c r="E518">
         <v>2022</v>
       </c>
       <c r="F518">
-        <v>0.1840712110564536</v>
+        <v>0.52767080502850028</v>
       </c>
       <c r="G518">
         <v>1</v>
       </c>
       <c r="H518">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I518">
-        <v>63.25</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J518">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K518">
         <v>100</v>
@@ -49926,22 +49926,22 @@
         <v>409</v>
       </c>
       <c r="D519" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E519">
         <v>2022</v>
       </c>
       <c r="F519">
-        <v>8.6513469196533188E-2</v>
+        <v>9.2955961583509064E-2</v>
       </c>
       <c r="G519">
         <v>1</v>
       </c>
       <c r="H519">
-        <v>3450</v>
+        <v>3450.0000000000005</v>
       </c>
       <c r="I519">
-        <v>63.25</v>
+        <v>63.249999999999993</v>
       </c>
       <c r="J519">
         <v>2.3100000000000005</v>
@@ -49979,13 +49979,13 @@
         <v>409</v>
       </c>
       <c r="D520" t="s">
-        <v>419</v>
+        <v>31</v>
       </c>
       <c r="E520">
         <v>2022</v>
       </c>
       <c r="F520">
-        <v>0.12762270633247449</v>
+        <v>7.9150620754275036E-2</v>
       </c>
       <c r="G520">
         <v>1</v>
@@ -49994,7 +49994,7 @@
         <v>3450</v>
       </c>
       <c r="I520">
-        <v>63.25</v>
+        <v>63.250000000000007</v>
       </c>
       <c r="J520">
         <v>2.3100000000000005</v>
@@ -50038,19 +50038,19 @@
         <v>2022</v>
       </c>
       <c r="F521">
-        <v>0.28837823065511065</v>
+        <v>0.36108635902240982</v>
       </c>
       <c r="G521">
         <v>1</v>
       </c>
       <c r="H521">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I521">
-        <v>63.25</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J521">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K521">
         <v>100</v>
@@ -50085,13 +50085,13 @@
         <v>409</v>
       </c>
       <c r="D522" t="s">
-        <v>35</v>
+        <v>421</v>
       </c>
       <c r="E522">
         <v>2022</v>
       </c>
       <c r="F522">
-        <v>0.12915663309127828</v>
+        <v>0.1840712110564536</v>
       </c>
       <c r="G522">
         <v>1</v>
@@ -50138,25 +50138,25 @@
         <v>409</v>
       </c>
       <c r="D523" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E523">
         <v>2022</v>
       </c>
       <c r="F523">
-        <v>0.10860201452330762</v>
+        <v>0.39268525025376771</v>
       </c>
       <c r="G523">
         <v>1</v>
       </c>
       <c r="H523">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I523">
-        <v>63.25</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J523">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K523">
         <v>100</v>
@@ -50191,25 +50191,25 @@
         <v>409</v>
       </c>
       <c r="D524" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E524">
         <v>2022</v>
       </c>
       <c r="F524">
-        <v>0.36814242211290721</v>
+        <v>7.1480986960256149E-2</v>
       </c>
       <c r="G524">
         <v>1</v>
       </c>
       <c r="H524">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I524">
-        <v>57.499999999999993</v>
+        <v>63.249999999999993</v>
       </c>
       <c r="J524">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K524">
         <v>100</v>
@@ -50244,25 +50244,25 @@
         <v>409</v>
       </c>
       <c r="D525" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E525">
         <v>2022</v>
       </c>
       <c r="F525">
-        <v>0.94673959553369302</v>
+        <v>8.6513469196533188E-2</v>
       </c>
       <c r="G525">
         <v>1</v>
       </c>
       <c r="H525">
-        <v>3000.0000000000005</v>
+        <v>3450</v>
       </c>
       <c r="I525">
-        <v>57.499999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J525">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K525">
         <v>100</v>
@@ -50297,22 +50297,22 @@
         <v>409</v>
       </c>
       <c r="D526" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E526">
         <v>2022</v>
       </c>
       <c r="F526">
-        <v>9.2955961583509064E-2</v>
+        <v>0.12762270633247449</v>
       </c>
       <c r="G526">
         <v>1</v>
       </c>
       <c r="H526">
-        <v>3450.0000000000005</v>
+        <v>3450</v>
       </c>
       <c r="I526">
-        <v>63.249999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J526">
         <v>2.3100000000000005</v>
@@ -50350,25 +50350,25 @@
         <v>409</v>
       </c>
       <c r="D527" t="s">
-        <v>394</v>
+        <v>142</v>
       </c>
       <c r="E527">
         <v>2022</v>
       </c>
       <c r="F527">
-        <v>0.92955961583509072</v>
+        <v>0.1840712110564536</v>
       </c>
       <c r="G527">
         <v>1</v>
       </c>
       <c r="H527">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I527">
-        <v>57.499999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J527">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K527">
         <v>100</v>
@@ -50403,25 +50403,25 @@
         <v>409</v>
       </c>
       <c r="D528" t="s">
-        <v>425</v>
+        <v>394</v>
       </c>
       <c r="E528">
         <v>2022</v>
       </c>
       <c r="F528">
-        <v>0.28500359178574231</v>
+        <v>0.92955961583509072</v>
       </c>
       <c r="G528">
         <v>1</v>
       </c>
       <c r="H528">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I528">
-        <v>63.25</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J528">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K528">
         <v>100</v>
@@ -50456,13 +50456,13 @@
         <v>409</v>
       </c>
       <c r="D529" t="s">
-        <v>25</v>
+        <v>426</v>
       </c>
       <c r="E529">
         <v>2022</v>
       </c>
       <c r="F529">
-        <v>0.11995307253845558</v>
+        <v>0.28500359178574231</v>
       </c>
       <c r="G529">
         <v>1</v>
@@ -50509,25 +50509,25 @@
         <v>409</v>
       </c>
       <c r="D530" t="s">
-        <v>426</v>
+        <v>25</v>
       </c>
       <c r="E530">
         <v>2022</v>
       </c>
       <c r="F530">
-        <v>0.36108635902240982</v>
+        <v>0.11995307253845558</v>
       </c>
       <c r="G530">
         <v>1</v>
       </c>
       <c r="H530">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I530">
-        <v>57.499999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J530">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K530">
         <v>100</v>
@@ -50562,13 +50562,13 @@
         <v>409</v>
       </c>
       <c r="D531" t="s">
-        <v>66</v>
+        <v>427</v>
       </c>
       <c r="E531">
         <v>2022</v>
       </c>
       <c r="F531">
-        <v>0.153392675880378</v>
+        <v>7.6696337940188999E-2</v>
       </c>
       <c r="G531">
         <v>1</v>
@@ -50615,25 +50615,25 @@
         <v>409</v>
       </c>
       <c r="D532" t="s">
-        <v>169</v>
+        <v>428</v>
       </c>
       <c r="E532">
         <v>2022</v>
       </c>
       <c r="F532">
-        <v>0.1902069180916687</v>
+        <v>0.59270929960178054</v>
       </c>
       <c r="G532">
         <v>1</v>
       </c>
       <c r="H532">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I532">
-        <v>63.25</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J532">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K532">
         <v>100</v>
@@ -50668,25 +50668,25 @@
         <v>409</v>
       </c>
       <c r="D533" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E533">
         <v>2022</v>
       </c>
       <c r="F533">
-        <v>0.17118622628250185</v>
+        <v>0.40495666432419791</v>
       </c>
       <c r="G533">
         <v>1</v>
       </c>
       <c r="H533">
-        <v>3450.0000000000005</v>
+        <v>3000</v>
       </c>
       <c r="I533">
-        <v>63.25</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J533">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K533">
         <v>100</v>
@@ -50721,25 +50721,25 @@
         <v>409</v>
       </c>
       <c r="D534" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E534">
         <v>2022</v>
       </c>
       <c r="F534">
-        <v>0.14664339814164137</v>
+        <v>0.48318692902319071</v>
       </c>
       <c r="G534">
         <v>1</v>
       </c>
       <c r="H534">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I534">
-        <v>63.25</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J534">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K534">
         <v>100</v>
@@ -50774,25 +50774,25 @@
         <v>409</v>
       </c>
       <c r="D535" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E535">
         <v>2022</v>
       </c>
       <c r="F535">
-        <v>0.1840712110564536</v>
+        <v>0.37028991957523255</v>
       </c>
       <c r="G535">
         <v>1</v>
       </c>
       <c r="H535">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I535">
-        <v>63.25</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J535">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K535">
         <v>100</v>
@@ -50827,25 +50827,25 @@
         <v>409</v>
       </c>
       <c r="D536" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E536">
         <v>2022</v>
       </c>
       <c r="F536">
-        <v>0.37305098774107925</v>
+        <v>0.17118622628250185</v>
       </c>
       <c r="G536">
         <v>1</v>
       </c>
       <c r="H536">
-        <v>3000</v>
+        <v>3450.0000000000005</v>
       </c>
       <c r="I536">
-        <v>57.499999999999986</v>
+        <v>63.25</v>
       </c>
       <c r="J536">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K536">
         <v>100</v>
@@ -50880,25 +50880,25 @@
         <v>409</v>
       </c>
       <c r="D537" t="s">
-        <v>431</v>
+        <v>169</v>
       </c>
       <c r="E537">
         <v>2022</v>
       </c>
       <c r="F537">
-        <v>0.39268525025376771</v>
+        <v>0.1902069180916687</v>
       </c>
       <c r="G537">
         <v>1</v>
       </c>
       <c r="H537">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I537">
-        <v>57.499999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J537">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K537">
         <v>100</v>
@@ -50933,13 +50933,13 @@
         <v>409</v>
       </c>
       <c r="D538" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E538">
         <v>2022</v>
       </c>
       <c r="F538">
-        <v>0.54331685796829887</v>
+        <v>0.46079159834465555</v>
       </c>
       <c r="G538">
         <v>1</v>
@@ -50986,25 +50986,25 @@
         <v>409</v>
       </c>
       <c r="D539" t="s">
-        <v>31</v>
+        <v>404</v>
       </c>
       <c r="E539">
         <v>2022</v>
       </c>
       <c r="F539">
-        <v>7.9150620754275036E-2</v>
+        <v>1.0955304911376598</v>
       </c>
       <c r="G539">
         <v>1</v>
       </c>
       <c r="H539">
-        <v>3450</v>
+        <v>3000</v>
       </c>
       <c r="I539">
-        <v>63.250000000000007</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="J539">
-        <v>2.3100000000000005</v>
+        <v>2.1</v>
       </c>
       <c r="K539">
         <v>100</v>
@@ -51039,25 +51039,25 @@
         <v>409</v>
       </c>
       <c r="D540" t="s">
-        <v>433</v>
+        <v>17</v>
       </c>
       <c r="E540">
         <v>2022</v>
       </c>
       <c r="F540">
-        <v>0.59270929960178054</v>
+        <v>0.13713305223705793</v>
       </c>
       <c r="G540">
         <v>1</v>
       </c>
       <c r="H540">
-        <v>3000</v>
+        <v>3450</v>
       </c>
       <c r="I540">
-        <v>57.499999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J540">
-        <v>2.1</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K540">
         <v>100</v>
@@ -51098,7 +51098,7 @@
         <v>2022</v>
       </c>
       <c r="F541">
-        <v>7.1480986960256149E-2</v>
+        <v>0.10338666354337477</v>
       </c>
       <c r="G541">
         <v>1</v>
@@ -51107,7 +51107,7 @@
         <v>3450</v>
       </c>
       <c r="I541">
-        <v>63.249999999999993</v>
+        <v>63.25</v>
       </c>
       <c r="J541">
         <v>2.3100000000000005</v>
@@ -51198,7 +51198,7 @@
         <v>409</v>
       </c>
       <c r="D543" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E543">
         <v>1964</v>
@@ -51251,7 +51251,7 @@
         <v>409</v>
       </c>
       <c r="D544" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E544">
         <v>1981</v>
@@ -51357,7 +51357,7 @@
         <v>409</v>
       </c>
       <c r="D546" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="E546">
         <v>1961</v>
@@ -51410,7 +51410,7 @@
         <v>409</v>
       </c>
       <c r="D547" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="E547">
         <v>1952</v>
@@ -51463,7 +51463,7 @@
         <v>409</v>
       </c>
       <c r="D548" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E548">
         <v>1963</v>
@@ -51622,7 +51622,7 @@
         <v>409</v>
       </c>
       <c r="D551" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E551">
         <v>1954</v>
@@ -51728,7 +51728,7 @@
         <v>409</v>
       </c>
       <c r="D553" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E553">
         <v>1963</v>
@@ -51781,7 +51781,7 @@
         <v>409</v>
       </c>
       <c r="D554" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E554">
         <v>1970</v>
@@ -51834,7 +51834,7 @@
         <v>409</v>
       </c>
       <c r="D555" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="E555">
         <v>1968</v>
@@ -52099,7 +52099,7 @@
         <v>409</v>
       </c>
       <c r="D560" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="E560">
         <v>1976</v>
@@ -52152,7 +52152,7 @@
         <v>409</v>
       </c>
       <c r="D561" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E561">
         <v>1961</v>
@@ -52258,7 +52258,7 @@
         <v>409</v>
       </c>
       <c r="D563" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="E563">
         <v>1968</v>
@@ -52364,7 +52364,7 @@
         <v>409</v>
       </c>
       <c r="D565" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="E565">
         <v>1965</v>
@@ -52523,7 +52523,7 @@
         <v>409</v>
       </c>
       <c r="D568" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E568">
         <v>1956</v>
@@ -52576,7 +52576,7 @@
         <v>409</v>
       </c>
       <c r="D569" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="E569">
         <v>1994</v>
@@ -52629,7 +52629,7 @@
         <v>409</v>
       </c>
       <c r="D570" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="E570">
         <v>1960</v>
@@ -52682,7 +52682,7 @@
         <v>409</v>
       </c>
       <c r="D571" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="E571">
         <v>1978</v>
@@ -52735,7 +52735,7 @@
         <v>409</v>
       </c>
       <c r="D572" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="E572">
         <v>1963</v>
@@ -52894,7 +52894,7 @@
         <v>409</v>
       </c>
       <c r="D575" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="E575">
         <v>1956</v>
@@ -53053,7 +53053,7 @@
         <v>409</v>
       </c>
       <c r="D578" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E578">
         <v>1973</v>
@@ -53265,7 +53265,7 @@
         <v>409</v>
       </c>
       <c r="D582" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="E582">
         <v>1959</v>
@@ -53371,7 +53371,7 @@
         <v>409</v>
       </c>
       <c r="D584" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="E584">
         <v>1979</v>
@@ -53424,7 +53424,7 @@
         <v>409</v>
       </c>
       <c r="D585" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="E585">
         <v>1979</v>
@@ -53530,7 +53530,7 @@
         <v>409</v>
       </c>
       <c r="D587" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="E587">
         <v>1960</v>
@@ -53583,7 +53583,7 @@
         <v>409</v>
       </c>
       <c r="D588" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E588">
         <v>1959</v>
@@ -53689,7 +53689,7 @@
         <v>409</v>
       </c>
       <c r="D590" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="E590">
         <v>1923</v>
@@ -53742,7 +53742,7 @@
         <v>409</v>
       </c>
       <c r="D591" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E591">
         <v>1957</v>
@@ -53795,7 +53795,7 @@
         <v>409</v>
       </c>
       <c r="D592" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="E592">
         <v>1976</v>
@@ -53848,7 +53848,7 @@
         <v>409</v>
       </c>
       <c r="D593" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="E593">
         <v>1989</v>
@@ -53901,7 +53901,7 @@
         <v>409</v>
       </c>
       <c r="D594" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E594">
         <v>1970</v>
@@ -54060,7 +54060,7 @@
         <v>409</v>
       </c>
       <c r="D597" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E597">
         <v>1967</v>
@@ -54537,7 +54537,7 @@
         <v>409</v>
       </c>
       <c r="D606" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E606">
         <v>1936</v>
@@ -54696,7 +54696,7 @@
         <v>409</v>
       </c>
       <c r="D609" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E609">
         <v>1959</v>
@@ -54749,7 +54749,7 @@
         <v>409</v>
       </c>
       <c r="D610" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E610">
         <v>1975</v>
@@ -55279,7 +55279,7 @@
         <v>409</v>
       </c>
       <c r="D620" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="E620">
         <v>1955</v>
@@ -55385,7 +55385,7 @@
         <v>409</v>
       </c>
       <c r="D622" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E622">
         <v>1930</v>
@@ -55438,7 +55438,7 @@
         <v>409</v>
       </c>
       <c r="D623" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E623">
         <v>1942</v>
@@ -55491,7 +55491,7 @@
         <v>409</v>
       </c>
       <c r="D624" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E624">
         <v>1975</v>
@@ -55544,7 +55544,7 @@
         <v>409</v>
       </c>
       <c r="D625" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E625">
         <v>1980</v>
@@ -55597,7 +55597,7 @@
         <v>409</v>
       </c>
       <c r="D626" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E626">
         <v>1966</v>
@@ -55650,7 +55650,7 @@
         <v>409</v>
       </c>
       <c r="D627" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E627">
         <v>1963</v>
@@ -56127,7 +56127,7 @@
         <v>409</v>
       </c>
       <c r="D636" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="E636">
         <v>1962</v>
@@ -56180,7 +56180,7 @@
         <v>409</v>
       </c>
       <c r="D637" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="E637">
         <v>1958</v>
@@ -56233,7 +56233,7 @@
         <v>409</v>
       </c>
       <c r="D638" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="E638">
         <v>1991</v>
@@ -56286,7 +56286,7 @@
         <v>409</v>
       </c>
       <c r="D639" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="E639">
         <v>1936</v>
@@ -56339,7 +56339,7 @@
         <v>409</v>
       </c>
       <c r="D640" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="E640">
         <v>1969</v>
@@ -56530,7 +56530,7 @@
         <v>409</v>
       </c>
       <c r="D644" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E644">
         <v>2022</v>
@@ -56562,7 +56562,7 @@
         <v>409</v>
       </c>
       <c r="D645" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E645">
         <v>1972</v>
@@ -56594,7 +56594,7 @@
         <v>409</v>
       </c>
       <c r="D646" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E646">
         <v>2022</v>
@@ -56690,7 +56690,7 @@
         <v>409</v>
       </c>
       <c r="D649" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E649">
         <v>1924</v>
@@ -57138,7 +57138,7 @@
         <v>409</v>
       </c>
       <c r="D663" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E663">
         <v>1960</v>
@@ -57298,7 +57298,7 @@
         <v>551</v>
       </c>
       <c r="D668" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="E668">
         <v>1962</v>
@@ -57362,7 +57362,7 @@
         <v>551</v>
       </c>
       <c r="D670" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="E670">
         <v>1964</v>
@@ -57394,7 +57394,7 @@
         <v>551</v>
       </c>
       <c r="D671" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E671">
         <v>1988</v>
@@ -57426,7 +57426,7 @@
         <v>551</v>
       </c>
       <c r="D672" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E672">
         <v>2005</v>
@@ -57458,7 +57458,7 @@
         <v>551</v>
       </c>
       <c r="D673" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="E673">
         <v>1999</v>
@@ -57490,7 +57490,7 @@
         <v>551</v>
       </c>
       <c r="D674" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="E674">
         <v>2014</v>
@@ -57522,7 +57522,7 @@
         <v>551</v>
       </c>
       <c r="D675" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="E675">
         <v>2033</v>
@@ -57554,7 +57554,7 @@
         <v>551</v>
       </c>
       <c r="D676" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="E676">
         <v>1986</v>
@@ -57650,7 +57650,7 @@
         <v>551</v>
       </c>
       <c r="D679" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E679">
         <v>1974</v>
@@ -57682,7 +57682,7 @@
         <v>551</v>
       </c>
       <c r="D680" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="E680">
         <v>1973</v>
@@ -57746,7 +57746,7 @@
         <v>551</v>
       </c>
       <c r="D682" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="E682">
         <v>1992</v>
@@ -57778,7 +57778,7 @@
         <v>551</v>
       </c>
       <c r="D683" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="E683">
         <v>1996</v>
@@ -57810,7 +57810,7 @@
         <v>551</v>
       </c>
       <c r="D684" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="E684">
         <v>1978</v>
@@ -57842,7 +57842,7 @@
         <v>551</v>
       </c>
       <c r="D685" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E685">
         <v>1980</v>
@@ -57874,7 +57874,7 @@
         <v>551</v>
       </c>
       <c r="D686" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="E686">
         <v>1980</v>
@@ -57906,7 +57906,7 @@
         <v>551</v>
       </c>
       <c r="D687" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E687">
         <v>1974</v>
@@ -57938,7 +57938,7 @@
         <v>551</v>
       </c>
       <c r="D688" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E688">
         <v>2007</v>
@@ -58002,7 +58002,7 @@
         <v>551</v>
       </c>
       <c r="D690" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E690">
         <v>1968</v>
@@ -58066,7 +58066,7 @@
         <v>551</v>
       </c>
       <c r="D692" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="E692">
         <v>1973</v>
@@ -58098,7 +58098,7 @@
         <v>551</v>
       </c>
       <c r="D693" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="E693">
         <v>1994</v>
@@ -58130,7 +58130,7 @@
         <v>551</v>
       </c>
       <c r="D694" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="E694">
         <v>1965</v>
@@ -58162,7 +58162,7 @@
         <v>551</v>
       </c>
       <c r="D695" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E695">
         <v>1983</v>
@@ -58226,7 +58226,7 @@
         <v>551</v>
       </c>
       <c r="D697" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="E697">
         <v>1982</v>
@@ -58290,7 +58290,7 @@
         <v>551</v>
       </c>
       <c r="D699" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="E699">
         <v>1965</v>
@@ -58354,7 +58354,7 @@
         <v>409</v>
       </c>
       <c r="D701" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="E701">
         <v>1981</v>
@@ -58418,7 +58418,7 @@
         <v>409</v>
       </c>
       <c r="D703" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E703">
         <v>1925</v>
@@ -58450,7 +58450,7 @@
         <v>409</v>
       </c>
       <c r="D704" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E704">
         <v>1943</v>
@@ -59442,7 +59442,7 @@
         <v>592</v>
       </c>
       <c r="D735" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E735">
         <v>1995</v>
@@ -59474,7 +59474,7 @@
         <v>592</v>
       </c>
       <c r="D736" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E736">
         <v>2002</v>
@@ -59666,7 +59666,7 @@
         <v>636</v>
       </c>
       <c r="D742" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E742">
         <v>1978</v>
@@ -59762,7 +59762,7 @@
         <v>636</v>
       </c>
       <c r="D745" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E745">
         <v>1981</v>
@@ -59794,7 +59794,7 @@
         <v>636</v>
       </c>
       <c r="D746" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E746">
         <v>1981</v>
@@ -59826,7 +59826,7 @@
         <v>636</v>
       </c>
       <c r="D747" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E747">
         <v>1987</v>
@@ -59858,7 +59858,7 @@
         <v>636</v>
       </c>
       <c r="D748" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E748">
         <v>1987</v>
@@ -60274,7 +60274,7 @@
         <v>636</v>
       </c>
       <c r="D761" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E761">
         <v>1973</v>
@@ -60568,7 +60568,7 @@
         <v>2022</v>
       </c>
       <c r="F770">
-        <v>17.631312619735244</v>
+        <v>18.698663529818063</v>
       </c>
       <c r="G770">
         <v>1</v>
@@ -60603,7 +60603,7 @@
         <v>2022</v>
       </c>
       <c r="F771">
-        <v>18.698663529818063</v>
+        <v>17.631312619735244</v>
       </c>
       <c r="G771">
         <v>1</v>
@@ -67807,7 +67807,7 @@
         <v>662</v>
       </c>
       <c r="D977" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E977">
         <v>2013</v>
@@ -67842,7 +67842,7 @@
         <v>662</v>
       </c>
       <c r="D978" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E978">
         <v>2014</v>
@@ -67877,7 +67877,7 @@
         <v>662</v>
       </c>
       <c r="D979" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E979">
         <v>2015</v>
@@ -67912,7 +67912,7 @@
         <v>662</v>
       </c>
       <c r="D980" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E980">
         <v>2016</v>
@@ -67947,7 +67947,7 @@
         <v>662</v>
       </c>
       <c r="D981" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E981">
         <v>2017</v>
@@ -67982,7 +67982,7 @@
         <v>662</v>
       </c>
       <c r="D982" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E982">
         <v>2018</v>
@@ -68017,7 +68017,7 @@
         <v>662</v>
       </c>
       <c r="D983" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E983">
         <v>2019</v>
@@ -68052,7 +68052,7 @@
         <v>662</v>
       </c>
       <c r="D984" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E984">
         <v>2020</v>
@@ -68087,7 +68087,7 @@
         <v>662</v>
       </c>
       <c r="D985" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E985">
         <v>2021</v>
@@ -68122,7 +68122,7 @@
         <v>662</v>
       </c>
       <c r="D986" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E986">
         <v>2022</v>
@@ -68157,7 +68157,7 @@
         <v>662</v>
       </c>
       <c r="D987" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E987">
         <v>2023</v>
@@ -68192,7 +68192,7 @@
         <v>662</v>
       </c>
       <c r="D988" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E988">
         <v>2024</v>
@@ -68227,7 +68227,7 @@
         <v>662</v>
       </c>
       <c r="D989" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E989">
         <v>2028</v>
@@ -68682,7 +68682,7 @@
         <v>662</v>
       </c>
       <c r="D1002" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1002">
         <v>2013</v>
@@ -68717,7 +68717,7 @@
         <v>662</v>
       </c>
       <c r="D1003" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1003">
         <v>2014</v>
@@ -68752,7 +68752,7 @@
         <v>662</v>
       </c>
       <c r="D1004" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1004">
         <v>2015</v>
@@ -68787,7 +68787,7 @@
         <v>662</v>
       </c>
       <c r="D1005" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1005">
         <v>2016</v>
@@ -68822,7 +68822,7 @@
         <v>662</v>
       </c>
       <c r="D1006" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1006">
         <v>2017</v>
@@ -68857,7 +68857,7 @@
         <v>662</v>
       </c>
       <c r="D1007" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1007">
         <v>2018</v>
@@ -68892,7 +68892,7 @@
         <v>662</v>
       </c>
       <c r="D1008" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1008">
         <v>2019</v>
@@ -68927,7 +68927,7 @@
         <v>662</v>
       </c>
       <c r="D1009" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1009">
         <v>2020</v>
@@ -68962,7 +68962,7 @@
         <v>662</v>
       </c>
       <c r="D1010" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1010">
         <v>2021</v>
@@ -68997,7 +68997,7 @@
         <v>662</v>
       </c>
       <c r="D1011" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1011">
         <v>2022</v>
@@ -69032,7 +69032,7 @@
         <v>662</v>
       </c>
       <c r="D1012" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1012">
         <v>2023</v>
@@ -69067,7 +69067,7 @@
         <v>662</v>
       </c>
       <c r="D1013" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1013">
         <v>2024</v>
@@ -69102,7 +69102,7 @@
         <v>662</v>
       </c>
       <c r="D1014" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E1014">
         <v>2028</v>
@@ -71132,13 +71132,13 @@
         <v>662</v>
       </c>
       <c r="D1072" t="s">
-        <v>605</v>
+        <v>224</v>
       </c>
       <c r="E1072">
         <v>2013</v>
       </c>
       <c r="F1072">
-        <v>2E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G1072">
         <v>1</v>
@@ -71156,7 +71156,7 @@
         <v>42</v>
       </c>
       <c r="L1072">
-        <v>0.1921131304391373</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1073" spans="2:12" x14ac:dyDescent="0.45">
@@ -71167,13 +71167,13 @@
         <v>662</v>
       </c>
       <c r="D1073" t="s">
-        <v>224</v>
+        <v>605</v>
       </c>
       <c r="E1073">
         <v>2013</v>
       </c>
       <c r="F1073">
-        <v>1.4E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="G1073">
         <v>1</v>
@@ -71191,7 +71191,7 @@
         <v>42</v>
       </c>
       <c r="L1073">
-        <v>0.1885335384832984</v>
+        <v>0.1921131304391373</v>
       </c>
     </row>
     <row r="1074" spans="2:12" x14ac:dyDescent="0.45">
@@ -71202,13 +71202,13 @@
         <v>662</v>
       </c>
       <c r="D1074" t="s">
-        <v>179</v>
+        <v>33</v>
       </c>
       <c r="E1074">
         <v>2013</v>
       </c>
       <c r="F1074">
-        <v>1.9E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1074">
         <v>1</v>
@@ -71217,7 +71217,7 @@
         <v>1458</v>
       </c>
       <c r="I1074">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1074">
         <v>0</v>
@@ -71226,7 +71226,7 @@
         <v>42</v>
       </c>
       <c r="L1074">
-        <v>0.18013391841854179</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1075" spans="2:12" x14ac:dyDescent="0.45">
@@ -71237,13 +71237,13 @@
         <v>662</v>
       </c>
       <c r="D1075" t="s">
-        <v>33</v>
+        <v>179</v>
       </c>
       <c r="E1075">
         <v>2013</v>
       </c>
       <c r="F1075">
-        <v>3.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1075">
         <v>1</v>
@@ -71252,7 +71252,7 @@
         <v>1458</v>
       </c>
       <c r="I1075">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1075">
         <v>0</v>
@@ -71261,7 +71261,7 @@
         <v>42</v>
       </c>
       <c r="L1075">
-        <v>0.19855392263260624</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1076" spans="2:12" x14ac:dyDescent="0.45">
@@ -71272,13 +71272,13 @@
         <v>662</v>
       </c>
       <c r="D1076" t="s">
-        <v>224</v>
+        <v>77</v>
       </c>
       <c r="E1076">
         <v>2014</v>
       </c>
       <c r="F1076">
-        <v>3.8999999999999998E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1076">
         <v>1</v>
@@ -71342,13 +71342,13 @@
         <v>662</v>
       </c>
       <c r="D1078" t="s">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="E1078">
         <v>2014</v>
       </c>
       <c r="F1078">
-        <v>2.5000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="G1078">
         <v>1</v>
@@ -71377,19 +71377,19 @@
         <v>662</v>
       </c>
       <c r="D1079" t="s">
-        <v>600</v>
+        <v>77</v>
       </c>
       <c r="E1079">
         <v>2015</v>
       </c>
       <c r="F1079">
-        <v>4.9000000000000007E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1079">
         <v>1</v>
       </c>
       <c r="H1079">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1079">
         <v>22.424999999999997</v>
@@ -71401,7 +71401,7 @@
         <v>40</v>
       </c>
       <c r="L1079">
-        <v>0.18956968490584708</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1080" spans="2:12" x14ac:dyDescent="0.45">
@@ -71447,13 +71447,13 @@
         <v>662</v>
       </c>
       <c r="D1081" t="s">
-        <v>725</v>
+        <v>224</v>
       </c>
       <c r="E1081">
         <v>2015</v>
       </c>
       <c r="F1081">
-        <v>1E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="G1081">
         <v>1</v>
@@ -71471,7 +71471,7 @@
         <v>40</v>
       </c>
       <c r="L1081">
-        <v>0.17907908788454549</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1082" spans="2:12" x14ac:dyDescent="0.45">
@@ -71482,19 +71482,19 @@
         <v>662</v>
       </c>
       <c r="D1082" t="s">
-        <v>77</v>
+        <v>600</v>
       </c>
       <c r="E1082">
         <v>2015</v>
       </c>
       <c r="F1082">
-        <v>1E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1082">
         <v>1</v>
       </c>
       <c r="H1082">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1082">
         <v>22.424999999999997</v>
@@ -71506,7 +71506,7 @@
         <v>40</v>
       </c>
       <c r="L1082">
-        <v>0.1885335384832984</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1083" spans="2:12" x14ac:dyDescent="0.45">
@@ -71517,13 +71517,13 @@
         <v>662</v>
       </c>
       <c r="D1083" t="s">
-        <v>224</v>
+        <v>725</v>
       </c>
       <c r="E1083">
         <v>2015</v>
       </c>
       <c r="F1083">
-        <v>6.4000000000000003E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1083">
         <v>1</v>
@@ -71541,7 +71541,7 @@
         <v>40</v>
       </c>
       <c r="L1083">
-        <v>0.1885335384832984</v>
+        <v>0.17907908788454549</v>
       </c>
     </row>
     <row r="1084" spans="2:12" x14ac:dyDescent="0.45">
@@ -71552,13 +71552,13 @@
         <v>662</v>
       </c>
       <c r="D1084" t="s">
-        <v>605</v>
+        <v>33</v>
       </c>
       <c r="E1084">
         <v>2016</v>
       </c>
       <c r="F1084">
-        <v>1E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G1084">
         <v>1</v>
@@ -71576,7 +71576,7 @@
         <v>39</v>
       </c>
       <c r="L1084">
-        <v>0.1921131304391373</v>
+        <v>0.19855392263260621</v>
       </c>
     </row>
     <row r="1085" spans="2:12" x14ac:dyDescent="0.45">
@@ -71587,13 +71587,13 @@
         <v>662</v>
       </c>
       <c r="D1085" t="s">
-        <v>33</v>
+        <v>605</v>
       </c>
       <c r="E1085">
         <v>2016</v>
       </c>
       <c r="F1085">
-        <v>1.5E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1085">
         <v>1</v>
@@ -71611,7 +71611,7 @@
         <v>39</v>
       </c>
       <c r="L1085">
-        <v>0.19855392263260621</v>
+        <v>0.1921131304391373</v>
       </c>
     </row>
     <row r="1086" spans="2:12" x14ac:dyDescent="0.45">
@@ -71622,13 +71622,13 @@
         <v>662</v>
       </c>
       <c r="D1086" t="s">
-        <v>224</v>
+        <v>52</v>
       </c>
       <c r="E1086">
         <v>2017</v>
       </c>
       <c r="F1086">
-        <v>4.4999999999999997E-3</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="G1086">
         <v>1</v>
@@ -71657,13 +71657,13 @@
         <v>662</v>
       </c>
       <c r="D1087" t="s">
-        <v>52</v>
+        <v>224</v>
       </c>
       <c r="E1087">
         <v>2017</v>
       </c>
       <c r="F1087">
-        <v>1.5699999999999999E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="G1087">
         <v>1</v>
@@ -72028,7 +72028,7 @@
         <v>730</v>
       </c>
       <c r="D1100" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1100">
         <v>2025</v>
@@ -72080,13 +72080,13 @@
         <v>2022</v>
       </c>
       <c r="F1102">
-        <v>0.2581233858557071</v>
+        <v>0.22233075482827466</v>
       </c>
       <c r="G1102">
         <v>0.33123000000000002</v>
       </c>
       <c r="L1102">
-        <v>0.38431032951329569</v>
+        <v>0.3843103295132958</v>
       </c>
     </row>
     <row r="1103" spans="2:12" x14ac:dyDescent="0.45">
@@ -72103,13 +72103,13 @@
         <v>2022</v>
       </c>
       <c r="F1103">
-        <v>0.22233075482827466</v>
+        <v>0.2581233858557071</v>
       </c>
       <c r="G1103">
         <v>0.33123000000000002</v>
       </c>
       <c r="L1103">
-        <v>0.38431032951329569</v>
+        <v>0.3843103295132958</v>
       </c>
     </row>
     <row r="1104" spans="2:12" x14ac:dyDescent="0.45">
@@ -72120,7 +72120,7 @@
         <v>736</v>
       </c>
       <c r="D1104" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1104">
         <v>2022</v>
@@ -72132,7 +72132,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1104">
-        <v>0.38431032951329569</v>
+        <v>0.3843103295132958</v>
       </c>
     </row>
     <row r="1105" spans="2:12" x14ac:dyDescent="0.45">
@@ -73086,7 +73086,7 @@
         <v>736</v>
       </c>
       <c r="D1146" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E1146">
         <v>2009</v>
@@ -73109,7 +73109,7 @@
         <v>736</v>
       </c>
       <c r="D1147" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E1147">
         <v>2010</v>
@@ -73132,7 +73132,7 @@
         <v>736</v>
       </c>
       <c r="D1148" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E1148">
         <v>2015</v>
@@ -74213,7 +74213,7 @@
         <v>736</v>
       </c>
       <c r="D1195" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1195">
         <v>2001</v>
@@ -74236,7 +74236,7 @@
         <v>736</v>
       </c>
       <c r="D1196" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1196">
         <v>2003</v>
@@ -74259,7 +74259,7 @@
         <v>736</v>
       </c>
       <c r="D1197" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1197">
         <v>2004</v>
@@ -74282,7 +74282,7 @@
         <v>736</v>
       </c>
       <c r="D1198" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1198">
         <v>2005</v>
@@ -74305,7 +74305,7 @@
         <v>736</v>
       </c>
       <c r="D1199" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1199">
         <v>2007</v>
@@ -74328,7 +74328,7 @@
         <v>736</v>
       </c>
       <c r="D1200" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1200">
         <v>2008</v>
@@ -74351,7 +74351,7 @@
         <v>736</v>
       </c>
       <c r="D1201" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1201">
         <v>2011</v>
@@ -74374,7 +74374,7 @@
         <v>736</v>
       </c>
       <c r="D1202" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1202">
         <v>2014</v>
@@ -74397,7 +74397,7 @@
         <v>736</v>
       </c>
       <c r="D1203" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1203">
         <v>2015</v>
@@ -74420,7 +74420,7 @@
         <v>736</v>
       </c>
       <c r="D1204" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1204">
         <v>2016</v>
@@ -74443,7 +74443,7 @@
         <v>736</v>
       </c>
       <c r="D1205" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1205">
         <v>2018</v>
@@ -74466,7 +74466,7 @@
         <v>736</v>
       </c>
       <c r="D1206" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1206">
         <v>2020</v>
@@ -74489,7 +74489,7 @@
         <v>736</v>
       </c>
       <c r="D1207" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1207">
         <v>2021</v>
@@ -74512,7 +74512,7 @@
         <v>736</v>
       </c>
       <c r="D1208" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1208">
         <v>2022</v>
@@ -74535,7 +74535,7 @@
         <v>736</v>
       </c>
       <c r="D1209" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1209">
         <v>2023</v>
@@ -74558,7 +74558,7 @@
         <v>736</v>
       </c>
       <c r="D1210" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E1210">
         <v>2024</v>

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C022E14-767D-44A3-A713-275A4A4FB75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{628D681C-D5D5-4E42-8A79-B603B903406E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D85BCD6D-876F-415B-A1F4-3C73946DD0BE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C83C7ED3-87E5-46AA-BB42-895B1C2C77F5}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3651,13 +3651,13 @@
     <t>Gobo power station_1</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - 25_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - 14_Missing Solar Capacity</t>
-  </si>
-  <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - 25_Missing Solar Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - IRENA Gap - 13_Missing Solar Capacity</t>
@@ -5153,7 +5153,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E15C9D-FD52-4790-A10F-3CE87C5F6941}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39DE71F9-04A3-42BE-AA3D-1FF767A67ABD}">
   <dimension ref="B9:T380"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23028,7 +23028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57109D54-5079-4B39-BEFB-ADCD40CD96B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C613C1-01D6-4BB4-BA08-ED7A937149A5}">
   <dimension ref="B9:T1231"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27268,7 +27268,7 @@
         <v>130</v>
       </c>
       <c r="P89" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="Q89" t="s">
         <v>824</v>
@@ -27321,7 +27321,7 @@
         <v>130</v>
       </c>
       <c r="P90" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="Q90" t="s">
         <v>824</v>
@@ -44864,7 +44864,7 @@
         <v>525</v>
       </c>
       <c r="P421" t="s">
-        <v>1095</v>
+        <v>884</v>
       </c>
       <c r="Q421" t="s">
         <v>824</v>
@@ -44917,7 +44917,7 @@
         <v>525</v>
       </c>
       <c r="P422" t="s">
-        <v>884</v>
+        <v>1095</v>
       </c>
       <c r="Q422" t="s">
         <v>824</v>
@@ -45182,7 +45182,7 @@
         <v>530</v>
       </c>
       <c r="P427" t="s">
-        <v>1098</v>
+        <v>884</v>
       </c>
       <c r="Q427" t="s">
         <v>824</v>
@@ -45235,7 +45235,7 @@
         <v>530</v>
       </c>
       <c r="P428" t="s">
-        <v>884</v>
+        <v>1098</v>
       </c>
       <c r="Q428" t="s">
         <v>824</v>
@@ -45288,7 +45288,7 @@
         <v>531</v>
       </c>
       <c r="P429" t="s">
-        <v>1099</v>
+        <v>884</v>
       </c>
       <c r="Q429" t="s">
         <v>824</v>
@@ -45341,7 +45341,7 @@
         <v>531</v>
       </c>
       <c r="P430" t="s">
-        <v>884</v>
+        <v>1099</v>
       </c>
       <c r="Q430" t="s">
         <v>824</v>
@@ -45712,7 +45712,7 @@
         <v>540</v>
       </c>
       <c r="P437" t="s">
-        <v>1105</v>
+        <v>884</v>
       </c>
       <c r="Q437" t="s">
         <v>824</v>
@@ -45765,7 +45765,7 @@
         <v>540</v>
       </c>
       <c r="P438" t="s">
-        <v>884</v>
+        <v>1105</v>
       </c>
       <c r="Q438" t="s">
         <v>824</v>
@@ -45818,7 +45818,7 @@
         <v>541</v>
       </c>
       <c r="P439" t="s">
-        <v>1106</v>
+        <v>884</v>
       </c>
       <c r="Q439" t="s">
         <v>824</v>
@@ -45871,7 +45871,7 @@
         <v>541</v>
       </c>
       <c r="P440" t="s">
-        <v>884</v>
+        <v>1106</v>
       </c>
       <c r="Q440" t="s">
         <v>824</v>
@@ -45924,7 +45924,7 @@
         <v>542</v>
       </c>
       <c r="P441" t="s">
-        <v>1107</v>
+        <v>884</v>
       </c>
       <c r="Q441" t="s">
         <v>824</v>
@@ -45977,7 +45977,7 @@
         <v>542</v>
       </c>
       <c r="P442" t="s">
-        <v>884</v>
+        <v>1107</v>
       </c>
       <c r="Q442" t="s">
         <v>824</v>
@@ -47514,7 +47514,7 @@
         <v>573</v>
       </c>
       <c r="P471" t="s">
-        <v>884</v>
+        <v>1121</v>
       </c>
       <c r="Q471" t="s">
         <v>824</v>
@@ -47567,7 +47567,7 @@
         <v>573</v>
       </c>
       <c r="P472" t="s">
-        <v>1121</v>
+        <v>884</v>
       </c>
       <c r="Q472" t="s">
         <v>824</v>
@@ -60712,7 +60712,7 @@
         <v>2022</v>
       </c>
       <c r="F770">
-        <v>18.582374503019896</v>
+        <v>17.802179718220831</v>
       </c>
       <c r="G770">
         <v>1</v>
@@ -60747,7 +60747,7 @@
         <v>2022</v>
       </c>
       <c r="F771">
-        <v>17.802179718220831</v>
+        <v>17.945745778759274</v>
       </c>
       <c r="G771">
         <v>1</v>
@@ -60782,7 +60782,7 @@
         <v>2022</v>
       </c>
       <c r="F772">
-        <v>17.945745778759274</v>
+        <v>18.582374503019896</v>
       </c>
       <c r="G772">
         <v>1</v>
@@ -71311,13 +71311,13 @@
         <v>689</v>
       </c>
       <c r="D1073" t="s">
-        <v>228</v>
+        <v>24</v>
       </c>
       <c r="E1073">
         <v>2013</v>
       </c>
       <c r="F1073">
-        <v>1.4E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1073">
         <v>1</v>
@@ -71326,7 +71326,7 @@
         <v>1458</v>
       </c>
       <c r="I1073">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1073">
         <v>0</v>
@@ -71335,7 +71335,7 @@
         <v>42</v>
       </c>
       <c r="L1073">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1074" spans="2:12" x14ac:dyDescent="0.45">
@@ -71346,13 +71346,13 @@
         <v>689</v>
       </c>
       <c r="D1074" t="s">
-        <v>632</v>
+        <v>228</v>
       </c>
       <c r="E1074">
         <v>2013</v>
       </c>
       <c r="F1074">
-        <v>2E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G1074">
         <v>1</v>
@@ -71370,7 +71370,7 @@
         <v>42</v>
       </c>
       <c r="L1074">
-        <v>0.1921131304391373</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1075" spans="2:12" x14ac:dyDescent="0.45">
@@ -71381,13 +71381,13 @@
         <v>689</v>
       </c>
       <c r="D1075" t="s">
-        <v>24</v>
+        <v>632</v>
       </c>
       <c r="E1075">
         <v>2013</v>
       </c>
       <c r="F1075">
-        <v>3.5000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="G1075">
         <v>1</v>
@@ -71396,7 +71396,7 @@
         <v>1458</v>
       </c>
       <c r="I1075">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1075">
         <v>0</v>
@@ -71405,7 +71405,7 @@
         <v>42</v>
       </c>
       <c r="L1075">
-        <v>0.19855392263260624</v>
+        <v>0.1921131304391373</v>
       </c>
     </row>
     <row r="1076" spans="2:12" x14ac:dyDescent="0.45">
@@ -71416,13 +71416,13 @@
         <v>689</v>
       </c>
       <c r="D1076" t="s">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="E1076">
         <v>2014</v>
       </c>
       <c r="F1076">
-        <v>2.5000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="G1076">
         <v>1</v>
@@ -71451,19 +71451,19 @@
         <v>689</v>
       </c>
       <c r="D1077" t="s">
-        <v>228</v>
+        <v>24</v>
       </c>
       <c r="E1077">
         <v>2014</v>
       </c>
       <c r="F1077">
-        <v>3.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G1077">
         <v>1</v>
       </c>
       <c r="H1077">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1077">
         <v>22.424999999999997</v>
@@ -71475,7 +71475,7 @@
         <v>41</v>
       </c>
       <c r="L1077">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260618</v>
       </c>
     </row>
     <row r="1078" spans="2:12" x14ac:dyDescent="0.45">
@@ -71486,19 +71486,19 @@
         <v>689</v>
       </c>
       <c r="D1078" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="E1078">
         <v>2014</v>
       </c>
       <c r="F1078">
-        <v>2.7000000000000001E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1078">
         <v>1</v>
       </c>
       <c r="H1078">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1078">
         <v>22.424999999999997</v>
@@ -71510,7 +71510,7 @@
         <v>41</v>
       </c>
       <c r="L1078">
-        <v>0.19855392263260618</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1079" spans="2:12" x14ac:dyDescent="0.45">
@@ -71521,13 +71521,13 @@
         <v>689</v>
       </c>
       <c r="D1079" t="s">
-        <v>752</v>
+        <v>228</v>
       </c>
       <c r="E1079">
         <v>2015</v>
       </c>
       <c r="F1079">
-        <v>1E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="G1079">
         <v>1</v>
@@ -71545,7 +71545,7 @@
         <v>40</v>
       </c>
       <c r="L1079">
-        <v>0.17907908788454549</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1080" spans="2:12" x14ac:dyDescent="0.45">
@@ -71556,13 +71556,13 @@
         <v>689</v>
       </c>
       <c r="D1080" t="s">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E1080">
         <v>2015</v>
       </c>
       <c r="F1080">
-        <v>6.4000000000000003E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1080">
         <v>1</v>
@@ -71626,7 +71626,7 @@
         <v>689</v>
       </c>
       <c r="D1082" t="s">
-        <v>74</v>
+        <v>752</v>
       </c>
       <c r="E1082">
         <v>2015</v>
@@ -71650,7 +71650,7 @@
         <v>40</v>
       </c>
       <c r="L1082">
-        <v>0.1885335384832984</v>
+        <v>0.17907908788454549</v>
       </c>
     </row>
     <row r="1083" spans="2:12" x14ac:dyDescent="0.45">
@@ -71766,13 +71766,13 @@
         <v>689</v>
       </c>
       <c r="D1086" t="s">
-        <v>228</v>
+        <v>47</v>
       </c>
       <c r="E1086">
         <v>2017</v>
       </c>
       <c r="F1086">
-        <v>4.4999999999999997E-3</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="G1086">
         <v>1</v>
@@ -71801,13 +71801,13 @@
         <v>689</v>
       </c>
       <c r="D1087" t="s">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="E1087">
         <v>2017</v>
       </c>
       <c r="F1087">
-        <v>1.5699999999999999E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="G1087">
         <v>1</v>
@@ -72023,7 +72023,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1093">
-        <v>0.38298883693604868</v>
+        <v>0.38298883693604863</v>
       </c>
     </row>
     <row r="1094" spans="2:12" x14ac:dyDescent="0.45">
@@ -72230,7 +72230,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1102">
-        <v>0.38431032951329558</v>
+        <v>0.38431032951329563</v>
       </c>
     </row>
     <row r="1103" spans="2:12" x14ac:dyDescent="0.45">
@@ -72253,7 +72253,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1103">
-        <v>0.38431032951329558</v>
+        <v>0.38431032951329563</v>
       </c>
     </row>
     <row r="1104" spans="2:12" x14ac:dyDescent="0.45">
@@ -72276,7 +72276,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1104">
-        <v>0.38431032951329558</v>
+        <v>0.38431032951329563</v>
       </c>
     </row>
     <row r="1105" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F307CE19-5760-4E7D-B2F0-4DD173868C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA27E351-328D-4DA2-B976-445C874F190D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{75C73794-96BF-4A47-B40E-55212691B0AA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{013ED7C8-6DE1-4143-BE51-C9089CA39F8D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5168,7 +5168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB3DA6BC-C50F-4AE0-8DD2-78660C77336B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C280905-401A-421E-9130-248D60A6F51E}">
   <dimension ref="B9:T380"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23043,7 +23043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E3954C-C5BE-48B5-893D-DA55B5B6352E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3AFDD13-3E76-460F-988D-91B01BBEE57E}">
   <dimension ref="B9:T1233"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -28343,7 +28343,7 @@
         <v>153</v>
       </c>
       <c r="P109" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="Q109" t="s">
         <v>829</v>
@@ -28396,7 +28396,7 @@
         <v>153</v>
       </c>
       <c r="P110" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="Q110" t="s">
         <v>829</v>
@@ -44667,7 +44667,7 @@
         <v>520</v>
       </c>
       <c r="P417" t="s">
-        <v>889</v>
+        <v>1098</v>
       </c>
       <c r="Q417" t="s">
         <v>829</v>
@@ -44720,7 +44720,7 @@
         <v>520</v>
       </c>
       <c r="P418" t="s">
-        <v>1098</v>
+        <v>889</v>
       </c>
       <c r="Q418" t="s">
         <v>829</v>
@@ -44879,7 +44879,7 @@
         <v>525</v>
       </c>
       <c r="P421" t="s">
-        <v>1100</v>
+        <v>889</v>
       </c>
       <c r="Q421" t="s">
         <v>829</v>
@@ -44932,7 +44932,7 @@
         <v>525</v>
       </c>
       <c r="P422" t="s">
-        <v>889</v>
+        <v>1100</v>
       </c>
       <c r="Q422" t="s">
         <v>829</v>
@@ -45303,7 +45303,7 @@
         <v>531</v>
       </c>
       <c r="P429" t="s">
-        <v>1104</v>
+        <v>889</v>
       </c>
       <c r="Q429" t="s">
         <v>829</v>
@@ -45356,7 +45356,7 @@
         <v>531</v>
       </c>
       <c r="P430" t="s">
-        <v>889</v>
+        <v>1104</v>
       </c>
       <c r="Q430" t="s">
         <v>829</v>
@@ -45621,7 +45621,7 @@
         <v>539</v>
       </c>
       <c r="P435" t="s">
-        <v>1109</v>
+        <v>889</v>
       </c>
       <c r="Q435" t="s">
         <v>829</v>
@@ -45674,7 +45674,7 @@
         <v>539</v>
       </c>
       <c r="P436" t="s">
-        <v>889</v>
+        <v>1109</v>
       </c>
       <c r="Q436" t="s">
         <v>829</v>
@@ -45939,7 +45939,7 @@
         <v>542</v>
       </c>
       <c r="P441" t="s">
-        <v>1112</v>
+        <v>889</v>
       </c>
       <c r="Q441" t="s">
         <v>829</v>
@@ -45992,7 +45992,7 @@
         <v>542</v>
       </c>
       <c r="P442" t="s">
-        <v>889</v>
+        <v>1112</v>
       </c>
       <c r="Q442" t="s">
         <v>829</v>
@@ -47529,7 +47529,7 @@
         <v>573</v>
       </c>
       <c r="P471" t="s">
-        <v>1126</v>
+        <v>889</v>
       </c>
       <c r="Q471" t="s">
         <v>829</v>
@@ -47582,7 +47582,7 @@
         <v>573</v>
       </c>
       <c r="P472" t="s">
-        <v>889</v>
+        <v>1126</v>
       </c>
       <c r="Q472" t="s">
         <v>829</v>
@@ -53677,7 +53677,7 @@
         <v>713</v>
       </c>
       <c r="P587" t="s">
-        <v>889</v>
+        <v>1210</v>
       </c>
       <c r="Q587" t="s">
         <v>829</v>
@@ -53730,7 +53730,7 @@
         <v>713</v>
       </c>
       <c r="P588" t="s">
-        <v>1210</v>
+        <v>889</v>
       </c>
       <c r="Q588" t="s">
         <v>829</v>
@@ -55638,7 +55638,7 @@
         <v>778</v>
       </c>
       <c r="P624" t="s">
-        <v>889</v>
+        <v>1219</v>
       </c>
       <c r="Q624" t="s">
         <v>829</v>
@@ -55691,7 +55691,7 @@
         <v>778</v>
       </c>
       <c r="P625" t="s">
-        <v>1219</v>
+        <v>889</v>
       </c>
       <c r="Q625" t="s">
         <v>829</v>
@@ -71333,13 +71333,13 @@
         <v>689</v>
       </c>
       <c r="D1072" t="s">
-        <v>24</v>
+        <v>183</v>
       </c>
       <c r="E1072">
         <v>2013</v>
       </c>
       <c r="F1072">
-        <v>3.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1072">
         <v>1</v>
@@ -71348,7 +71348,7 @@
         <v>1458</v>
       </c>
       <c r="I1072">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1072">
         <v>0</v>
@@ -71357,7 +71357,7 @@
         <v>42</v>
       </c>
       <c r="L1072">
-        <v>0.19855392263260624</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1073" spans="2:12" x14ac:dyDescent="0.45">
@@ -71438,13 +71438,13 @@
         <v>689</v>
       </c>
       <c r="D1075" t="s">
-        <v>183</v>
+        <v>24</v>
       </c>
       <c r="E1075">
         <v>2013</v>
       </c>
       <c r="F1075">
-        <v>1.9E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1075">
         <v>1</v>
@@ -71453,7 +71453,7 @@
         <v>1458</v>
       </c>
       <c r="I1075">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1075">
         <v>0</v>
@@ -71462,7 +71462,7 @@
         <v>42</v>
       </c>
       <c r="L1075">
-        <v>0.18013391841854179</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1076" spans="2:12" x14ac:dyDescent="0.45">
@@ -71473,19 +71473,19 @@
         <v>689</v>
       </c>
       <c r="D1076" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="E1076">
         <v>2014</v>
       </c>
       <c r="F1076">
-        <v>2.5000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G1076">
         <v>1</v>
       </c>
       <c r="H1076">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1076">
         <v>22.424999999999997</v>
@@ -71497,7 +71497,7 @@
         <v>41</v>
       </c>
       <c r="L1076">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260618</v>
       </c>
     </row>
     <row r="1077" spans="2:12" x14ac:dyDescent="0.45">
@@ -71508,13 +71508,13 @@
         <v>689</v>
       </c>
       <c r="D1077" t="s">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E1077">
         <v>2014</v>
       </c>
       <c r="F1077">
-        <v>3.8999999999999998E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1077">
         <v>1</v>
@@ -71543,19 +71543,19 @@
         <v>689</v>
       </c>
       <c r="D1078" t="s">
-        <v>24</v>
+        <v>228</v>
       </c>
       <c r="E1078">
         <v>2014</v>
       </c>
       <c r="F1078">
-        <v>2.7000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="G1078">
         <v>1</v>
       </c>
       <c r="H1078">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1078">
         <v>22.424999999999997</v>
@@ -71567,7 +71567,7 @@
         <v>41</v>
       </c>
       <c r="L1078">
-        <v>0.19855392263260618</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1079" spans="2:12" x14ac:dyDescent="0.45">
@@ -71578,7 +71578,7 @@
         <v>689</v>
       </c>
       <c r="D1079" t="s">
-        <v>74</v>
+        <v>751</v>
       </c>
       <c r="E1079">
         <v>2015</v>
@@ -71602,7 +71602,7 @@
         <v>40</v>
       </c>
       <c r="L1079">
-        <v>0.1885335384832984</v>
+        <v>0.17907908788454549</v>
       </c>
     </row>
     <row r="1080" spans="2:12" x14ac:dyDescent="0.45">
@@ -71613,13 +71613,13 @@
         <v>689</v>
       </c>
       <c r="D1080" t="s">
-        <v>24</v>
+        <v>228</v>
       </c>
       <c r="E1080">
         <v>2015</v>
       </c>
       <c r="F1080">
-        <v>9.6999999999999986E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="G1080">
         <v>1</v>
@@ -71628,7 +71628,7 @@
         <v>1458</v>
       </c>
       <c r="I1080">
-        <v>22.425000000000001</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1080">
         <v>0</v>
@@ -71637,7 +71637,7 @@
         <v>40</v>
       </c>
       <c r="L1080">
-        <v>0.19855392263260621</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1081" spans="2:12" x14ac:dyDescent="0.45">
@@ -71648,22 +71648,22 @@
         <v>689</v>
       </c>
       <c r="D1081" t="s">
-        <v>627</v>
+        <v>24</v>
       </c>
       <c r="E1081">
         <v>2015</v>
       </c>
       <c r="F1081">
-        <v>4.9000000000000007E-3</v>
+        <v>9.6999999999999986E-3</v>
       </c>
       <c r="G1081">
         <v>1</v>
       </c>
       <c r="H1081">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1081">
-        <v>22.424999999999997</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J1081">
         <v>0</v>
@@ -71672,7 +71672,7 @@
         <v>40</v>
       </c>
       <c r="L1081">
-        <v>0.18956968490584708</v>
+        <v>0.19855392263260621</v>
       </c>
     </row>
     <row r="1082" spans="2:12" x14ac:dyDescent="0.45">
@@ -71683,19 +71683,19 @@
         <v>689</v>
       </c>
       <c r="D1082" t="s">
-        <v>751</v>
+        <v>627</v>
       </c>
       <c r="E1082">
         <v>2015</v>
       </c>
       <c r="F1082">
-        <v>1E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1082">
         <v>1</v>
       </c>
       <c r="H1082">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1082">
         <v>22.424999999999997</v>
@@ -71707,7 +71707,7 @@
         <v>40</v>
       </c>
       <c r="L1082">
-        <v>0.17907908788454549</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1083" spans="2:12" x14ac:dyDescent="0.45">
@@ -71718,13 +71718,13 @@
         <v>689</v>
       </c>
       <c r="D1083" t="s">
-        <v>228</v>
+        <v>74</v>
       </c>
       <c r="E1083">
         <v>2015</v>
       </c>
       <c r="F1083">
-        <v>6.4000000000000003E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1083">
         <v>1</v>
@@ -71753,13 +71753,13 @@
         <v>689</v>
       </c>
       <c r="D1084" t="s">
-        <v>632</v>
+        <v>24</v>
       </c>
       <c r="E1084">
         <v>2016</v>
       </c>
       <c r="F1084">
-        <v>1E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G1084">
         <v>1</v>
@@ -71777,7 +71777,7 @@
         <v>39</v>
       </c>
       <c r="L1084">
-        <v>0.1921131304391373</v>
+        <v>0.19855392263260621</v>
       </c>
     </row>
     <row r="1085" spans="2:12" x14ac:dyDescent="0.45">
@@ -71788,13 +71788,13 @@
         <v>689</v>
       </c>
       <c r="D1085" t="s">
-        <v>24</v>
+        <v>632</v>
       </c>
       <c r="E1085">
         <v>2016</v>
       </c>
       <c r="F1085">
-        <v>1.5E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1085">
         <v>1</v>
@@ -71812,7 +71812,7 @@
         <v>39</v>
       </c>
       <c r="L1085">
-        <v>0.19855392263260621</v>
+        <v>0.1921131304391373</v>
       </c>
     </row>
     <row r="1086" spans="2:12" x14ac:dyDescent="0.45">
@@ -72471,7 +72471,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1110">
-        <v>0.38431032951329563</v>
+        <v>0.38431032951329575</v>
       </c>
     </row>
     <row r="1111" spans="2:12" x14ac:dyDescent="0.45">
@@ -72517,7 +72517,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1112">
-        <v>0.38431032951329563</v>
+        <v>0.38431032951329575</v>
       </c>
     </row>
     <row r="1113" spans="2:12" x14ac:dyDescent="0.45">
@@ -74771,7 +74771,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1210">
-        <v>0.38431032951329563</v>
+        <v>0.38431032951329575</v>
       </c>
     </row>
     <row r="1211" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FFDFB94-6239-475A-8BA6-0B780709F416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21CCE224-CF32-4B06-AA51-819E71DA9CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6353F233-48AA-46AD-8A5D-09C079A815C2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E77E27F2-C954-4054-840D-55C4190A3CF7}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5435,7 +5435,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7A3D9F7-4F76-49A1-AA9C-AB77062CB636}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E755B4C-CD8F-4EE9-9A02-11BA773B3A85}">
   <dimension ref="B9:T381"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23828,7 +23828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0F62091-0195-47BE-A8A2-90726BEE21E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B59465-898B-4D04-803F-A8E512813DC1}">
   <dimension ref="B9:T1234"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -73116,13 +73116,13 @@
         <v>750</v>
       </c>
       <c r="D1073" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="E1073">
         <v>2013</v>
       </c>
       <c r="F1073">
-        <v>3.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1073">
         <v>1</v>
@@ -73131,7 +73131,7 @@
         <v>1458</v>
       </c>
       <c r="I1073">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1073">
         <v>0</v>
@@ -73140,7 +73140,7 @@
         <v>42</v>
       </c>
       <c r="L1073">
-        <v>0.19855392263260624</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1074" spans="2:12" x14ac:dyDescent="0.45">
@@ -73151,13 +73151,13 @@
         <v>750</v>
       </c>
       <c r="D1074" t="s">
-        <v>202</v>
+        <v>24</v>
       </c>
       <c r="E1074">
         <v>2013</v>
       </c>
       <c r="F1074">
-        <v>1.9E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1074">
         <v>1</v>
@@ -73166,7 +73166,7 @@
         <v>1458</v>
       </c>
       <c r="I1074">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1074">
         <v>0</v>
@@ -73175,7 +73175,7 @@
         <v>42</v>
       </c>
       <c r="L1074">
-        <v>0.18013391841854179</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1075" spans="2:12" x14ac:dyDescent="0.45">
@@ -73256,19 +73256,19 @@
         <v>750</v>
       </c>
       <c r="D1077" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="E1077">
         <v>2014</v>
       </c>
       <c r="F1077">
-        <v>2.5000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G1077">
         <v>1</v>
       </c>
       <c r="H1077">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1077">
         <v>22.424999999999997</v>
@@ -73280,7 +73280,7 @@
         <v>41</v>
       </c>
       <c r="L1077">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260618</v>
       </c>
     </row>
     <row r="1078" spans="2:12" x14ac:dyDescent="0.45">
@@ -73291,19 +73291,19 @@
         <v>750</v>
       </c>
       <c r="D1078" t="s">
-        <v>24</v>
+        <v>259</v>
       </c>
       <c r="E1078">
         <v>2014</v>
       </c>
       <c r="F1078">
-        <v>2.7000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="G1078">
         <v>1</v>
       </c>
       <c r="H1078">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1078">
         <v>22.424999999999997</v>
@@ -73315,7 +73315,7 @@
         <v>41</v>
       </c>
       <c r="L1078">
-        <v>0.19855392263260618</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1079" spans="2:12" x14ac:dyDescent="0.45">
@@ -73326,13 +73326,13 @@
         <v>750</v>
       </c>
       <c r="D1079" t="s">
-        <v>259</v>
+        <v>74</v>
       </c>
       <c r="E1079">
         <v>2014</v>
       </c>
       <c r="F1079">
-        <v>3.8999999999999998E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1079">
         <v>1</v>
@@ -73361,19 +73361,19 @@
         <v>750</v>
       </c>
       <c r="D1080" t="s">
-        <v>815</v>
+        <v>688</v>
       </c>
       <c r="E1080">
         <v>2015</v>
       </c>
       <c r="F1080">
-        <v>1E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1080">
         <v>1</v>
       </c>
       <c r="H1080">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1080">
         <v>22.424999999999997</v>
@@ -73385,7 +73385,7 @@
         <v>40</v>
       </c>
       <c r="L1080">
-        <v>0.17907908788454549</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1081" spans="2:12" x14ac:dyDescent="0.45">
@@ -73431,22 +73431,22 @@
         <v>750</v>
       </c>
       <c r="D1082" t="s">
-        <v>688</v>
+        <v>24</v>
       </c>
       <c r="E1082">
         <v>2015</v>
       </c>
       <c r="F1082">
-        <v>4.9000000000000007E-3</v>
+        <v>9.6999999999999986E-3</v>
       </c>
       <c r="G1082">
         <v>1</v>
       </c>
       <c r="H1082">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1082">
-        <v>22.424999999999997</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J1082">
         <v>0</v>
@@ -73455,7 +73455,7 @@
         <v>40</v>
       </c>
       <c r="L1082">
-        <v>0.18956968490584708</v>
+        <v>0.19855392263260621</v>
       </c>
     </row>
     <row r="1083" spans="2:12" x14ac:dyDescent="0.45">
@@ -73501,13 +73501,13 @@
         <v>750</v>
       </c>
       <c r="D1084" t="s">
-        <v>24</v>
+        <v>815</v>
       </c>
       <c r="E1084">
         <v>2015</v>
       </c>
       <c r="F1084">
-        <v>9.6999999999999986E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1084">
         <v>1</v>
@@ -73516,7 +73516,7 @@
         <v>1458</v>
       </c>
       <c r="I1084">
-        <v>22.425000000000001</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1084">
         <v>0</v>
@@ -73525,7 +73525,7 @@
         <v>40</v>
       </c>
       <c r="L1084">
-        <v>0.19855392263260621</v>
+        <v>0.17907908788454549</v>
       </c>
     </row>
     <row r="1085" spans="2:12" x14ac:dyDescent="0.45">
@@ -74254,7 +74254,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1111">
-        <v>0.31912881156466849</v>
+        <v>0.3191288115646686</v>
       </c>
     </row>
     <row r="1112" spans="2:12" x14ac:dyDescent="0.45">
@@ -74300,7 +74300,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1113">
-        <v>0.31912881156466849</v>
+        <v>0.3191288115646686</v>
       </c>
     </row>
     <row r="1114" spans="2:12" x14ac:dyDescent="0.45">
@@ -76600,7 +76600,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1213">
-        <v>0.31912881156466849</v>
+        <v>0.3191288115646686</v>
       </c>
     </row>
     <row r="1214" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7BDF44A-F6EF-42EC-97CD-E950E90ABBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F072E721-6972-4135-BE6E-71E5CCC3E932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1C9292E4-5947-4FB1-9491-CD4082007BCC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{290FD71E-4C34-44F8-B8EC-3615A1A01D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6064,7 +6064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8358951-240F-42C5-A609-FCF7702AF18B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C7A417E-9344-48C7-8526-117490A98962}">
   <dimension ref="B9:T394"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24912,7 +24912,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AF821C6-3FAC-4B26-AC31-A25DE8FDB740}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64FA7B79-2920-4011-B05D-7B57D4214895}">
   <dimension ref="B9:T131"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31471,7 +31471,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874BE13B-656C-4781-9EE8-5B25ECD83F37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B90514A-72A4-4572-BBE1-7A930849653B}">
   <dimension ref="B9:T1244"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -68995,7 +68995,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L771">
-        <v>0.18371110025790011</v>
+        <v>0.18371110025790013</v>
       </c>
     </row>
     <row r="772" spans="2:12" x14ac:dyDescent="0.45">
@@ -69018,7 +69018,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L772">
-        <v>0.18371110025790011</v>
+        <v>0.18371110025790013</v>
       </c>
     </row>
     <row r="773" spans="2:12" x14ac:dyDescent="0.45">
@@ -69041,7 +69041,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L773">
-        <v>0.18371110025790011</v>
+        <v>0.18371110025790013</v>
       </c>
     </row>
     <row r="774" spans="2:12" x14ac:dyDescent="0.45">
@@ -80077,19 +80077,19 @@
         <v>750</v>
       </c>
       <c r="D1089" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="E1089">
         <v>2014</v>
       </c>
       <c r="F1089">
-        <v>2.7000000000000001E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1089">
         <v>1</v>
       </c>
       <c r="H1089">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1089">
         <v>22.424999999999997</v>
@@ -80101,7 +80101,7 @@
         <v>41</v>
       </c>
       <c r="L1089">
-        <v>0.19855392263260618</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1090" spans="2:12" x14ac:dyDescent="0.45">
@@ -80112,19 +80112,19 @@
         <v>750</v>
       </c>
       <c r="D1090" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E1090">
         <v>2014</v>
       </c>
       <c r="F1090">
-        <v>2.5000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G1090">
         <v>1</v>
       </c>
       <c r="H1090">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1090">
         <v>22.424999999999997</v>
@@ -80136,7 +80136,7 @@
         <v>41</v>
       </c>
       <c r="L1090">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260618</v>
       </c>
     </row>
     <row r="1091" spans="2:12" x14ac:dyDescent="0.45">
@@ -80182,13 +80182,13 @@
         <v>750</v>
       </c>
       <c r="D1092" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="E1092">
         <v>2015</v>
       </c>
       <c r="F1092">
-        <v>9.6999999999999986E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1092">
         <v>1</v>
@@ -80197,7 +80197,7 @@
         <v>1458</v>
       </c>
       <c r="I1092">
-        <v>22.425000000000001</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1092">
         <v>0</v>
@@ -80206,7 +80206,7 @@
         <v>40</v>
       </c>
       <c r="L1092">
-        <v>0.19855392263260621</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1093" spans="2:12" x14ac:dyDescent="0.45">
@@ -80217,19 +80217,19 @@
         <v>750</v>
       </c>
       <c r="D1093" t="s">
-        <v>289</v>
+        <v>702</v>
       </c>
       <c r="E1093">
         <v>2015</v>
       </c>
       <c r="F1093">
-        <v>6.4000000000000003E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1093">
         <v>1</v>
       </c>
       <c r="H1093">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1093">
         <v>22.424999999999997</v>
@@ -80241,7 +80241,7 @@
         <v>40</v>
       </c>
       <c r="L1093">
-        <v>0.1885335384832984</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1094" spans="2:12" x14ac:dyDescent="0.45">
@@ -80252,13 +80252,13 @@
         <v>750</v>
       </c>
       <c r="D1094" t="s">
-        <v>814</v>
+        <v>289</v>
       </c>
       <c r="E1094">
         <v>2015</v>
       </c>
       <c r="F1094">
-        <v>1E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="G1094">
         <v>1</v>
@@ -80276,7 +80276,7 @@
         <v>40</v>
       </c>
       <c r="L1094">
-        <v>0.17907908788454549</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1095" spans="2:12" x14ac:dyDescent="0.45">
@@ -80287,7 +80287,7 @@
         <v>750</v>
       </c>
       <c r="D1095" t="s">
-        <v>72</v>
+        <v>814</v>
       </c>
       <c r="E1095">
         <v>2015</v>
@@ -80311,7 +80311,7 @@
         <v>40</v>
       </c>
       <c r="L1095">
-        <v>0.1885335384832984</v>
+        <v>0.17907908788454549</v>
       </c>
     </row>
     <row r="1096" spans="2:12" x14ac:dyDescent="0.45">
@@ -80322,22 +80322,22 @@
         <v>750</v>
       </c>
       <c r="D1096" t="s">
-        <v>702</v>
+        <v>24</v>
       </c>
       <c r="E1096">
         <v>2015</v>
       </c>
       <c r="F1096">
-        <v>4.9000000000000007E-3</v>
+        <v>9.6999999999999986E-3</v>
       </c>
       <c r="G1096">
         <v>1</v>
       </c>
       <c r="H1096">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1096">
-        <v>22.424999999999997</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J1096">
         <v>0</v>
@@ -80346,7 +80346,7 @@
         <v>40</v>
       </c>
       <c r="L1096">
-        <v>0.18956968490584708</v>
+        <v>0.19855392263260621</v>
       </c>
     </row>
     <row r="1097" spans="2:12" x14ac:dyDescent="0.45">
@@ -80392,13 +80392,13 @@
         <v>750</v>
       </c>
       <c r="D1098" t="s">
-        <v>47</v>
+        <v>289</v>
       </c>
       <c r="E1098">
         <v>2017</v>
       </c>
       <c r="F1098">
-        <v>1.5699999999999999E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="G1098">
         <v>1</v>
@@ -80427,13 +80427,13 @@
         <v>750</v>
       </c>
       <c r="D1099" t="s">
-        <v>289</v>
+        <v>47</v>
       </c>
       <c r="E1099">
         <v>2017</v>
       </c>
       <c r="F1099">
-        <v>4.4999999999999997E-3</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="G1099">
         <v>1</v>
@@ -80649,7 +80649,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1105">
-        <v>0.41074925609602886</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1106" spans="2:12" x14ac:dyDescent="0.45">
@@ -80672,7 +80672,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1106">
-        <v>0.41074925609602886</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1107" spans="2:12" x14ac:dyDescent="0.45">
@@ -80695,7 +80695,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1107">
-        <v>0.41074925609602886</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1108" spans="2:12" x14ac:dyDescent="0.45">
@@ -85463,7 +85463,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{592BC5AC-605D-4F9D-92D5-97B3900B6795}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06889AC6-6E8A-47FC-B41A-2D752118969C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C89C6722-78DE-404D-93B6-BCBAC2E998D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F13B77FF-00C0-4F49-9895-D78A90F32345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{31AC3507-E811-429A-9CB5-3BCE2869B101}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8880F2EC-0283-4B71-9BD6-681060820DB5}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6088,7 +6088,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458714BB-069A-44CA-B768-D9D2B53E1C8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{237EEC94-FE7C-457E-8D8F-3D25C847EC86}">
   <dimension ref="B9:T394"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24936,7 +24936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8B1089-1138-4829-9EED-66B16A9AC18F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11263B7-11CA-4103-A1D7-2FD85C5FC4F8}">
   <dimension ref="B9:T131"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31495,7 +31495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6C5FC51-F303-41F6-8134-CD39812E6195}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{325A834B-5241-46CF-8A65-98615984C001}">
   <dimension ref="B9:T1244"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49986,7 +49986,7 @@
         <v>441</v>
       </c>
       <c r="P364" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q364" t="s">
         <v>894</v>
@@ -50039,7 +50039,7 @@
         <v>441</v>
       </c>
       <c r="P365" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q365" t="s">
         <v>894</v>
@@ -63751,7 +63751,7 @@
         <v>764</v>
       </c>
       <c r="P630" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q630" t="s">
         <v>894</v>
@@ -63801,7 +63801,7 @@
         <v>764</v>
       </c>
       <c r="P631" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q631" t="s">
         <v>894</v>
@@ -63951,7 +63951,7 @@
         <v>770</v>
       </c>
       <c r="P634" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q634" t="s">
         <v>894</v>
@@ -64001,7 +64001,7 @@
         <v>770</v>
       </c>
       <c r="P635" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q635" t="s">
         <v>894</v>
@@ -64651,7 +64651,7 @@
         <v>792</v>
       </c>
       <c r="P648" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q648" t="s">
         <v>894</v>
@@ -64701,7 +64701,7 @@
         <v>792</v>
       </c>
       <c r="P649" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q649" t="s">
         <v>894</v>
@@ -64751,7 +64751,7 @@
         <v>794</v>
       </c>
       <c r="P650" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q650" t="s">
         <v>894</v>
@@ -64801,7 +64801,7 @@
         <v>794</v>
       </c>
       <c r="P651" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q651" t="s">
         <v>894</v>
@@ -64901,7 +64901,7 @@
         <v>797</v>
       </c>
       <c r="P653" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q653" t="s">
         <v>894</v>
@@ -64951,7 +64951,7 @@
         <v>797</v>
       </c>
       <c r="P654" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q654" t="s">
         <v>894</v>
@@ -65101,7 +65101,7 @@
         <v>803</v>
       </c>
       <c r="P657" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q657" t="s">
         <v>894</v>
@@ -65151,7 +65151,7 @@
         <v>803</v>
       </c>
       <c r="P658" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q658" t="s">
         <v>894</v>
@@ -66359,7 +66359,7 @@
         <v>854</v>
       </c>
       <c r="P686" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q686" t="s">
         <v>894</v>
@@ -66400,7 +66400,7 @@
         <v>854</v>
       </c>
       <c r="P687" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q687" t="s">
         <v>894</v>
@@ -66687,7 +66687,7 @@
         <v>868</v>
       </c>
       <c r="P694" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q694" t="s">
         <v>894</v>
@@ -66728,7 +66728,7 @@
         <v>868</v>
       </c>
       <c r="P695" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q695" t="s">
         <v>894</v>
@@ -66851,7 +66851,7 @@
         <v>872</v>
       </c>
       <c r="P698" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q698" t="s">
         <v>894</v>
@@ -66892,7 +66892,7 @@
         <v>872</v>
       </c>
       <c r="P699" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q699" t="s">
         <v>894</v>
@@ -67145,7 +67145,7 @@
         <v>881</v>
       </c>
       <c r="P704" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q704" t="s">
         <v>894</v>
@@ -67198,7 +67198,7 @@
         <v>881</v>
       </c>
       <c r="P705" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q705" t="s">
         <v>894</v>
@@ -80311,13 +80311,13 @@
         <v>750</v>
       </c>
       <c r="D1086" t="s">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="E1086">
         <v>2013</v>
       </c>
       <c r="F1086">
-        <v>1.9E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G1086">
         <v>1</v>
@@ -80335,7 +80335,7 @@
         <v>42</v>
       </c>
       <c r="L1086">
-        <v>0.18013391841854179</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1087" spans="2:12" x14ac:dyDescent="0.45">
@@ -80346,13 +80346,13 @@
         <v>750</v>
       </c>
       <c r="D1087" t="s">
-        <v>289</v>
+        <v>202</v>
       </c>
       <c r="E1087">
         <v>2013</v>
       </c>
       <c r="F1087">
-        <v>1.4E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1087">
         <v>1</v>
@@ -80370,7 +80370,7 @@
         <v>42</v>
       </c>
       <c r="L1087">
-        <v>0.1885335384832984</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1088" spans="2:12" x14ac:dyDescent="0.45">
@@ -80416,19 +80416,19 @@
         <v>750</v>
       </c>
       <c r="D1089" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="E1089">
         <v>2014</v>
       </c>
       <c r="F1089">
-        <v>2.7000000000000001E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1089">
         <v>1</v>
       </c>
       <c r="H1089">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1089">
         <v>22.424999999999997</v>
@@ -80440,7 +80440,7 @@
         <v>41</v>
       </c>
       <c r="L1089">
-        <v>0.19855392263260618</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1090" spans="2:12" x14ac:dyDescent="0.45">
@@ -80486,19 +80486,19 @@
         <v>750</v>
       </c>
       <c r="D1091" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E1091">
         <v>2014</v>
       </c>
       <c r="F1091">
-        <v>2.5000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G1091">
         <v>1</v>
       </c>
       <c r="H1091">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1091">
         <v>22.424999999999997</v>
@@ -80510,7 +80510,7 @@
         <v>41</v>
       </c>
       <c r="L1091">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260618</v>
       </c>
     </row>
     <row r="1092" spans="2:12" x14ac:dyDescent="0.45">
@@ -80521,19 +80521,19 @@
         <v>750</v>
       </c>
       <c r="D1092" t="s">
-        <v>702</v>
+        <v>814</v>
       </c>
       <c r="E1092">
         <v>2015</v>
       </c>
       <c r="F1092">
-        <v>4.9000000000000007E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1092">
         <v>1</v>
       </c>
       <c r="H1092">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1092">
         <v>22.424999999999997</v>
@@ -80545,7 +80545,7 @@
         <v>40</v>
       </c>
       <c r="L1092">
-        <v>0.18956968490584708</v>
+        <v>0.17907908788454549</v>
       </c>
     </row>
     <row r="1093" spans="2:12" x14ac:dyDescent="0.45">
@@ -80556,13 +80556,13 @@
         <v>750</v>
       </c>
       <c r="D1093" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="E1093">
         <v>2015</v>
       </c>
       <c r="F1093">
-        <v>9.6999999999999986E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1093">
         <v>1</v>
@@ -80571,7 +80571,7 @@
         <v>1458</v>
       </c>
       <c r="I1093">
-        <v>22.425000000000001</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1093">
         <v>0</v>
@@ -80580,7 +80580,7 @@
         <v>40</v>
       </c>
       <c r="L1093">
-        <v>0.19855392263260621</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1094" spans="2:12" x14ac:dyDescent="0.45">
@@ -80591,13 +80591,13 @@
         <v>750</v>
       </c>
       <c r="D1094" t="s">
-        <v>72</v>
+        <v>289</v>
       </c>
       <c r="E1094">
         <v>2015</v>
       </c>
       <c r="F1094">
-        <v>1E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="G1094">
         <v>1</v>
@@ -80626,19 +80626,19 @@
         <v>750</v>
       </c>
       <c r="D1095" t="s">
-        <v>289</v>
+        <v>702</v>
       </c>
       <c r="E1095">
         <v>2015</v>
       </c>
       <c r="F1095">
-        <v>6.4000000000000003E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1095">
         <v>1</v>
       </c>
       <c r="H1095">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1095">
         <v>22.424999999999997</v>
@@ -80650,7 +80650,7 @@
         <v>40</v>
       </c>
       <c r="L1095">
-        <v>0.1885335384832984</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1096" spans="2:12" x14ac:dyDescent="0.45">
@@ -80661,13 +80661,13 @@
         <v>750</v>
       </c>
       <c r="D1096" t="s">
-        <v>814</v>
+        <v>24</v>
       </c>
       <c r="E1096">
         <v>2015</v>
       </c>
       <c r="F1096">
-        <v>1E-3</v>
+        <v>9.6999999999999986E-3</v>
       </c>
       <c r="G1096">
         <v>1</v>
@@ -80676,7 +80676,7 @@
         <v>1458</v>
       </c>
       <c r="I1096">
-        <v>22.424999999999997</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J1096">
         <v>0</v>
@@ -80685,7 +80685,7 @@
         <v>40</v>
       </c>
       <c r="L1096">
-        <v>0.17907908788454549</v>
+        <v>0.19855392263260621</v>
       </c>
     </row>
     <row r="1097" spans="2:12" x14ac:dyDescent="0.45">
@@ -80731,13 +80731,13 @@
         <v>750</v>
       </c>
       <c r="D1098" t="s">
-        <v>47</v>
+        <v>289</v>
       </c>
       <c r="E1098">
         <v>2017</v>
       </c>
       <c r="F1098">
-        <v>1.5699999999999999E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="G1098">
         <v>1</v>
@@ -80766,13 +80766,13 @@
         <v>750</v>
       </c>
       <c r="D1099" t="s">
-        <v>289</v>
+        <v>47</v>
       </c>
       <c r="E1099">
         <v>2017</v>
       </c>
       <c r="F1099">
-        <v>4.4999999999999997E-3</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="G1099">
         <v>1</v>
@@ -80988,7 +80988,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1105">
-        <v>0.41074925609602886</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1106" spans="2:12" x14ac:dyDescent="0.45">
@@ -81011,7 +81011,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1106">
-        <v>0.41074925609602886</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1107" spans="2:12" x14ac:dyDescent="0.45">
@@ -81034,7 +81034,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1107">
-        <v>0.41074925609602886</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1108" spans="2:12" x14ac:dyDescent="0.45">
@@ -85802,7 +85802,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F29919A4-09E2-4DE4-B5C8-16F8091AB206}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9810EC3-5990-426E-A6C3-5D2B38BBD19C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F13B77FF-00C0-4F49-9895-D78A90F32345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F90B6366-2C1C-4682-A990-F2521956A1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8880F2EC-0283-4B71-9BD6-681060820DB5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{97B85833-5E76-4E37-B942-A6161EF2532B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6088,7 +6088,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{237EEC94-FE7C-457E-8D8F-3D25C847EC86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EDD2003-0FB8-41A8-A94D-ACA4915AF0F8}">
   <dimension ref="B9:T394"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24936,7 +24936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11263B7-11CA-4103-A1D7-2FD85C5FC4F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE18E8D-0F75-494D-977E-DD92A78070F1}">
   <dimension ref="B9:T131"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31495,7 +31495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{325A834B-5241-46CF-8A65-98615984C001}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8626C060-3695-44E0-8BD2-ED3A48001D16}">
   <dimension ref="B9:T1244"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -63751,7 +63751,7 @@
         <v>764</v>
       </c>
       <c r="P630" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q630" t="s">
         <v>894</v>
@@ -63801,7 +63801,7 @@
         <v>764</v>
       </c>
       <c r="P631" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q631" t="s">
         <v>894</v>
@@ -63951,7 +63951,7 @@
         <v>770</v>
       </c>
       <c r="P634" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q634" t="s">
         <v>894</v>
@@ -64001,7 +64001,7 @@
         <v>770</v>
       </c>
       <c r="P635" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q635" t="s">
         <v>894</v>
@@ -64901,7 +64901,7 @@
         <v>797</v>
       </c>
       <c r="P653" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q653" t="s">
         <v>894</v>
@@ -64951,7 +64951,7 @@
         <v>797</v>
       </c>
       <c r="P654" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q654" t="s">
         <v>894</v>
@@ -66687,7 +66687,7 @@
         <v>868</v>
       </c>
       <c r="P694" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q694" t="s">
         <v>894</v>
@@ -66728,7 +66728,7 @@
         <v>868</v>
       </c>
       <c r="P695" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q695" t="s">
         <v>894</v>
@@ -66851,7 +66851,7 @@
         <v>872</v>
       </c>
       <c r="P698" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q698" t="s">
         <v>894</v>
@@ -66892,7 +66892,7 @@
         <v>872</v>
       </c>
       <c r="P699" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q699" t="s">
         <v>894</v>
@@ -80311,13 +80311,13 @@
         <v>750</v>
       </c>
       <c r="D1086" t="s">
-        <v>289</v>
+        <v>202</v>
       </c>
       <c r="E1086">
         <v>2013</v>
       </c>
       <c r="F1086">
-        <v>1.4E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1086">
         <v>1</v>
@@ -80335,7 +80335,7 @@
         <v>42</v>
       </c>
       <c r="L1086">
-        <v>0.1885335384832984</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1087" spans="2:12" x14ac:dyDescent="0.45">
@@ -80346,13 +80346,13 @@
         <v>750</v>
       </c>
       <c r="D1087" t="s">
-        <v>202</v>
+        <v>24</v>
       </c>
       <c r="E1087">
         <v>2013</v>
       </c>
       <c r="F1087">
-        <v>1.9E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1087">
         <v>1</v>
@@ -80361,7 +80361,7 @@
         <v>1458</v>
       </c>
       <c r="I1087">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1087">
         <v>0</v>
@@ -80370,7 +80370,7 @@
         <v>42</v>
       </c>
       <c r="L1087">
-        <v>0.18013391841854179</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1088" spans="2:12" x14ac:dyDescent="0.45">
@@ -80381,13 +80381,13 @@
         <v>750</v>
       </c>
       <c r="D1088" t="s">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="E1088">
         <v>2013</v>
       </c>
       <c r="F1088">
-        <v>3.5000000000000001E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G1088">
         <v>1</v>
@@ -80396,7 +80396,7 @@
         <v>1458</v>
       </c>
       <c r="I1088">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1088">
         <v>0</v>
@@ -80405,7 +80405,7 @@
         <v>42</v>
       </c>
       <c r="L1088">
-        <v>0.19855392263260624</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1089" spans="2:12" x14ac:dyDescent="0.45">
@@ -80416,19 +80416,19 @@
         <v>750</v>
       </c>
       <c r="D1089" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E1089">
         <v>2014</v>
       </c>
       <c r="F1089">
-        <v>2.5000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G1089">
         <v>1</v>
       </c>
       <c r="H1089">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1089">
         <v>22.424999999999997</v>
@@ -80440,7 +80440,7 @@
         <v>41</v>
       </c>
       <c r="L1089">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260618</v>
       </c>
     </row>
     <row r="1090" spans="2:12" x14ac:dyDescent="0.45">
@@ -80451,13 +80451,13 @@
         <v>750</v>
       </c>
       <c r="D1090" t="s">
-        <v>289</v>
+        <v>72</v>
       </c>
       <c r="E1090">
         <v>2014</v>
       </c>
       <c r="F1090">
-        <v>3.8999999999999998E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1090">
         <v>1</v>
@@ -80486,19 +80486,19 @@
         <v>750</v>
       </c>
       <c r="D1091" t="s">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="E1091">
         <v>2014</v>
       </c>
       <c r="F1091">
-        <v>2.7000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="G1091">
         <v>1</v>
       </c>
       <c r="H1091">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1091">
         <v>22.424999999999997</v>
@@ -80510,7 +80510,7 @@
         <v>41</v>
       </c>
       <c r="L1091">
-        <v>0.19855392263260618</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1092" spans="2:12" x14ac:dyDescent="0.45">
@@ -80521,19 +80521,19 @@
         <v>750</v>
       </c>
       <c r="D1092" t="s">
-        <v>814</v>
+        <v>702</v>
       </c>
       <c r="E1092">
         <v>2015</v>
       </c>
       <c r="F1092">
-        <v>1E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1092">
         <v>1</v>
       </c>
       <c r="H1092">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1092">
         <v>22.424999999999997</v>
@@ -80545,7 +80545,7 @@
         <v>40</v>
       </c>
       <c r="L1092">
-        <v>0.17907908788454549</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1093" spans="2:12" x14ac:dyDescent="0.45">
@@ -80626,19 +80626,19 @@
         <v>750</v>
       </c>
       <c r="D1095" t="s">
-        <v>702</v>
+        <v>814</v>
       </c>
       <c r="E1095">
         <v>2015</v>
       </c>
       <c r="F1095">
-        <v>4.9000000000000007E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1095">
         <v>1</v>
       </c>
       <c r="H1095">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1095">
         <v>22.424999999999997</v>
@@ -80650,7 +80650,7 @@
         <v>40</v>
       </c>
       <c r="L1095">
-        <v>0.18956968490584708</v>
+        <v>0.17907908788454549</v>
       </c>
     </row>
     <row r="1096" spans="2:12" x14ac:dyDescent="0.45">
@@ -80731,13 +80731,13 @@
         <v>750</v>
       </c>
       <c r="D1098" t="s">
-        <v>289</v>
+        <v>47</v>
       </c>
       <c r="E1098">
         <v>2017</v>
       </c>
       <c r="F1098">
-        <v>4.4999999999999997E-3</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="G1098">
         <v>1</v>
@@ -80766,13 +80766,13 @@
         <v>750</v>
       </c>
       <c r="D1099" t="s">
-        <v>47</v>
+        <v>289</v>
       </c>
       <c r="E1099">
         <v>2017</v>
       </c>
       <c r="F1099">
-        <v>1.5699999999999999E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="G1099">
         <v>1</v>
@@ -80988,7 +80988,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1105">
-        <v>0.4107492560960288</v>
+        <v>0.41074925609602886</v>
       </c>
     </row>
     <row r="1106" spans="2:12" x14ac:dyDescent="0.45">
@@ -81011,7 +81011,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1106">
-        <v>0.4107492560960288</v>
+        <v>0.41074925609602886</v>
       </c>
     </row>
     <row r="1107" spans="2:12" x14ac:dyDescent="0.45">
@@ -81034,7 +81034,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1107">
-        <v>0.4107492560960288</v>
+        <v>0.41074925609602886</v>
       </c>
     </row>
     <row r="1108" spans="2:12" x14ac:dyDescent="0.45">
@@ -85802,7 +85802,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9810EC3-5990-426E-A6C3-5D2B38BBD19C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A174AB95-7C88-49BB-BAC7-8A6F80920CDF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F90B6366-2C1C-4682-A990-F2521956A1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E082C4DE-2342-429E-BB71-2E34F96C76BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{97B85833-5E76-4E37-B942-A6161EF2532B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F94E194D-70AA-47A0-AEC3-0102B82CA6D5}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6088,7 +6088,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EDD2003-0FB8-41A8-A94D-ACA4915AF0F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{994E15AD-7E83-42DC-9564-5E4071E36633}">
   <dimension ref="B9:T394"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24936,7 +24936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE18E8D-0F75-494D-977E-DD92A78070F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94184D2D-2675-433F-814B-093C67AF6203}">
   <dimension ref="B9:T131"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31495,7 +31495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8626C060-3695-44E0-8BD2-ED3A48001D16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C667766-6995-4CEC-B44C-12AEAC626751}">
   <dimension ref="B9:T1244"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49986,7 +49986,7 @@
         <v>441</v>
       </c>
       <c r="P364" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q364" t="s">
         <v>894</v>
@@ -50039,7 +50039,7 @@
         <v>441</v>
       </c>
       <c r="P365" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q365" t="s">
         <v>894</v>
@@ -63951,7 +63951,7 @@
         <v>770</v>
       </c>
       <c r="P634" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q634" t="s">
         <v>894</v>
@@ -64001,7 +64001,7 @@
         <v>770</v>
       </c>
       <c r="P635" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q635" t="s">
         <v>894</v>
@@ -64751,7 +64751,7 @@
         <v>794</v>
       </c>
       <c r="P650" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q650" t="s">
         <v>894</v>
@@ -64801,7 +64801,7 @@
         <v>794</v>
       </c>
       <c r="P651" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q651" t="s">
         <v>894</v>
@@ -64901,7 +64901,7 @@
         <v>797</v>
       </c>
       <c r="P653" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q653" t="s">
         <v>894</v>
@@ -64951,7 +64951,7 @@
         <v>797</v>
       </c>
       <c r="P654" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q654" t="s">
         <v>894</v>
@@ -65101,7 +65101,7 @@
         <v>803</v>
       </c>
       <c r="P657" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q657" t="s">
         <v>894</v>
@@ -65151,7 +65151,7 @@
         <v>803</v>
       </c>
       <c r="P658" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q658" t="s">
         <v>894</v>
@@ -66277,7 +66277,7 @@
         <v>852</v>
       </c>
       <c r="P684" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q684" t="s">
         <v>894</v>
@@ -66318,7 +66318,7 @@
         <v>852</v>
       </c>
       <c r="P685" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q685" t="s">
         <v>894</v>
@@ -66359,7 +66359,7 @@
         <v>854</v>
       </c>
       <c r="P686" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q686" t="s">
         <v>894</v>
@@ -66400,7 +66400,7 @@
         <v>854</v>
       </c>
       <c r="P687" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q687" t="s">
         <v>894</v>
@@ -66687,7 +66687,7 @@
         <v>868</v>
       </c>
       <c r="P694" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q694" t="s">
         <v>894</v>
@@ -66728,7 +66728,7 @@
         <v>868</v>
       </c>
       <c r="P695" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q695" t="s">
         <v>894</v>
@@ -66851,7 +66851,7 @@
         <v>872</v>
       </c>
       <c r="P698" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q698" t="s">
         <v>894</v>
@@ -66892,7 +66892,7 @@
         <v>872</v>
       </c>
       <c r="P699" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q699" t="s">
         <v>894</v>
@@ -67145,7 +67145,7 @@
         <v>881</v>
       </c>
       <c r="P704" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q704" t="s">
         <v>894</v>
@@ -67198,7 +67198,7 @@
         <v>881</v>
       </c>
       <c r="P705" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q705" t="s">
         <v>894</v>
@@ -80311,13 +80311,13 @@
         <v>750</v>
       </c>
       <c r="D1086" t="s">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="E1086">
         <v>2013</v>
       </c>
       <c r="F1086">
-        <v>1.9E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G1086">
         <v>1</v>
@@ -80335,7 +80335,7 @@
         <v>42</v>
       </c>
       <c r="L1086">
-        <v>0.18013391841854179</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1087" spans="2:12" x14ac:dyDescent="0.45">
@@ -80346,13 +80346,13 @@
         <v>750</v>
       </c>
       <c r="D1087" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="E1087">
         <v>2013</v>
       </c>
       <c r="F1087">
-        <v>3.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1087">
         <v>1</v>
@@ -80361,7 +80361,7 @@
         <v>1458</v>
       </c>
       <c r="I1087">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1087">
         <v>0</v>
@@ -80370,7 +80370,7 @@
         <v>42</v>
       </c>
       <c r="L1087">
-        <v>0.19855392263260624</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1088" spans="2:12" x14ac:dyDescent="0.45">
@@ -80381,13 +80381,13 @@
         <v>750</v>
       </c>
       <c r="D1088" t="s">
-        <v>289</v>
+        <v>24</v>
       </c>
       <c r="E1088">
         <v>2013</v>
       </c>
       <c r="F1088">
-        <v>1.4E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1088">
         <v>1</v>
@@ -80396,7 +80396,7 @@
         <v>1458</v>
       </c>
       <c r="I1088">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1088">
         <v>0</v>
@@ -80405,7 +80405,7 @@
         <v>42</v>
       </c>
       <c r="L1088">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1089" spans="2:12" x14ac:dyDescent="0.45">
@@ -80451,13 +80451,13 @@
         <v>750</v>
       </c>
       <c r="D1090" t="s">
-        <v>72</v>
+        <v>289</v>
       </c>
       <c r="E1090">
         <v>2014</v>
       </c>
       <c r="F1090">
-        <v>2.5000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="G1090">
         <v>1</v>
@@ -80486,13 +80486,13 @@
         <v>750</v>
       </c>
       <c r="D1091" t="s">
-        <v>289</v>
+        <v>72</v>
       </c>
       <c r="E1091">
         <v>2014</v>
       </c>
       <c r="F1091">
-        <v>3.8999999999999998E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1091">
         <v>1</v>
@@ -80521,19 +80521,19 @@
         <v>750</v>
       </c>
       <c r="D1092" t="s">
-        <v>702</v>
+        <v>72</v>
       </c>
       <c r="E1092">
         <v>2015</v>
       </c>
       <c r="F1092">
-        <v>4.9000000000000007E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1092">
         <v>1</v>
       </c>
       <c r="H1092">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1092">
         <v>22.424999999999997</v>
@@ -80545,7 +80545,7 @@
         <v>40</v>
       </c>
       <c r="L1092">
-        <v>0.18956968490584708</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1093" spans="2:12" x14ac:dyDescent="0.45">
@@ -80556,13 +80556,13 @@
         <v>750</v>
       </c>
       <c r="D1093" t="s">
-        <v>72</v>
+        <v>289</v>
       </c>
       <c r="E1093">
         <v>2015</v>
       </c>
       <c r="F1093">
-        <v>1E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="G1093">
         <v>1</v>
@@ -80591,13 +80591,13 @@
         <v>750</v>
       </c>
       <c r="D1094" t="s">
-        <v>289</v>
+        <v>24</v>
       </c>
       <c r="E1094">
         <v>2015</v>
       </c>
       <c r="F1094">
-        <v>6.4000000000000003E-3</v>
+        <v>9.6999999999999986E-3</v>
       </c>
       <c r="G1094">
         <v>1</v>
@@ -80606,7 +80606,7 @@
         <v>1458</v>
       </c>
       <c r="I1094">
-        <v>22.424999999999997</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J1094">
         <v>0</v>
@@ -80615,7 +80615,7 @@
         <v>40</v>
       </c>
       <c r="L1094">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260621</v>
       </c>
     </row>
     <row r="1095" spans="2:12" x14ac:dyDescent="0.45">
@@ -80626,19 +80626,19 @@
         <v>750</v>
       </c>
       <c r="D1095" t="s">
-        <v>814</v>
+        <v>702</v>
       </c>
       <c r="E1095">
         <v>2015</v>
       </c>
       <c r="F1095">
-        <v>1E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1095">
         <v>1</v>
       </c>
       <c r="H1095">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1095">
         <v>22.424999999999997</v>
@@ -80650,7 +80650,7 @@
         <v>40</v>
       </c>
       <c r="L1095">
-        <v>0.17907908788454549</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1096" spans="2:12" x14ac:dyDescent="0.45">
@@ -80661,13 +80661,13 @@
         <v>750</v>
       </c>
       <c r="D1096" t="s">
-        <v>24</v>
+        <v>814</v>
       </c>
       <c r="E1096">
         <v>2015</v>
       </c>
       <c r="F1096">
-        <v>9.6999999999999986E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1096">
         <v>1</v>
@@ -80676,7 +80676,7 @@
         <v>1458</v>
       </c>
       <c r="I1096">
-        <v>22.425000000000001</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1096">
         <v>0</v>
@@ -80685,7 +80685,7 @@
         <v>40</v>
       </c>
       <c r="L1096">
-        <v>0.19855392263260621</v>
+        <v>0.17907908788454549</v>
       </c>
     </row>
     <row r="1097" spans="2:12" x14ac:dyDescent="0.45">
@@ -80731,13 +80731,13 @@
         <v>750</v>
       </c>
       <c r="D1098" t="s">
-        <v>47</v>
+        <v>289</v>
       </c>
       <c r="E1098">
         <v>2017</v>
       </c>
       <c r="F1098">
-        <v>1.5699999999999999E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="G1098">
         <v>1</v>
@@ -80766,13 +80766,13 @@
         <v>750</v>
       </c>
       <c r="D1099" t="s">
-        <v>289</v>
+        <v>47</v>
       </c>
       <c r="E1099">
         <v>2017</v>
       </c>
       <c r="F1099">
-        <v>4.4999999999999997E-3</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="G1099">
         <v>1</v>
@@ -81337,7 +81337,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1116">
-        <v>0.31140597495500799</v>
+        <v>0.31140597495500794</v>
       </c>
     </row>
     <row r="1117" spans="2:12" x14ac:dyDescent="0.45">
@@ -81360,7 +81360,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1117">
-        <v>0.31140597495500799</v>
+        <v>0.31140597495500794</v>
       </c>
     </row>
     <row r="1118" spans="2:12" x14ac:dyDescent="0.45">
@@ -81383,7 +81383,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1118">
-        <v>0.31140597495500799</v>
+        <v>0.31140597495500794</v>
       </c>
     </row>
     <row r="1119" spans="2:12" x14ac:dyDescent="0.45">
@@ -85802,7 +85802,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A174AB95-7C88-49BB-BAC7-8A6F80920CDF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF7CC5FA-3FBC-4A91-8DA2-D02869F9C940}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E082C4DE-2342-429E-BB71-2E34F96C76BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17DF5FA1-22B3-44F6-868E-8E40E73CE6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F94E194D-70AA-47A0-AEC3-0102B82CA6D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EE2B0D64-C74D-4A61-A988-1792A1BD321D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6088,7 +6088,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{994E15AD-7E83-42DC-9564-5E4071E36633}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21DCD99C-AE03-479D-9E69-DE0DA7D6DDCC}">
   <dimension ref="B9:T394"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24936,7 +24936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94184D2D-2675-433F-814B-093C67AF6203}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3914CE58-F5BA-4F74-B8DA-094476D5FBDE}">
   <dimension ref="B9:T131"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31495,7 +31495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C667766-6995-4CEC-B44C-12AEAC626751}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D3C0D2E-1B1D-48D9-97E3-345581A58ED1}">
   <dimension ref="B9:T1244"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -63951,7 +63951,7 @@
         <v>770</v>
       </c>
       <c r="P634" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q634" t="s">
         <v>894</v>
@@ -64001,7 +64001,7 @@
         <v>770</v>
       </c>
       <c r="P635" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q635" t="s">
         <v>894</v>
@@ -64051,7 +64051,7 @@
         <v>772</v>
       </c>
       <c r="P636" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q636" t="s">
         <v>894</v>
@@ -64101,7 +64101,7 @@
         <v>772</v>
       </c>
       <c r="P637" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q637" t="s">
         <v>894</v>
@@ -64651,7 +64651,7 @@
         <v>792</v>
       </c>
       <c r="P648" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q648" t="s">
         <v>894</v>
@@ -64701,7 +64701,7 @@
         <v>792</v>
       </c>
       <c r="P649" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q649" t="s">
         <v>894</v>
@@ -64751,7 +64751,7 @@
         <v>794</v>
       </c>
       <c r="P650" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q650" t="s">
         <v>894</v>
@@ -64801,7 +64801,7 @@
         <v>794</v>
       </c>
       <c r="P651" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q651" t="s">
         <v>894</v>
@@ -64901,7 +64901,7 @@
         <v>797</v>
       </c>
       <c r="P653" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q653" t="s">
         <v>894</v>
@@ -64951,7 +64951,7 @@
         <v>797</v>
       </c>
       <c r="P654" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q654" t="s">
         <v>894</v>
@@ -65101,7 +65101,7 @@
         <v>803</v>
       </c>
       <c r="P657" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q657" t="s">
         <v>894</v>
@@ -65151,7 +65151,7 @@
         <v>803</v>
       </c>
       <c r="P658" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q658" t="s">
         <v>894</v>
@@ -66359,7 +66359,7 @@
         <v>854</v>
       </c>
       <c r="P686" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q686" t="s">
         <v>894</v>
@@ -66400,7 +66400,7 @@
         <v>854</v>
       </c>
       <c r="P687" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q687" t="s">
         <v>894</v>
@@ -66687,7 +66687,7 @@
         <v>868</v>
       </c>
       <c r="P694" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q694" t="s">
         <v>894</v>
@@ -66728,7 +66728,7 @@
         <v>868</v>
       </c>
       <c r="P695" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q695" t="s">
         <v>894</v>
@@ -80311,13 +80311,13 @@
         <v>750</v>
       </c>
       <c r="D1086" t="s">
-        <v>289</v>
+        <v>24</v>
       </c>
       <c r="E1086">
         <v>2013</v>
       </c>
       <c r="F1086">
-        <v>1.4E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1086">
         <v>1</v>
@@ -80326,7 +80326,7 @@
         <v>1458</v>
       </c>
       <c r="I1086">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1086">
         <v>0</v>
@@ -80335,7 +80335,7 @@
         <v>42</v>
       </c>
       <c r="L1086">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1087" spans="2:12" x14ac:dyDescent="0.45">
@@ -80346,13 +80346,13 @@
         <v>750</v>
       </c>
       <c r="D1087" t="s">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="E1087">
         <v>2013</v>
       </c>
       <c r="F1087">
-        <v>1.9E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G1087">
         <v>1</v>
@@ -80370,7 +80370,7 @@
         <v>42</v>
       </c>
       <c r="L1087">
-        <v>0.18013391841854179</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1088" spans="2:12" x14ac:dyDescent="0.45">
@@ -80381,13 +80381,13 @@
         <v>750</v>
       </c>
       <c r="D1088" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="E1088">
         <v>2013</v>
       </c>
       <c r="F1088">
-        <v>3.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1088">
         <v>1</v>
@@ -80396,7 +80396,7 @@
         <v>1458</v>
       </c>
       <c r="I1088">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1088">
         <v>0</v>
@@ -80405,7 +80405,7 @@
         <v>42</v>
       </c>
       <c r="L1088">
-        <v>0.19855392263260624</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1089" spans="2:12" x14ac:dyDescent="0.45">
@@ -80416,19 +80416,19 @@
         <v>750</v>
       </c>
       <c r="D1089" t="s">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="E1089">
         <v>2014</v>
       </c>
       <c r="F1089">
-        <v>2.7000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="G1089">
         <v>1</v>
       </c>
       <c r="H1089">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1089">
         <v>22.424999999999997</v>
@@ -80440,7 +80440,7 @@
         <v>41</v>
       </c>
       <c r="L1089">
-        <v>0.19855392263260618</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1090" spans="2:12" x14ac:dyDescent="0.45">
@@ -80451,13 +80451,13 @@
         <v>750</v>
       </c>
       <c r="D1090" t="s">
-        <v>289</v>
+        <v>72</v>
       </c>
       <c r="E1090">
         <v>2014</v>
       </c>
       <c r="F1090">
-        <v>3.8999999999999998E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1090">
         <v>1</v>
@@ -80486,19 +80486,19 @@
         <v>750</v>
       </c>
       <c r="D1091" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E1091">
         <v>2014</v>
       </c>
       <c r="F1091">
-        <v>2.5000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G1091">
         <v>1</v>
       </c>
       <c r="H1091">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1091">
         <v>22.424999999999997</v>
@@ -80510,7 +80510,7 @@
         <v>41</v>
       </c>
       <c r="L1091">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260618</v>
       </c>
     </row>
     <row r="1092" spans="2:12" x14ac:dyDescent="0.45">
@@ -80521,13 +80521,13 @@
         <v>750</v>
       </c>
       <c r="D1092" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E1092">
         <v>2015</v>
       </c>
       <c r="F1092">
-        <v>1E-3</v>
+        <v>9.6999999999999986E-3</v>
       </c>
       <c r="G1092">
         <v>1</v>
@@ -80536,7 +80536,7 @@
         <v>1458</v>
       </c>
       <c r="I1092">
-        <v>22.424999999999997</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J1092">
         <v>0</v>
@@ -80545,7 +80545,7 @@
         <v>40</v>
       </c>
       <c r="L1092">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260621</v>
       </c>
     </row>
     <row r="1093" spans="2:12" x14ac:dyDescent="0.45">
@@ -80556,19 +80556,19 @@
         <v>750</v>
       </c>
       <c r="D1093" t="s">
-        <v>289</v>
+        <v>702</v>
       </c>
       <c r="E1093">
         <v>2015</v>
       </c>
       <c r="F1093">
-        <v>6.4000000000000003E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1093">
         <v>1</v>
       </c>
       <c r="H1093">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1093">
         <v>22.424999999999997</v>
@@ -80580,7 +80580,7 @@
         <v>40</v>
       </c>
       <c r="L1093">
-        <v>0.1885335384832984</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1094" spans="2:12" x14ac:dyDescent="0.45">
@@ -80591,13 +80591,13 @@
         <v>750</v>
       </c>
       <c r="D1094" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="E1094">
         <v>2015</v>
       </c>
       <c r="F1094">
-        <v>9.6999999999999986E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1094">
         <v>1</v>
@@ -80606,7 +80606,7 @@
         <v>1458</v>
       </c>
       <c r="I1094">
-        <v>22.425000000000001</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1094">
         <v>0</v>
@@ -80615,7 +80615,7 @@
         <v>40</v>
       </c>
       <c r="L1094">
-        <v>0.19855392263260621</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1095" spans="2:12" x14ac:dyDescent="0.45">
@@ -80626,19 +80626,19 @@
         <v>750</v>
       </c>
       <c r="D1095" t="s">
-        <v>702</v>
+        <v>289</v>
       </c>
       <c r="E1095">
         <v>2015</v>
       </c>
       <c r="F1095">
-        <v>4.9000000000000007E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="G1095">
         <v>1</v>
       </c>
       <c r="H1095">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1095">
         <v>22.424999999999997</v>
@@ -80650,7 +80650,7 @@
         <v>40</v>
       </c>
       <c r="L1095">
-        <v>0.18956968490584708</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1096" spans="2:12" x14ac:dyDescent="0.45">
@@ -80988,7 +80988,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1105">
-        <v>0.41074925609602886</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1106" spans="2:12" x14ac:dyDescent="0.45">
@@ -81011,7 +81011,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1106">
-        <v>0.41074925609602886</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1107" spans="2:12" x14ac:dyDescent="0.45">
@@ -81034,7 +81034,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1107">
-        <v>0.41074925609602886</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1108" spans="2:12" x14ac:dyDescent="0.45">
@@ -81337,7 +81337,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1116">
-        <v>0.31140597495500794</v>
+        <v>0.31140597495500799</v>
       </c>
     </row>
     <row r="1117" spans="2:12" x14ac:dyDescent="0.45">
@@ -81360,7 +81360,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1117">
-        <v>0.31140597495500794</v>
+        <v>0.31140597495500799</v>
       </c>
     </row>
     <row r="1118" spans="2:12" x14ac:dyDescent="0.45">
@@ -81383,7 +81383,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1118">
-        <v>0.31140597495500794</v>
+        <v>0.31140597495500799</v>
       </c>
     </row>
     <row r="1119" spans="2:12" x14ac:dyDescent="0.45">
@@ -85802,7 +85802,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF7CC5FA-3FBC-4A91-8DA2-D02869F9C940}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86F20F2-BCCA-4CD9-A5D5-6E4E1BEB1BF5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17DF5FA1-22B3-44F6-868E-8E40E73CE6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31FBB133-6F22-40B0-B8EF-3CCABE229F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EE2B0D64-C74D-4A61-A988-1792A1BD321D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D3BAD268-3BD4-42C4-9134-980460A05547}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6088,7 +6088,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21DCD99C-AE03-479D-9E69-DE0DA7D6DDCC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0BB756-AB55-405A-A58C-C1C565A2C90B}">
   <dimension ref="B9:T394"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24936,7 +24936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3914CE58-F5BA-4F74-B8DA-094476D5FBDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA8CF5F-5C66-4B38-9F0A-1DF1B11B6A33}">
   <dimension ref="B9:T131"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31495,7 +31495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D3C0D2E-1B1D-48D9-97E3-345581A58ED1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C74E6E80-4D5E-4058-8BC0-E27E89C6B4FA}">
   <dimension ref="B9:T1244"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -50304,7 +50304,7 @@
         <v>448</v>
       </c>
       <c r="P370" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q370" t="s">
         <v>894</v>
@@ -50357,7 +50357,7 @@
         <v>448</v>
       </c>
       <c r="P371" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q371" t="s">
         <v>894</v>
@@ -64751,7 +64751,7 @@
         <v>794</v>
       </c>
       <c r="P650" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q650" t="s">
         <v>894</v>
@@ -64801,7 +64801,7 @@
         <v>794</v>
       </c>
       <c r="P651" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q651" t="s">
         <v>894</v>
@@ -64901,7 +64901,7 @@
         <v>797</v>
       </c>
       <c r="P653" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q653" t="s">
         <v>894</v>
@@ -64951,7 +64951,7 @@
         <v>797</v>
       </c>
       <c r="P654" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q654" t="s">
         <v>894</v>
@@ -66359,7 +66359,7 @@
         <v>854</v>
       </c>
       <c r="P686" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q686" t="s">
         <v>894</v>
@@ -66400,7 +66400,7 @@
         <v>854</v>
       </c>
       <c r="P687" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q687" t="s">
         <v>894</v>
@@ -66687,7 +66687,7 @@
         <v>868</v>
       </c>
       <c r="P694" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q694" t="s">
         <v>894</v>
@@ -66728,7 +66728,7 @@
         <v>868</v>
       </c>
       <c r="P695" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q695" t="s">
         <v>894</v>
@@ -67145,7 +67145,7 @@
         <v>881</v>
       </c>
       <c r="P704" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="Q704" t="s">
         <v>894</v>
@@ -67198,7 +67198,7 @@
         <v>881</v>
       </c>
       <c r="P705" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q705" t="s">
         <v>894</v>
@@ -80311,13 +80311,13 @@
         <v>750</v>
       </c>
       <c r="D1086" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="E1086">
         <v>2013</v>
       </c>
       <c r="F1086">
-        <v>3.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1086">
         <v>1</v>
@@ -80326,7 +80326,7 @@
         <v>1458</v>
       </c>
       <c r="I1086">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1086">
         <v>0</v>
@@ -80335,7 +80335,7 @@
         <v>42</v>
       </c>
       <c r="L1086">
-        <v>0.19855392263260624</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1087" spans="2:12" x14ac:dyDescent="0.45">
@@ -80346,13 +80346,13 @@
         <v>750</v>
       </c>
       <c r="D1087" t="s">
-        <v>289</v>
+        <v>24</v>
       </c>
       <c r="E1087">
         <v>2013</v>
       </c>
       <c r="F1087">
-        <v>1.4E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1087">
         <v>1</v>
@@ -80361,7 +80361,7 @@
         <v>1458</v>
       </c>
       <c r="I1087">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1087">
         <v>0</v>
@@ -80370,7 +80370,7 @@
         <v>42</v>
       </c>
       <c r="L1087">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1088" spans="2:12" x14ac:dyDescent="0.45">
@@ -80381,13 +80381,13 @@
         <v>750</v>
       </c>
       <c r="D1088" t="s">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="E1088">
         <v>2013</v>
       </c>
       <c r="F1088">
-        <v>1.9E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G1088">
         <v>1</v>
@@ -80405,7 +80405,7 @@
         <v>42</v>
       </c>
       <c r="L1088">
-        <v>0.18013391841854179</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1089" spans="2:12" x14ac:dyDescent="0.45">
@@ -80416,19 +80416,19 @@
         <v>750</v>
       </c>
       <c r="D1089" t="s">
-        <v>289</v>
+        <v>24</v>
       </c>
       <c r="E1089">
         <v>2014</v>
       </c>
       <c r="F1089">
-        <v>3.8999999999999998E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G1089">
         <v>1</v>
       </c>
       <c r="H1089">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1089">
         <v>22.424999999999997</v>
@@ -80440,7 +80440,7 @@
         <v>41</v>
       </c>
       <c r="L1089">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260618</v>
       </c>
     </row>
     <row r="1090" spans="2:12" x14ac:dyDescent="0.45">
@@ -80486,19 +80486,19 @@
         <v>750</v>
       </c>
       <c r="D1091" t="s">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="E1091">
         <v>2014</v>
       </c>
       <c r="F1091">
-        <v>2.7000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="G1091">
         <v>1</v>
       </c>
       <c r="H1091">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1091">
         <v>22.424999999999997</v>
@@ -80510,7 +80510,7 @@
         <v>41</v>
       </c>
       <c r="L1091">
-        <v>0.19855392263260618</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1092" spans="2:12" x14ac:dyDescent="0.45">
@@ -80521,13 +80521,13 @@
         <v>750</v>
       </c>
       <c r="D1092" t="s">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="E1092">
         <v>2015</v>
       </c>
       <c r="F1092">
-        <v>9.6999999999999986E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="G1092">
         <v>1</v>
@@ -80536,7 +80536,7 @@
         <v>1458</v>
       </c>
       <c r="I1092">
-        <v>22.425000000000001</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1092">
         <v>0</v>
@@ -80545,7 +80545,7 @@
         <v>40</v>
       </c>
       <c r="L1092">
-        <v>0.19855392263260621</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1093" spans="2:12" x14ac:dyDescent="0.45">
@@ -80556,19 +80556,19 @@
         <v>750</v>
       </c>
       <c r="D1093" t="s">
-        <v>702</v>
+        <v>72</v>
       </c>
       <c r="E1093">
         <v>2015</v>
       </c>
       <c r="F1093">
-        <v>4.9000000000000007E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1093">
         <v>1</v>
       </c>
       <c r="H1093">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1093">
         <v>22.424999999999997</v>
@@ -80580,7 +80580,7 @@
         <v>40</v>
       </c>
       <c r="L1093">
-        <v>0.18956968490584708</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1094" spans="2:12" x14ac:dyDescent="0.45">
@@ -80591,7 +80591,7 @@
         <v>750</v>
       </c>
       <c r="D1094" t="s">
-        <v>72</v>
+        <v>814</v>
       </c>
       <c r="E1094">
         <v>2015</v>
@@ -80615,7 +80615,7 @@
         <v>40</v>
       </c>
       <c r="L1094">
-        <v>0.1885335384832984</v>
+        <v>0.17907908788454549</v>
       </c>
     </row>
     <row r="1095" spans="2:12" x14ac:dyDescent="0.45">
@@ -80626,19 +80626,19 @@
         <v>750</v>
       </c>
       <c r="D1095" t="s">
-        <v>289</v>
+        <v>702</v>
       </c>
       <c r="E1095">
         <v>2015</v>
       </c>
       <c r="F1095">
-        <v>6.4000000000000003E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1095">
         <v>1</v>
       </c>
       <c r="H1095">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1095">
         <v>22.424999999999997</v>
@@ -80650,7 +80650,7 @@
         <v>40</v>
       </c>
       <c r="L1095">
-        <v>0.1885335384832984</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1096" spans="2:12" x14ac:dyDescent="0.45">
@@ -80661,13 +80661,13 @@
         <v>750</v>
       </c>
       <c r="D1096" t="s">
-        <v>814</v>
+        <v>24</v>
       </c>
       <c r="E1096">
         <v>2015</v>
       </c>
       <c r="F1096">
-        <v>1E-3</v>
+        <v>9.6999999999999986E-3</v>
       </c>
       <c r="G1096">
         <v>1</v>
@@ -80676,7 +80676,7 @@
         <v>1458</v>
       </c>
       <c r="I1096">
-        <v>22.424999999999997</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J1096">
         <v>0</v>
@@ -80685,7 +80685,7 @@
         <v>40</v>
       </c>
       <c r="L1096">
-        <v>0.17907908788454549</v>
+        <v>0.19855392263260621</v>
       </c>
     </row>
     <row r="1097" spans="2:12" x14ac:dyDescent="0.45">
@@ -80731,13 +80731,13 @@
         <v>750</v>
       </c>
       <c r="D1098" t="s">
-        <v>289</v>
+        <v>47</v>
       </c>
       <c r="E1098">
         <v>2017</v>
       </c>
       <c r="F1098">
-        <v>4.4999999999999997E-3</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="G1098">
         <v>1</v>
@@ -80766,13 +80766,13 @@
         <v>750</v>
       </c>
       <c r="D1099" t="s">
-        <v>47</v>
+        <v>289</v>
       </c>
       <c r="E1099">
         <v>2017</v>
       </c>
       <c r="F1099">
-        <v>1.5699999999999999E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="G1099">
         <v>1</v>
@@ -85802,7 +85802,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86F20F2-BCCA-4CD9-A5D5-6E4E1BEB1BF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8163EB81-21FB-4C05-AD63-11537AB244A6}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0267DD9-0510-45C2-A65E-7C75E3D58A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8577A582-588A-488E-9142-925727DA0F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A16EA498-E98A-462B-A1C3-2CE515E7A6C0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E8924006-6DFA-4995-8FC6-5F1D69E21EE6}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6133,7 +6133,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B833A0E5-9CE1-415B-B27D-6A22A4B36A5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77CEDEDB-47C0-4BB5-960D-616021BC667D}">
   <dimension ref="B9:T277"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21159,7 +21159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08C09853-76E7-4B47-8F9E-C1BA112D631F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034B8B46-819F-4CBF-AE64-BD42C6DA1BCA}">
   <dimension ref="B9:T131"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27718,7 +27718,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23C332A4-459A-4A41-B6DC-22C97F576E98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CB2FC5C-C816-47DE-BC7C-E31A14F9E0C7}">
   <dimension ref="B9:T1230"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46209,7 +46209,7 @@
         <v>441</v>
       </c>
       <c r="P364" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="Q364" t="s">
         <v>896</v>
@@ -46262,7 +46262,7 @@
         <v>441</v>
       </c>
       <c r="P365" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="Q365" t="s">
         <v>896</v>
@@ -61224,7 +61224,7 @@
         <v>802</v>
       </c>
       <c r="P655" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="Q655" t="s">
         <v>896</v>
@@ -61274,7 +61274,7 @@
         <v>802</v>
       </c>
       <c r="P656" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="Q656" t="s">
         <v>896</v>
@@ -63368,7 +63368,7 @@
         <v>883</v>
       </c>
       <c r="P704" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="Q704" t="s">
         <v>896</v>
@@ -63421,7 +63421,7 @@
         <v>883</v>
       </c>
       <c r="P705" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="Q705" t="s">
         <v>896</v>
@@ -65557,7 +65557,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L771">
-        <v>0.18336292113835728</v>
+        <v>0.18336292113835725</v>
       </c>
     </row>
     <row r="772" spans="2:12" x14ac:dyDescent="0.45">
@@ -65580,7 +65580,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L772">
-        <v>0.18336292113835728</v>
+        <v>0.18336292113835725</v>
       </c>
     </row>
     <row r="773" spans="2:12" x14ac:dyDescent="0.45">
@@ -65603,7 +65603,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L773">
-        <v>0.18336292113835728</v>
+        <v>0.18336292113835725</v>
       </c>
     </row>
     <row r="774" spans="2:12" x14ac:dyDescent="0.45">
@@ -76044,13 +76044,13 @@
         <v>750</v>
       </c>
       <c r="D1072" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="E1072">
         <v>2013</v>
       </c>
       <c r="F1072">
-        <v>3.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1072">
         <v>1</v>
@@ -76059,7 +76059,7 @@
         <v>1458</v>
       </c>
       <c r="I1072">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1072">
         <v>0</v>
@@ -76068,7 +76068,7 @@
         <v>42</v>
       </c>
       <c r="L1072">
-        <v>0.19855392263260624</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1073" spans="2:12" x14ac:dyDescent="0.45">
@@ -76079,13 +76079,13 @@
         <v>750</v>
       </c>
       <c r="D1073" t="s">
-        <v>202</v>
+        <v>24</v>
       </c>
       <c r="E1073">
         <v>2013</v>
       </c>
       <c r="F1073">
-        <v>1.9E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1073">
         <v>1</v>
@@ -76094,7 +76094,7 @@
         <v>1458</v>
       </c>
       <c r="I1073">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1073">
         <v>0</v>
@@ -76103,7 +76103,7 @@
         <v>42</v>
       </c>
       <c r="L1073">
-        <v>0.18013391841854179</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1074" spans="2:12" x14ac:dyDescent="0.45">
@@ -76219,19 +76219,19 @@
         <v>750</v>
       </c>
       <c r="D1077" t="s">
-        <v>702</v>
+        <v>72</v>
       </c>
       <c r="E1077">
         <v>2015</v>
       </c>
       <c r="F1077">
-        <v>4.9000000000000007E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1077">
         <v>1</v>
       </c>
       <c r="H1077">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1077">
         <v>22.424999999999997</v>
@@ -76243,7 +76243,7 @@
         <v>40</v>
       </c>
       <c r="L1077">
-        <v>0.18956968490584708</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1078" spans="2:12" x14ac:dyDescent="0.45">
@@ -76254,13 +76254,13 @@
         <v>750</v>
       </c>
       <c r="D1078" t="s">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="E1078">
         <v>2015</v>
       </c>
       <c r="F1078">
-        <v>9.6999999999999986E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="G1078">
         <v>1</v>
@@ -76269,7 +76269,7 @@
         <v>1458</v>
       </c>
       <c r="I1078">
-        <v>22.425000000000001</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1078">
         <v>0</v>
@@ -76278,7 +76278,7 @@
         <v>40</v>
       </c>
       <c r="L1078">
-        <v>0.19855392263260621</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1079" spans="2:12" x14ac:dyDescent="0.45">
@@ -76324,13 +76324,13 @@
         <v>750</v>
       </c>
       <c r="D1080" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E1080">
         <v>2015</v>
       </c>
       <c r="F1080">
-        <v>1E-3</v>
+        <v>9.6999999999999986E-3</v>
       </c>
       <c r="G1080">
         <v>1</v>
@@ -76339,7 +76339,7 @@
         <v>1458</v>
       </c>
       <c r="I1080">
-        <v>22.424999999999997</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J1080">
         <v>0</v>
@@ -76348,7 +76348,7 @@
         <v>40</v>
       </c>
       <c r="L1080">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260621</v>
       </c>
     </row>
     <row r="1081" spans="2:12" x14ac:dyDescent="0.45">
@@ -76359,19 +76359,19 @@
         <v>750</v>
       </c>
       <c r="D1081" t="s">
-        <v>289</v>
+        <v>702</v>
       </c>
       <c r="E1081">
         <v>2015</v>
       </c>
       <c r="F1081">
-        <v>6.4000000000000003E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1081">
         <v>1</v>
       </c>
       <c r="H1081">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1081">
         <v>22.424999999999997</v>
@@ -76383,7 +76383,7 @@
         <v>40</v>
       </c>
       <c r="L1081">
-        <v>0.1885335384832984</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1082" spans="2:12" x14ac:dyDescent="0.45">
@@ -76429,13 +76429,13 @@
         <v>750</v>
       </c>
       <c r="D1083" t="s">
-        <v>289</v>
+        <v>47</v>
       </c>
       <c r="E1083">
         <v>2017</v>
       </c>
       <c r="F1083">
-        <v>4.4999999999999997E-3</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="G1083">
         <v>1</v>
@@ -76464,13 +76464,13 @@
         <v>750</v>
       </c>
       <c r="D1084" t="s">
-        <v>47</v>
+        <v>289</v>
       </c>
       <c r="E1084">
         <v>2017</v>
       </c>
       <c r="F1084">
-        <v>1.5699999999999999E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="G1084">
         <v>1</v>
@@ -81535,7 +81535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9625DE8-6B1A-4A12-A7A6-E2B46D4403B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A7C2A36-E3CA-4253-A7C3-A0C83C3A52D9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8577A582-588A-488E-9142-925727DA0F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{611F243B-8FD4-464E-B80E-7B45015325B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E8924006-6DFA-4995-8FC6-5F1D69E21EE6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3E454AB4-8CB3-4F01-B41C-26B1799759C2}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6133,7 +6133,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77CEDEDB-47C0-4BB5-960D-616021BC667D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1878F398-E91E-4E25-A5DB-258824C3284A}">
   <dimension ref="B9:T277"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21159,7 +21159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034B8B46-819F-4CBF-AE64-BD42C6DA1BCA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42BEDF7A-F9ED-4DF2-B572-D39564740540}">
   <dimension ref="B9:T131"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27718,7 +27718,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CB2FC5C-C816-47DE-BC7C-E31A14F9E0C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E988F0BF-7489-4693-871E-8219F3CD8334}">
   <dimension ref="B9:T1230"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46209,7 +46209,7 @@
         <v>441</v>
       </c>
       <c r="P364" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="Q364" t="s">
         <v>896</v>
@@ -46262,7 +46262,7 @@
         <v>441</v>
       </c>
       <c r="P365" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="Q365" t="s">
         <v>896</v>
@@ -60224,7 +60224,7 @@
         <v>774</v>
       </c>
       <c r="P635" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="Q635" t="s">
         <v>896</v>
@@ -60274,7 +60274,7 @@
         <v>774</v>
       </c>
       <c r="P636" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="Q636" t="s">
         <v>896</v>
@@ -60574,7 +60574,7 @@
         <v>783</v>
       </c>
       <c r="P642" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="Q642" t="s">
         <v>896</v>
@@ -60624,7 +60624,7 @@
         <v>783</v>
       </c>
       <c r="P643" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="Q643" t="s">
         <v>896</v>
@@ -63074,7 +63074,7 @@
         <v>875</v>
       </c>
       <c r="P698" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="Q698" t="s">
         <v>896</v>
@@ -63115,7 +63115,7 @@
         <v>875</v>
       </c>
       <c r="P699" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="Q699" t="s">
         <v>896</v>
@@ -63262,7 +63262,7 @@
         <v>881</v>
       </c>
       <c r="P702" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="Q702" t="s">
         <v>896</v>
@@ -63315,7 +63315,7 @@
         <v>881</v>
       </c>
       <c r="P703" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="Q703" t="s">
         <v>896</v>
@@ -63368,7 +63368,7 @@
         <v>883</v>
       </c>
       <c r="P704" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="Q704" t="s">
         <v>896</v>
@@ -63421,7 +63421,7 @@
         <v>883</v>
       </c>
       <c r="P705" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="Q705" t="s">
         <v>896</v>
@@ -65557,7 +65557,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L771">
-        <v>0.18336292113835725</v>
+        <v>0.18336292113835728</v>
       </c>
     </row>
     <row r="772" spans="2:12" x14ac:dyDescent="0.45">
@@ -65580,7 +65580,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L772">
-        <v>0.18336292113835725</v>
+        <v>0.18336292113835728</v>
       </c>
     </row>
     <row r="773" spans="2:12" x14ac:dyDescent="0.45">
@@ -65603,7 +65603,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L773">
-        <v>0.18336292113835725</v>
+        <v>0.18336292113835728</v>
       </c>
     </row>
     <row r="774" spans="2:12" x14ac:dyDescent="0.45">
@@ -76044,13 +76044,13 @@
         <v>750</v>
       </c>
       <c r="D1072" t="s">
-        <v>202</v>
+        <v>24</v>
       </c>
       <c r="E1072">
         <v>2013</v>
       </c>
       <c r="F1072">
-        <v>1.9E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1072">
         <v>1</v>
@@ -76059,7 +76059,7 @@
         <v>1458</v>
       </c>
       <c r="I1072">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1072">
         <v>0</v>
@@ -76068,7 +76068,7 @@
         <v>42</v>
       </c>
       <c r="L1072">
-        <v>0.18013391841854179</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1073" spans="2:12" x14ac:dyDescent="0.45">
@@ -76079,13 +76079,13 @@
         <v>750</v>
       </c>
       <c r="D1073" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="E1073">
         <v>2013</v>
       </c>
       <c r="F1073">
-        <v>3.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1073">
         <v>1</v>
@@ -76094,7 +76094,7 @@
         <v>1458</v>
       </c>
       <c r="I1073">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1073">
         <v>0</v>
@@ -76103,7 +76103,7 @@
         <v>42</v>
       </c>
       <c r="L1073">
-        <v>0.19855392263260624</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1074" spans="2:12" x14ac:dyDescent="0.45">
@@ -76114,19 +76114,19 @@
         <v>750</v>
       </c>
       <c r="D1074" t="s">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="E1074">
         <v>2014</v>
       </c>
       <c r="F1074">
-        <v>2.7000000000000001E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="G1074">
         <v>1</v>
       </c>
       <c r="H1074">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1074">
         <v>22.424999999999997</v>
@@ -76138,7 +76138,7 @@
         <v>41</v>
       </c>
       <c r="L1074">
-        <v>0.19855392263260618</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1075" spans="2:12" x14ac:dyDescent="0.45">
@@ -76149,19 +76149,19 @@
         <v>750</v>
       </c>
       <c r="D1075" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E1075">
         <v>2014</v>
       </c>
       <c r="F1075">
-        <v>2.5000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G1075">
         <v>1</v>
       </c>
       <c r="H1075">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1075">
         <v>22.424999999999997</v>
@@ -76173,7 +76173,7 @@
         <v>41</v>
       </c>
       <c r="L1075">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260618</v>
       </c>
     </row>
     <row r="1076" spans="2:12" x14ac:dyDescent="0.45">
@@ -76184,13 +76184,13 @@
         <v>750</v>
       </c>
       <c r="D1076" t="s">
-        <v>289</v>
+        <v>72</v>
       </c>
       <c r="E1076">
         <v>2014</v>
       </c>
       <c r="F1076">
-        <v>3.8999999999999998E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1076">
         <v>1</v>
@@ -76219,19 +76219,19 @@
         <v>750</v>
       </c>
       <c r="D1077" t="s">
-        <v>72</v>
+        <v>702</v>
       </c>
       <c r="E1077">
         <v>2015</v>
       </c>
       <c r="F1077">
-        <v>1E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1077">
         <v>1</v>
       </c>
       <c r="H1077">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1077">
         <v>22.424999999999997</v>
@@ -76243,7 +76243,7 @@
         <v>40</v>
       </c>
       <c r="L1077">
-        <v>0.1885335384832984</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1078" spans="2:12" x14ac:dyDescent="0.45">
@@ -76254,13 +76254,13 @@
         <v>750</v>
       </c>
       <c r="D1078" t="s">
-        <v>289</v>
+        <v>814</v>
       </c>
       <c r="E1078">
         <v>2015</v>
       </c>
       <c r="F1078">
-        <v>6.4000000000000003E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1078">
         <v>1</v>
@@ -76278,7 +76278,7 @@
         <v>40</v>
       </c>
       <c r="L1078">
-        <v>0.1885335384832984</v>
+        <v>0.17907908788454549</v>
       </c>
     </row>
     <row r="1079" spans="2:12" x14ac:dyDescent="0.45">
@@ -76289,7 +76289,7 @@
         <v>750</v>
       </c>
       <c r="D1079" t="s">
-        <v>814</v>
+        <v>72</v>
       </c>
       <c r="E1079">
         <v>2015</v>
@@ -76313,7 +76313,7 @@
         <v>40</v>
       </c>
       <c r="L1079">
-        <v>0.17907908788454549</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1080" spans="2:12" x14ac:dyDescent="0.45">
@@ -76359,19 +76359,19 @@
         <v>750</v>
       </c>
       <c r="D1081" t="s">
-        <v>702</v>
+        <v>289</v>
       </c>
       <c r="E1081">
         <v>2015</v>
       </c>
       <c r="F1081">
-        <v>4.9000000000000007E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="G1081">
         <v>1</v>
       </c>
       <c r="H1081">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1081">
         <v>22.424999999999997</v>
@@ -76383,7 +76383,7 @@
         <v>40</v>
       </c>
       <c r="L1081">
-        <v>0.18956968490584708</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1082" spans="2:12" x14ac:dyDescent="0.45">
@@ -76429,13 +76429,13 @@
         <v>750</v>
       </c>
       <c r="D1083" t="s">
-        <v>47</v>
+        <v>289</v>
       </c>
       <c r="E1083">
         <v>2017</v>
       </c>
       <c r="F1083">
-        <v>1.5699999999999999E-2</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="G1083">
         <v>1</v>
@@ -76464,13 +76464,13 @@
         <v>750</v>
       </c>
       <c r="D1084" t="s">
-        <v>289</v>
+        <v>47</v>
       </c>
       <c r="E1084">
         <v>2017</v>
       </c>
       <c r="F1084">
-        <v>4.4999999999999997E-3</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="G1084">
         <v>1</v>
@@ -76686,7 +76686,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1090">
-        <v>0.41074925609602886</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1091" spans="2:12" x14ac:dyDescent="0.45">
@@ -76709,7 +76709,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1091">
-        <v>0.41074925609602886</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1092" spans="2:12" x14ac:dyDescent="0.45">
@@ -76732,7 +76732,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1092">
-        <v>0.41074925609602886</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1093" spans="2:12" x14ac:dyDescent="0.45">
@@ -81535,7 +81535,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A7C2A36-E3CA-4253-A7C3-A0C83C3A52D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C13EEB-912C-471F-B160-6FAC582DF935}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33A67DBF-3E7C-449B-9FB7-E373D36CE957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D0FA0F7-4985-4A3F-B788-EACC89F98B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{90DC8FEA-8B49-40C4-9455-A7D5D382E2D0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3E0A691E-83EC-4B9B-9BA9-D81945F3C1DF}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4172,7 +4172,7 @@
     <t>en_pc_solar_pv_007</t>
   </si>
   <si>
-    <t>en_pc_solar_pv_009</t>
+    <t>en_pc_solar_pv_011</t>
   </si>
   <si>
     <t>en_pc_solar_pv_021</t>
@@ -6124,7 +6124,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10DAB0E-81C1-4D1A-A5AE-24585D6EFDD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFC8AFD4-C1F9-4051-AF35-088CCAE1D095}">
   <dimension ref="B9:T277"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21150,7 +21150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29DBC11-AF1B-46B6-AC05-21EAC8DEFEC4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E721759F-733E-4E16-8CD0-69019926E79D}">
   <dimension ref="B9:T131"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25778,7 +25778,7 @@
         <v>750</v>
       </c>
       <c r="D94" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="E94">
         <v>2025</v>
@@ -25802,7 +25802,7 @@
         <v>30</v>
       </c>
       <c r="L94">
-        <v>0.19067081479710349</v>
+        <v>0.19008013066509069</v>
       </c>
       <c r="N94" t="s">
         <v>891</v>
@@ -25834,7 +25834,7 @@
         <v>750</v>
       </c>
       <c r="D95" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="E95">
         <v>2026</v>
@@ -25858,7 +25858,7 @@
         <v>30</v>
       </c>
       <c r="L95">
-        <v>0.19067081479710349</v>
+        <v>0.19008013066509069</v>
       </c>
       <c r="N95" t="s">
         <v>891</v>
@@ -27709,7 +27709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12601DDA-A0F0-4683-9EE7-66E712D24138}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA43B82-6072-4C3A-8590-CB03DAC34057}">
   <dimension ref="B9:T1235"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46518,7 +46518,7 @@
         <v>448</v>
       </c>
       <c r="P370" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="Q370" t="s">
         <v>893</v>
@@ -46571,7 +46571,7 @@
         <v>448</v>
       </c>
       <c r="P371" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="Q371" t="s">
         <v>893</v>
@@ -59965,7 +59965,7 @@
         <v>764</v>
       </c>
       <c r="P630" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="Q630" t="s">
         <v>893</v>
@@ -60015,7 +60015,7 @@
         <v>764</v>
       </c>
       <c r="P631" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="Q631" t="s">
         <v>893</v>
@@ -62409,7 +62409,7 @@
         <v>850</v>
       </c>
       <c r="P682" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="Q682" t="s">
         <v>893</v>
@@ -62450,7 +62450,7 @@
         <v>850</v>
       </c>
       <c r="P683" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="Q683" t="s">
         <v>893</v>
@@ -62901,7 +62901,7 @@
         <v>868</v>
       </c>
       <c r="P694" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="Q694" t="s">
         <v>893</v>
@@ -62942,7 +62942,7 @@
         <v>868</v>
       </c>
       <c r="P695" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="Q695" t="s">
         <v>893</v>
@@ -65527,7 +65527,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L771">
-        <v>0.18320255283232129</v>
+        <v>0.18316422679765962</v>
       </c>
     </row>
     <row r="772" spans="2:12" x14ac:dyDescent="0.45">
@@ -65550,7 +65550,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L772">
-        <v>0.18320255283232129</v>
+        <v>0.18316422679765962</v>
       </c>
     </row>
     <row r="773" spans="2:12" x14ac:dyDescent="0.45">
@@ -65573,7 +65573,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L773">
-        <v>0.18320255283232129</v>
+        <v>0.18316422679765962</v>
       </c>
     </row>
     <row r="774" spans="2:12" x14ac:dyDescent="0.45">
@@ -68040,16 +68040,16 @@
         <v>2013</v>
       </c>
       <c r="F844">
-        <v>4.5700000000000011E-2</v>
+        <v>1.09E-2</v>
       </c>
       <c r="G844">
         <v>1</v>
       </c>
       <c r="H844">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I844">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J844">
         <v>0</v>
@@ -68058,7 +68058,7 @@
         <v>42</v>
       </c>
       <c r="L844">
-        <v>0.18972426857005958</v>
+        <v>0.18550629799122259</v>
       </c>
     </row>
     <row r="845" spans="2:12" x14ac:dyDescent="0.45">
@@ -68075,16 +68075,16 @@
         <v>2014</v>
       </c>
       <c r="F845">
-        <v>0.10339999999999999</v>
+        <v>2.2699999999999998E-2</v>
       </c>
       <c r="G845">
         <v>1</v>
       </c>
       <c r="H845">
-        <v>1458</v>
+        <v>1458.0000000000002</v>
       </c>
       <c r="I845">
-        <v>22.424999999999986</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J845">
         <v>0</v>
@@ -68093,7 +68093,7 @@
         <v>41</v>
       </c>
       <c r="L845">
-        <v>0.18972426857005975</v>
+        <v>0.18550629799122262</v>
       </c>
     </row>
     <row r="846" spans="2:12" x14ac:dyDescent="0.45">
@@ -68110,16 +68110,16 @@
         <v>2015</v>
       </c>
       <c r="F846">
-        <v>0.16430000000000006</v>
+        <v>7.0699999999999985E-2</v>
       </c>
       <c r="G846">
         <v>1</v>
       </c>
       <c r="H846">
-        <v>1457.9999999999995</v>
+        <v>1458.0000000000002</v>
       </c>
       <c r="I846">
-        <v>22.424999999999986</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J846">
         <v>0</v>
@@ -68128,7 +68128,7 @@
         <v>40</v>
       </c>
       <c r="L846">
-        <v>0.18972426857005975</v>
+        <v>0.18550629799122267</v>
       </c>
     </row>
     <row r="847" spans="2:12" x14ac:dyDescent="0.45">
@@ -68145,16 +68145,16 @@
         <v>2016</v>
       </c>
       <c r="F847">
-        <v>0.11509999999999998</v>
+        <v>1.6400000000000001E-2</v>
       </c>
       <c r="G847">
         <v>1</v>
       </c>
       <c r="H847">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I847">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J847">
         <v>0</v>
@@ -68163,7 +68163,7 @@
         <v>39</v>
       </c>
       <c r="L847">
-        <v>0.18972426857005978</v>
+        <v>0.18550629799122256</v>
       </c>
     </row>
     <row r="848" spans="2:12" x14ac:dyDescent="0.45">
@@ -68180,7 +68180,7 @@
         <v>2017</v>
       </c>
       <c r="F848">
-        <v>9.0499999999999997E-2</v>
+        <v>6.0600000000000001E-2</v>
       </c>
       <c r="G848">
         <v>1</v>
@@ -68189,7 +68189,7 @@
         <v>1458</v>
       </c>
       <c r="I848">
-        <v>22.42499999999999</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J848">
         <v>0</v>
@@ -68198,7 +68198,7 @@
         <v>38</v>
       </c>
       <c r="L848">
-        <v>0.18972426857005975</v>
+        <v>0.18550629799122262</v>
       </c>
     </row>
     <row r="849" spans="2:12" x14ac:dyDescent="0.45">
@@ -68215,16 +68215,16 @@
         <v>2018</v>
       </c>
       <c r="F849">
-        <v>0.12670000000000001</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="G849">
         <v>1</v>
       </c>
       <c r="H849">
-        <v>1294.3378058405683</v>
+        <v>1458</v>
       </c>
       <c r="I849">
-        <v>19.810951065509069</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J849">
         <v>0</v>
@@ -68233,7 +68233,7 @@
         <v>37</v>
       </c>
       <c r="L849">
-        <v>0.18972426857005972</v>
+        <v>0.18550629799122256</v>
       </c>
     </row>
     <row r="850" spans="2:12" x14ac:dyDescent="0.45">
@@ -68250,16 +68250,16 @@
         <v>2019</v>
       </c>
       <c r="F850">
-        <v>5.3999999999999999E-2</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="G850">
         <v>1</v>
       </c>
       <c r="H850">
-        <v>1458</v>
+        <v>1458.0000000000002</v>
       </c>
       <c r="I850">
-        <v>22.424999999999997</v>
+        <v>22.425000000000004</v>
       </c>
       <c r="J850">
         <v>0</v>
@@ -68268,7 +68268,7 @@
         <v>36</v>
       </c>
       <c r="L850">
-        <v>0.18972426857005967</v>
+        <v>0.18550629799122259</v>
       </c>
     </row>
     <row r="851" spans="2:12" x14ac:dyDescent="0.45">
@@ -68285,7 +68285,7 @@
         <v>2020</v>
       </c>
       <c r="F851">
-        <v>6.7600000000000007E-2</v>
+        <v>4.6899999999999997E-2</v>
       </c>
       <c r="G851">
         <v>1</v>
@@ -68294,7 +68294,7 @@
         <v>1458</v>
       </c>
       <c r="I851">
-        <v>22.424999999999997</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J851">
         <v>0</v>
@@ -68303,7 +68303,7 @@
         <v>35</v>
       </c>
       <c r="L851">
-        <v>0.18972426857005961</v>
+        <v>0.18550629799122259</v>
       </c>
     </row>
     <row r="852" spans="2:12" x14ac:dyDescent="0.45">
@@ -68320,16 +68320,16 @@
         <v>2021</v>
       </c>
       <c r="F852">
-        <v>0.15260000000000001</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="G852">
         <v>1</v>
       </c>
       <c r="H852">
-        <v>1316.453473132372</v>
+        <v>1458</v>
       </c>
       <c r="I852">
-        <v>20.164187418086495</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J852">
         <v>0</v>
@@ -68338,7 +68338,7 @@
         <v>34</v>
       </c>
       <c r="L852">
-        <v>0.1897242685700597</v>
+        <v>0.18550629799122262</v>
       </c>
     </row>
     <row r="853" spans="2:12" x14ac:dyDescent="0.45">
@@ -68355,16 +68355,16 @@
         <v>2022</v>
       </c>
       <c r="F853">
-        <v>0.12540000000000001</v>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="G853">
         <v>1</v>
       </c>
       <c r="H853">
-        <v>1364.9856459330144</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I853">
-        <v>20.93935406698564</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J853">
         <v>0</v>
@@ -68373,7 +68373,7 @@
         <v>33</v>
       </c>
       <c r="L853">
-        <v>0.18972426857005975</v>
+        <v>0.18550629799122256</v>
       </c>
     </row>
     <row r="854" spans="2:12" x14ac:dyDescent="0.45">
@@ -68390,16 +68390,16 @@
         <v>2023</v>
       </c>
       <c r="F854">
-        <v>3.5700000000000003E-2</v>
+        <v>1.89E-2</v>
       </c>
       <c r="G854">
         <v>1</v>
       </c>
       <c r="H854">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I854">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J854">
         <v>0</v>
@@ -68408,24 +68408,24 @@
         <v>32</v>
       </c>
       <c r="L854">
-        <v>0.18972426857005967</v>
+        <v>0.18550629799122259</v>
       </c>
     </row>
     <row r="855" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B855" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C855" t="s">
         <v>750</v>
       </c>
       <c r="D855" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="E855">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="F855">
-        <v>5.2700000000000004E-2</v>
+        <v>4.5899999999999996E-2</v>
       </c>
       <c r="G855">
         <v>1</v>
@@ -68440,10 +68440,10 @@
         <v>0</v>
       </c>
       <c r="K855">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="L855">
-        <v>0.18972426857005967</v>
+        <v>0.18691405777187248</v>
       </c>
     </row>
     <row r="856" spans="2:12" x14ac:dyDescent="0.45">
@@ -68457,10 +68457,10 @@
         <v>771</v>
       </c>
       <c r="E856">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="F856">
-        <v>0.1555</v>
+        <v>0.13450000000000001</v>
       </c>
       <c r="G856">
         <v>1</v>
@@ -68475,10 +68475,10 @@
         <v>0</v>
       </c>
       <c r="K856">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L856">
-        <v>0.19067081479710368</v>
+        <v>0.1869140577718725</v>
       </c>
     </row>
     <row r="857" spans="2:12" x14ac:dyDescent="0.45">
@@ -68492,28 +68492,28 @@
         <v>771</v>
       </c>
       <c r="E857">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="F857">
-        <v>0.22669999999999996</v>
+        <v>0.10060000000000001</v>
       </c>
       <c r="G857">
         <v>1</v>
       </c>
       <c r="H857">
-        <v>1379.8703131892373</v>
+        <v>1458</v>
       </c>
       <c r="I857">
-        <v>21.177095280105881</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J857">
         <v>0</v>
       </c>
       <c r="K857">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L857">
-        <v>0.19067081479710371</v>
+        <v>0.18691405777187248</v>
       </c>
     </row>
     <row r="858" spans="2:12" x14ac:dyDescent="0.45">
@@ -68527,28 +68527,28 @@
         <v>771</v>
       </c>
       <c r="E858">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F858">
-        <v>0.42839999999999995</v>
+        <v>8.2200000000000009E-2</v>
       </c>
       <c r="G858">
         <v>1</v>
       </c>
       <c r="H858">
-        <v>1458.0000000000002</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I858">
-        <v>22.425000000000033</v>
+        <v>22.424999999999976</v>
       </c>
       <c r="J858">
         <v>0</v>
       </c>
       <c r="K858">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L858">
-        <v>0.19067081479710346</v>
+        <v>0.18691405777187245</v>
       </c>
     </row>
     <row r="859" spans="2:12" x14ac:dyDescent="0.45">
@@ -68562,28 +68562,28 @@
         <v>771</v>
       </c>
       <c r="E859">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F859">
-        <v>0.19400000000000006</v>
+        <v>6.8099999999999994E-2</v>
       </c>
       <c r="G859">
         <v>1</v>
       </c>
       <c r="H859">
-        <v>1457.9999999999995</v>
+        <v>1458</v>
       </c>
       <c r="I859">
-        <v>22.425000000000001</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J859">
         <v>0</v>
       </c>
       <c r="K859">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L859">
-        <v>0.19067081479710357</v>
+        <v>0.18691405777187248</v>
       </c>
     </row>
     <row r="860" spans="2:12" x14ac:dyDescent="0.45">
@@ -68597,28 +68597,28 @@
         <v>771</v>
       </c>
       <c r="E860">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="F860">
-        <v>0.1978</v>
+        <v>7.9199999999999993E-2</v>
       </c>
       <c r="G860">
         <v>1</v>
       </c>
       <c r="H860">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I860">
-        <v>22.424999999999997</v>
+        <v>22.42499999999999</v>
       </c>
       <c r="J860">
         <v>0</v>
       </c>
       <c r="K860">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L860">
-        <v>0.19067081479710352</v>
+        <v>0.1869140577718725</v>
       </c>
     </row>
     <row r="861" spans="2:12" x14ac:dyDescent="0.45">
@@ -68632,16 +68632,16 @@
         <v>771</v>
       </c>
       <c r="E861">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F861">
-        <v>0.13719999999999999</v>
+        <v>6.1900000000000004E-2</v>
       </c>
       <c r="G861">
         <v>1</v>
       </c>
       <c r="H861">
-        <v>1458.0000000000002</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I861">
         <v>22.42499999999999</v>
@@ -68650,10 +68650,10 @@
         <v>0</v>
       </c>
       <c r="K861">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L861">
-        <v>0.19067081479710354</v>
+        <v>0.18691405777187248</v>
       </c>
     </row>
     <row r="862" spans="2:12" x14ac:dyDescent="0.45">
@@ -68667,28 +68667,28 @@
         <v>771</v>
       </c>
       <c r="E862">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="F862">
-        <v>0.31189999999999996</v>
+        <v>0.13190000000000004</v>
       </c>
       <c r="G862">
         <v>1</v>
       </c>
       <c r="H862">
-        <v>1384.5918563642192</v>
+        <v>1374.4821834723275</v>
       </c>
       <c r="I862">
-        <v>21.252508816928504</v>
+        <v>21.091034874905223</v>
       </c>
       <c r="J862">
         <v>0</v>
       </c>
       <c r="K862">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L862">
-        <v>0.19067081479710352</v>
+        <v>0.18691405777187242</v>
       </c>
     </row>
     <row r="863" spans="2:12" x14ac:dyDescent="0.45">
@@ -68702,28 +68702,28 @@
         <v>771</v>
       </c>
       <c r="E863">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F863">
-        <v>0.2712</v>
+        <v>0.12609999999999999</v>
       </c>
       <c r="G863">
         <v>1</v>
       </c>
       <c r="H863">
-        <v>1458.0000000000002</v>
+        <v>1458</v>
       </c>
       <c r="I863">
-        <v>22.425000000000011</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J863">
         <v>0</v>
       </c>
       <c r="K863">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L863">
-        <v>0.1906708147971036</v>
+        <v>0.18691405777187248</v>
       </c>
     </row>
     <row r="864" spans="2:12" x14ac:dyDescent="0.45">
@@ -68737,10 +68737,10 @@
         <v>771</v>
       </c>
       <c r="E864">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F864">
-        <v>0.16799999999999998</v>
+        <v>6.2400000000000004E-2</v>
       </c>
       <c r="G864">
         <v>1</v>
@@ -68755,10 +68755,10 @@
         <v>0</v>
       </c>
       <c r="K864">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L864">
-        <v>0.19067081479710357</v>
+        <v>0.18691405777187248</v>
       </c>
     </row>
     <row r="865" spans="2:12" x14ac:dyDescent="0.45">
@@ -68772,28 +68772,28 @@
         <v>771</v>
       </c>
       <c r="E865">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F865">
-        <v>0.23450000000000004</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="G865">
         <v>1</v>
       </c>
       <c r="H865">
-        <v>1399.9701492537308</v>
+        <v>1458</v>
       </c>
       <c r="I865">
-        <v>21.498134328358205</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J865">
         <v>0</v>
       </c>
       <c r="K865">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L865">
-        <v>0.19067081479710349</v>
+        <v>0.18691405777187253</v>
       </c>
     </row>
     <row r="866" spans="2:12" x14ac:dyDescent="0.45">
@@ -68807,10 +68807,10 @@
         <v>771</v>
       </c>
       <c r="E866">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F866">
-        <v>0.1154</v>
+        <v>2E-3</v>
       </c>
       <c r="G866">
         <v>1</v>
@@ -68825,45 +68825,45 @@
         <v>0</v>
       </c>
       <c r="K866">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L866">
-        <v>0.19067081479710346</v>
+        <v>0.1869140577718725</v>
       </c>
     </row>
     <row r="867" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B867" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C867" t="s">
         <v>750</v>
       </c>
       <c r="D867" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E867">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="F867">
-        <v>3.8999999999999998E-3</v>
+        <v>4.5700000000000011E-2</v>
       </c>
       <c r="G867">
         <v>1</v>
       </c>
       <c r="H867">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I867">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J867">
         <v>0</v>
       </c>
       <c r="K867">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="L867">
-        <v>0.19067081479710349</v>
+        <v>0.18972426857005958</v>
       </c>
     </row>
     <row r="868" spans="2:12" x14ac:dyDescent="0.45">
@@ -68877,10 +68877,10 @@
         <v>773</v>
       </c>
       <c r="E868">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="F868">
-        <v>6.9199999999999998E-2</v>
+        <v>0.10339999999999999</v>
       </c>
       <c r="G868">
         <v>1</v>
@@ -68889,16 +68889,16 @@
         <v>1458</v>
       </c>
       <c r="I868">
-        <v>22.425000000000001</v>
+        <v>22.424999999999986</v>
       </c>
       <c r="J868">
         <v>0</v>
       </c>
       <c r="K868">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L868">
-        <v>0.18738924720585975</v>
+        <v>0.18972426857005975</v>
       </c>
     </row>
     <row r="869" spans="2:12" x14ac:dyDescent="0.45">
@@ -68912,28 +68912,28 @@
         <v>773</v>
       </c>
       <c r="E869">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="F869">
-        <v>0.1143</v>
+        <v>0.16430000000000006</v>
       </c>
       <c r="G869">
         <v>1</v>
       </c>
       <c r="H869">
-        <v>1458</v>
+        <v>1457.9999999999995</v>
       </c>
       <c r="I869">
-        <v>22.42499999999999</v>
+        <v>22.424999999999986</v>
       </c>
       <c r="J869">
         <v>0</v>
       </c>
       <c r="K869">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L869">
-        <v>0.18738924720585984</v>
+        <v>0.18972426857005975</v>
       </c>
     </row>
     <row r="870" spans="2:12" x14ac:dyDescent="0.45">
@@ -68947,10 +68947,10 @@
         <v>773</v>
       </c>
       <c r="E870">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F870">
-        <v>0.1225</v>
+        <v>0.11509999999999998</v>
       </c>
       <c r="G870">
         <v>1</v>
@@ -68965,10 +68965,10 @@
         <v>0</v>
       </c>
       <c r="K870">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L870">
-        <v>0.18738924720585984</v>
+        <v>0.18972426857005978</v>
       </c>
     </row>
     <row r="871" spans="2:12" x14ac:dyDescent="0.45">
@@ -68982,28 +68982,28 @@
         <v>773</v>
       </c>
       <c r="E871">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F871">
-        <v>0.13639999999999994</v>
+        <v>9.0499999999999997E-2</v>
       </c>
       <c r="G871">
         <v>1</v>
       </c>
       <c r="H871">
-        <v>1458.0000000000002</v>
+        <v>1458</v>
       </c>
       <c r="I871">
-        <v>22.425000000000001</v>
+        <v>22.42499999999999</v>
       </c>
       <c r="J871">
         <v>0</v>
       </c>
       <c r="K871">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L871">
-        <v>0.18738924720586</v>
+        <v>0.18972426857005975</v>
       </c>
     </row>
     <row r="872" spans="2:12" x14ac:dyDescent="0.45">
@@ -69017,28 +69017,28 @@
         <v>773</v>
       </c>
       <c r="E872">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="F872">
-        <v>5.2999999999999999E-2</v>
+        <v>0.12670000000000001</v>
       </c>
       <c r="G872">
         <v>1</v>
       </c>
       <c r="H872">
-        <v>1458</v>
+        <v>1294.3378058405683</v>
       </c>
       <c r="I872">
-        <v>22.424999999999994</v>
+        <v>19.810951065509069</v>
       </c>
       <c r="J872">
         <v>0</v>
       </c>
       <c r="K872">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L872">
-        <v>0.18738924720585984</v>
+        <v>0.18972426857005972</v>
       </c>
     </row>
     <row r="873" spans="2:12" x14ac:dyDescent="0.45">
@@ -69052,16 +69052,16 @@
         <v>773</v>
       </c>
       <c r="E873">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F873">
-        <v>3.9800000000000002E-2</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="G873">
         <v>1</v>
       </c>
       <c r="H873">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I873">
         <v>22.424999999999997</v>
@@ -69070,10 +69070,10 @@
         <v>0</v>
       </c>
       <c r="K873">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L873">
-        <v>0.18738924720585978</v>
+        <v>0.18972426857005967</v>
       </c>
     </row>
     <row r="874" spans="2:12" x14ac:dyDescent="0.45">
@@ -69087,28 +69087,28 @@
         <v>773</v>
       </c>
       <c r="E874">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="F874">
-        <v>7.0400000000000004E-2</v>
+        <v>6.7600000000000007E-2</v>
       </c>
       <c r="G874">
         <v>1</v>
       </c>
       <c r="H874">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I874">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J874">
         <v>0</v>
       </c>
       <c r="K874">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L874">
-        <v>0.18738924720585981</v>
+        <v>0.18972426857005961</v>
       </c>
     </row>
     <row r="875" spans="2:12" x14ac:dyDescent="0.45">
@@ -69122,28 +69122,28 @@
         <v>773</v>
       </c>
       <c r="E875">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F875">
-        <v>0.14220000000000002</v>
+        <v>0.15260000000000001</v>
       </c>
       <c r="G875">
         <v>1</v>
       </c>
       <c r="H875">
-        <v>1380.5316455696204</v>
+        <v>1316.453473132372</v>
       </c>
       <c r="I875">
-        <v>21.187658227848093</v>
+        <v>20.164187418086495</v>
       </c>
       <c r="J875">
         <v>0</v>
       </c>
       <c r="K875">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L875">
-        <v>0.18738924720585981</v>
+        <v>0.1897242685700597</v>
       </c>
     </row>
     <row r="876" spans="2:12" x14ac:dyDescent="0.45">
@@ -69157,28 +69157,28 @@
         <v>773</v>
       </c>
       <c r="E876">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F876">
-        <v>0.14990000000000001</v>
+        <v>0.12540000000000001</v>
       </c>
       <c r="G876">
         <v>1</v>
       </c>
       <c r="H876">
-        <v>1458</v>
+        <v>1364.9856459330144</v>
       </c>
       <c r="I876">
-        <v>22.424999999999994</v>
+        <v>20.93935406698564</v>
       </c>
       <c r="J876">
         <v>0</v>
       </c>
       <c r="K876">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L876">
-        <v>0.18738924720585978</v>
+        <v>0.18972426857005975</v>
       </c>
     </row>
     <row r="877" spans="2:12" x14ac:dyDescent="0.45">
@@ -69192,10 +69192,10 @@
         <v>773</v>
       </c>
       <c r="E877">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F877">
-        <v>9.8600000000000007E-2</v>
+        <v>3.5700000000000003E-2</v>
       </c>
       <c r="G877">
         <v>1</v>
@@ -69210,10 +69210,10 @@
         <v>0</v>
       </c>
       <c r="K877">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L877">
-        <v>0.18738924720585978</v>
+        <v>0.18972426857005967</v>
       </c>
     </row>
     <row r="878" spans="2:12" x14ac:dyDescent="0.45">
@@ -69227,10 +69227,10 @@
         <v>773</v>
       </c>
       <c r="E878">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F878">
-        <v>1.1800000000000001E-2</v>
+        <v>5.2700000000000004E-2</v>
       </c>
       <c r="G878">
         <v>1</v>
@@ -69239,51 +69239,51 @@
         <v>1458</v>
       </c>
       <c r="I878">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J878">
         <v>0</v>
       </c>
       <c r="K878">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L878">
-        <v>0.18738924720585978</v>
+        <v>0.18972426857005967</v>
       </c>
     </row>
     <row r="879" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B879" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C879" t="s">
         <v>750</v>
       </c>
       <c r="D879" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E879">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="F879">
-        <v>4.0000000000000001E-3</v>
+        <v>0.18839999999999998</v>
       </c>
       <c r="G879">
         <v>1</v>
       </c>
       <c r="H879">
-        <v>1458</v>
+        <v>1458.0000000000002</v>
       </c>
       <c r="I879">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J879">
         <v>0</v>
       </c>
       <c r="K879">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="L879">
-        <v>0.18738924720585981</v>
+        <v>0.19008013066509072</v>
       </c>
     </row>
     <row r="880" spans="2:12" x14ac:dyDescent="0.45">
@@ -69297,28 +69297,28 @@
         <v>775</v>
       </c>
       <c r="E880">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="F880">
-        <v>2.0500000000000004E-2</v>
+        <v>0.26159999999999994</v>
       </c>
       <c r="G880">
         <v>1</v>
       </c>
       <c r="H880">
-        <v>1458</v>
+        <v>1390.2935779816514</v>
       </c>
       <c r="I880">
-        <v>22.424999999999997</v>
+        <v>21.343577981651396</v>
       </c>
       <c r="J880">
         <v>0</v>
       </c>
       <c r="K880">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L880">
-        <v>0.18539287912319005</v>
+        <v>0.19008013066509064</v>
       </c>
     </row>
     <row r="881" spans="2:12" x14ac:dyDescent="0.45">
@@ -69332,28 +69332,28 @@
         <v>775</v>
       </c>
       <c r="E881">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="F881">
-        <v>7.7799999999999994E-2</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="G881">
         <v>1</v>
       </c>
       <c r="H881">
-        <v>1457.9999999999995</v>
+        <v>1458.0000000000002</v>
       </c>
       <c r="I881">
-        <v>22.42499999999999</v>
+        <v>22.425000000000033</v>
       </c>
       <c r="J881">
         <v>0</v>
       </c>
       <c r="K881">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L881">
-        <v>0.18539287912319016</v>
+        <v>0.1900801306650903</v>
       </c>
     </row>
     <row r="882" spans="2:12" x14ac:dyDescent="0.45">
@@ -69367,28 +69367,28 @@
         <v>775</v>
       </c>
       <c r="E882">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F882">
-        <v>0.1114</v>
+        <v>0.27680000000000005</v>
       </c>
       <c r="G882">
         <v>1</v>
       </c>
       <c r="H882">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I882">
-        <v>22.42499999999999</v>
+        <v>22.425000000000026</v>
       </c>
       <c r="J882">
         <v>0</v>
       </c>
       <c r="K882">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L882">
-        <v>0.18539287912319011</v>
+        <v>0.19008013066509044</v>
       </c>
     </row>
     <row r="883" spans="2:12" x14ac:dyDescent="0.45">
@@ -69402,16 +69402,16 @@
         <v>775</v>
       </c>
       <c r="E883">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F883">
-        <v>4.4999999999999998E-2</v>
+        <v>0.20770000000000002</v>
       </c>
       <c r="G883">
         <v>1</v>
       </c>
       <c r="H883">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I883">
         <v>22.425000000000001</v>
@@ -69420,10 +69420,10 @@
         <v>0</v>
       </c>
       <c r="K883">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L883">
-        <v>0.18539287912319011</v>
+        <v>0.19008013066509066</v>
       </c>
     </row>
     <row r="884" spans="2:12" x14ac:dyDescent="0.45">
@@ -69437,28 +69437,28 @@
         <v>775</v>
       </c>
       <c r="E884">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="F884">
-        <v>8.5600000000000009E-2</v>
+        <v>0.1421</v>
       </c>
       <c r="G884">
         <v>1</v>
       </c>
       <c r="H884">
-        <v>1458</v>
+        <v>1458.0000000000002</v>
       </c>
       <c r="I884">
-        <v>22.424999999999994</v>
+        <v>22.424999999999986</v>
       </c>
       <c r="J884">
         <v>0</v>
       </c>
       <c r="K884">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L884">
-        <v>0.18539287912319014</v>
+        <v>0.19008013066509077</v>
       </c>
     </row>
     <row r="885" spans="2:12" x14ac:dyDescent="0.45">
@@ -69472,28 +69472,28 @@
         <v>775</v>
       </c>
       <c r="E885">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F885">
-        <v>5.3100000000000001E-2</v>
+        <v>0.32169999999999999</v>
       </c>
       <c r="G885">
         <v>1</v>
       </c>
       <c r="H885">
-        <v>1458</v>
+        <v>1386.8281007149517</v>
       </c>
       <c r="I885">
-        <v>22.42499999999999</v>
+        <v>21.288226608641597</v>
       </c>
       <c r="J885">
         <v>0</v>
       </c>
       <c r="K885">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L885">
-        <v>0.18539287912319011</v>
+        <v>0.19008013066509064</v>
       </c>
     </row>
     <row r="886" spans="2:12" x14ac:dyDescent="0.45">
@@ -69507,28 +69507,28 @@
         <v>775</v>
       </c>
       <c r="E886">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="F886">
-        <v>1.8200000000000001E-2</v>
+        <v>0.2883</v>
       </c>
       <c r="G886">
         <v>1</v>
       </c>
       <c r="H886">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I886">
-        <v>22.425000000000001</v>
+        <v>22.425000000000008</v>
       </c>
       <c r="J886">
         <v>0</v>
       </c>
       <c r="K886">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L886">
-        <v>0.18539287912319011</v>
+        <v>0.19008013066509061</v>
       </c>
     </row>
     <row r="887" spans="2:12" x14ac:dyDescent="0.45">
@@ -69542,10 +69542,10 @@
         <v>775</v>
       </c>
       <c r="E887">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="F887">
-        <v>5.3699999999999998E-2</v>
+        <v>0.19179999999999997</v>
       </c>
       <c r="G887">
         <v>1</v>
@@ -69554,16 +69554,16 @@
         <v>1458</v>
       </c>
       <c r="I887">
-        <v>22.425000000000004</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J887">
         <v>0</v>
       </c>
       <c r="K887">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L887">
-        <v>0.18539287912319011</v>
+        <v>0.19008013066509075</v>
       </c>
     </row>
     <row r="888" spans="2:12" x14ac:dyDescent="0.45">
@@ -69577,28 +69577,28 @@
         <v>775</v>
       </c>
       <c r="E888">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F888">
-        <v>3.7999999999999999E-2</v>
+        <v>0.27520000000000006</v>
       </c>
       <c r="G888">
         <v>1</v>
       </c>
       <c r="H888">
-        <v>1458</v>
+        <v>1408.5523255813955</v>
       </c>
       <c r="I888">
-        <v>22.424999999999997</v>
+        <v>21.635210755813958</v>
       </c>
       <c r="J888">
         <v>0</v>
       </c>
       <c r="K888">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L888">
-        <v>0.18539287912319011</v>
+        <v>0.19008013066509058</v>
       </c>
     </row>
     <row r="889" spans="2:12" x14ac:dyDescent="0.45">
@@ -69612,10 +69612,10 @@
         <v>775</v>
       </c>
       <c r="E889">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F889">
-        <v>1.5300000000000001E-2</v>
+        <v>0.12320000000000002</v>
       </c>
       <c r="G889">
         <v>1</v>
@@ -69630,10 +69630,10 @@
         <v>0</v>
       </c>
       <c r="K889">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L889">
-        <v>0.18539287912319011</v>
+        <v>0.19008013066509069</v>
       </c>
     </row>
     <row r="890" spans="2:12" x14ac:dyDescent="0.45">
@@ -69647,10 +69647,10 @@
         <v>775</v>
       </c>
       <c r="E890">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F890">
-        <v>2.07E-2</v>
+        <v>5.9000000000000007E-3</v>
       </c>
       <c r="G890">
         <v>1</v>
@@ -69659,16 +69659,16 @@
         <v>1458</v>
       </c>
       <c r="I890">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J890">
         <v>0</v>
       </c>
       <c r="K890">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L890">
-        <v>0.18539287912319011</v>
+        <v>0.19008013066509069</v>
       </c>
     </row>
     <row r="891" spans="2:12" x14ac:dyDescent="0.45">
@@ -76049,13 +76049,13 @@
         <v>750</v>
       </c>
       <c r="D1073" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="E1073">
         <v>2013</v>
       </c>
       <c r="F1073">
-        <v>3.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1073">
         <v>1</v>
@@ -76064,7 +76064,7 @@
         <v>1458</v>
       </c>
       <c r="I1073">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1073">
         <v>0</v>
@@ -76073,7 +76073,7 @@
         <v>42</v>
       </c>
       <c r="L1073">
-        <v>0.19855392263260624</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1074" spans="2:12" x14ac:dyDescent="0.45">
@@ -76084,13 +76084,13 @@
         <v>750</v>
       </c>
       <c r="D1074" t="s">
-        <v>202</v>
+        <v>24</v>
       </c>
       <c r="E1074">
         <v>2013</v>
       </c>
       <c r="F1074">
-        <v>1.9E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1074">
         <v>1</v>
@@ -76099,7 +76099,7 @@
         <v>1458</v>
       </c>
       <c r="I1074">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1074">
         <v>0</v>
@@ -76108,7 +76108,7 @@
         <v>42</v>
       </c>
       <c r="L1074">
-        <v>0.18013391841854179</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1075" spans="2:12" x14ac:dyDescent="0.45">
@@ -76154,13 +76154,13 @@
         <v>750</v>
       </c>
       <c r="D1076" t="s">
-        <v>289</v>
+        <v>72</v>
       </c>
       <c r="E1076">
         <v>2014</v>
       </c>
       <c r="F1076">
-        <v>3.8999999999999998E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1076">
         <v>1</v>
@@ -76224,13 +76224,13 @@
         <v>750</v>
       </c>
       <c r="D1078" t="s">
-        <v>121</v>
+        <v>289</v>
       </c>
       <c r="E1078">
         <v>2014</v>
       </c>
       <c r="F1078">
-        <v>2E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="G1078">
         <v>1</v>
@@ -76248,7 +76248,7 @@
         <v>41</v>
       </c>
       <c r="L1078">
-        <v>0.18076608822185891</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1079" spans="2:12" x14ac:dyDescent="0.45">
@@ -76259,13 +76259,13 @@
         <v>750</v>
       </c>
       <c r="D1079" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="E1079">
         <v>2014</v>
       </c>
       <c r="F1079">
-        <v>2.5000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="G1079">
         <v>1</v>
@@ -76283,7 +76283,7 @@
         <v>41</v>
       </c>
       <c r="L1079">
-        <v>0.1885335384832984</v>
+        <v>0.18076608822185891</v>
       </c>
     </row>
     <row r="1080" spans="2:12" x14ac:dyDescent="0.45">
@@ -76294,13 +76294,13 @@
         <v>750</v>
       </c>
       <c r="D1080" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="E1080">
         <v>2015</v>
       </c>
       <c r="F1080">
-        <v>1E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="G1080">
         <v>1</v>
@@ -76318,7 +76318,7 @@
         <v>40</v>
       </c>
       <c r="L1080">
-        <v>0.1885335384832984</v>
+        <v>0.1835968744267317</v>
       </c>
     </row>
     <row r="1081" spans="2:12" x14ac:dyDescent="0.45">
@@ -76364,19 +76364,19 @@
         <v>750</v>
       </c>
       <c r="D1082" t="s">
-        <v>702</v>
+        <v>289</v>
       </c>
       <c r="E1082">
         <v>2015</v>
       </c>
       <c r="F1082">
-        <v>4.9000000000000007E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="G1082">
         <v>1</v>
       </c>
       <c r="H1082">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1082">
         <v>22.424999999999997</v>
@@ -76388,7 +76388,7 @@
         <v>40</v>
       </c>
       <c r="L1082">
-        <v>0.18956968490584708</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1083" spans="2:12" x14ac:dyDescent="0.45">
@@ -76399,13 +76399,13 @@
         <v>750</v>
       </c>
       <c r="D1083" t="s">
-        <v>289</v>
+        <v>72</v>
       </c>
       <c r="E1083">
         <v>2015</v>
       </c>
       <c r="F1083">
-        <v>6.4000000000000003E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G1083">
         <v>1</v>
@@ -76469,19 +76469,19 @@
         <v>750</v>
       </c>
       <c r="D1085" t="s">
-        <v>121</v>
+        <v>702</v>
       </c>
       <c r="E1085">
         <v>2015</v>
       </c>
       <c r="F1085">
-        <v>2E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1085">
         <v>1</v>
       </c>
       <c r="H1085">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1085">
         <v>22.424999999999997</v>
@@ -76493,7 +76493,7 @@
         <v>40</v>
       </c>
       <c r="L1085">
-        <v>0.1835968744267317</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1086" spans="2:12" x14ac:dyDescent="0.45">
@@ -76609,13 +76609,13 @@
         <v>750</v>
       </c>
       <c r="D1089" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="E1089">
         <v>2018</v>
       </c>
       <c r="F1089">
-        <v>2.1000000000000001E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="G1089">
         <v>1</v>
@@ -76633,7 +76633,7 @@
         <v>37</v>
       </c>
       <c r="L1089">
-        <v>0.1885335384832984</v>
+        <v>0.1835968744267317</v>
       </c>
     </row>
     <row r="1090" spans="2:12" x14ac:dyDescent="0.45">
@@ -76644,13 +76644,13 @@
         <v>750</v>
       </c>
       <c r="D1090" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="E1090">
         <v>2018</v>
       </c>
       <c r="F1090">
-        <v>1E-3</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G1090">
         <v>1</v>
@@ -76668,7 +76668,7 @@
         <v>37</v>
       </c>
       <c r="L1090">
-        <v>0.1835968744267317</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1091" spans="2:12" x14ac:dyDescent="0.45">
@@ -81680,7 +81680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA57A0F-159E-4031-A873-E8C3188AAA22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E30F29-F95E-4A6C-8EA6-C053150D0967}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D0FA0F7-4985-4A3F-B788-EACC89F98B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84AC5568-6CFC-409D-9131-51CA7B435180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3E0A691E-83EC-4B9B-9BA9-D81945F3C1DF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{732CF2C3-D16A-409A-BABB-77216955AFB8}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4172,7 +4172,7 @@
     <t>en_pc_solar_pv_007</t>
   </si>
   <si>
-    <t>en_pc_solar_pv_011</t>
+    <t>en_pc_solar_pv_009</t>
   </si>
   <si>
     <t>en_pc_solar_pv_021</t>
@@ -6124,7 +6124,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFC8AFD4-C1F9-4051-AF35-088CCAE1D095}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{384C8227-21E0-4924-8056-C294D894C3C6}">
   <dimension ref="B9:T277"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21150,7 +21150,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E721759F-733E-4E16-8CD0-69019926E79D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6012D931-4933-41D4-B9F3-EE68D730F39B}">
   <dimension ref="B9:T131"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25778,7 +25778,7 @@
         <v>750</v>
       </c>
       <c r="D94" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="E94">
         <v>2025</v>
@@ -25802,7 +25802,7 @@
         <v>30</v>
       </c>
       <c r="L94">
-        <v>0.19008013066509069</v>
+        <v>0.19067081479710349</v>
       </c>
       <c r="N94" t="s">
         <v>891</v>
@@ -25834,7 +25834,7 @@
         <v>750</v>
       </c>
       <c r="D95" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="E95">
         <v>2026</v>
@@ -25858,7 +25858,7 @@
         <v>30</v>
       </c>
       <c r="L95">
-        <v>0.19008013066509069</v>
+        <v>0.19067081479710349</v>
       </c>
       <c r="N95" t="s">
         <v>891</v>
@@ -27709,7 +27709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA43B82-6072-4C3A-8590-CB03DAC34057}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACD27ABB-FEAD-4069-B068-E6E7C7D7C45C}">
   <dimension ref="B9:T1235"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46200,7 +46200,7 @@
         <v>441</v>
       </c>
       <c r="P364" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="Q364" t="s">
         <v>893</v>
@@ -46253,7 +46253,7 @@
         <v>441</v>
       </c>
       <c r="P365" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="Q365" t="s">
         <v>893</v>
@@ -46518,7 +46518,7 @@
         <v>448</v>
       </c>
       <c r="P370" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="Q370" t="s">
         <v>893</v>
@@ -46571,7 +46571,7 @@
         <v>448</v>
       </c>
       <c r="P371" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="Q371" t="s">
         <v>893</v>
@@ -60065,7 +60065,7 @@
         <v>766</v>
       </c>
       <c r="P632" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="Q632" t="s">
         <v>893</v>
@@ -60115,7 +60115,7 @@
         <v>766</v>
       </c>
       <c r="P633" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="Q633" t="s">
         <v>893</v>
@@ -60165,7 +60165,7 @@
         <v>767</v>
       </c>
       <c r="P634" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="Q634" t="s">
         <v>893</v>
@@ -60215,7 +60215,7 @@
         <v>767</v>
       </c>
       <c r="P635" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="Q635" t="s">
         <v>893</v>
@@ -60865,7 +60865,7 @@
         <v>792</v>
       </c>
       <c r="P648" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="Q648" t="s">
         <v>893</v>
@@ -60915,7 +60915,7 @@
         <v>792</v>
       </c>
       <c r="P649" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="Q649" t="s">
         <v>893</v>
@@ -61015,7 +61015,7 @@
         <v>795</v>
       </c>
       <c r="P651" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="Q651" t="s">
         <v>893</v>
@@ -61065,7 +61065,7 @@
         <v>795</v>
       </c>
       <c r="P652" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="Q652" t="s">
         <v>893</v>
@@ -62901,7 +62901,7 @@
         <v>868</v>
       </c>
       <c r="P694" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="Q694" t="s">
         <v>893</v>
@@ -62942,7 +62942,7 @@
         <v>868</v>
       </c>
       <c r="P695" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="Q695" t="s">
         <v>893</v>
@@ -63253,7 +63253,7 @@
         <v>879</v>
       </c>
       <c r="P702" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="Q702" t="s">
         <v>893</v>
@@ -63306,7 +63306,7 @@
         <v>879</v>
       </c>
       <c r="P703" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="Q703" t="s">
         <v>893</v>
@@ -65527,7 +65527,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L771">
-        <v>0.18316422679765962</v>
+        <v>0.18320255283232129</v>
       </c>
     </row>
     <row r="772" spans="2:12" x14ac:dyDescent="0.45">
@@ -65550,7 +65550,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L772">
-        <v>0.18316422679765962</v>
+        <v>0.18320255283232129</v>
       </c>
     </row>
     <row r="773" spans="2:12" x14ac:dyDescent="0.45">
@@ -65573,7 +65573,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L773">
-        <v>0.18316422679765962</v>
+        <v>0.18320255283232129</v>
       </c>
     </row>
     <row r="774" spans="2:12" x14ac:dyDescent="0.45">
@@ -68040,16 +68040,16 @@
         <v>2013</v>
       </c>
       <c r="F844">
-        <v>1.09E-2</v>
+        <v>4.5700000000000011E-2</v>
       </c>
       <c r="G844">
         <v>1</v>
       </c>
       <c r="H844">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I844">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J844">
         <v>0</v>
@@ -68058,7 +68058,7 @@
         <v>42</v>
       </c>
       <c r="L844">
-        <v>0.18550629799122259</v>
+        <v>0.18972426857005958</v>
       </c>
     </row>
     <row r="845" spans="2:12" x14ac:dyDescent="0.45">
@@ -68075,16 +68075,16 @@
         <v>2014</v>
       </c>
       <c r="F845">
-        <v>2.2699999999999998E-2</v>
+        <v>0.10339999999999999</v>
       </c>
       <c r="G845">
         <v>1</v>
       </c>
       <c r="H845">
-        <v>1458.0000000000002</v>
+        <v>1458</v>
       </c>
       <c r="I845">
-        <v>22.424999999999997</v>
+        <v>22.424999999999986</v>
       </c>
       <c r="J845">
         <v>0</v>
@@ -68093,7 +68093,7 @@
         <v>41</v>
       </c>
       <c r="L845">
-        <v>0.18550629799122262</v>
+        <v>0.18972426857005975</v>
       </c>
     </row>
     <row r="846" spans="2:12" x14ac:dyDescent="0.45">
@@ -68110,16 +68110,16 @@
         <v>2015</v>
       </c>
       <c r="F846">
-        <v>7.0699999999999985E-2</v>
+        <v>0.16430000000000006</v>
       </c>
       <c r="G846">
         <v>1</v>
       </c>
       <c r="H846">
-        <v>1458.0000000000002</v>
+        <v>1457.9999999999995</v>
       </c>
       <c r="I846">
-        <v>22.424999999999997</v>
+        <v>22.424999999999986</v>
       </c>
       <c r="J846">
         <v>0</v>
@@ -68128,7 +68128,7 @@
         <v>40</v>
       </c>
       <c r="L846">
-        <v>0.18550629799122267</v>
+        <v>0.18972426857005975</v>
       </c>
     </row>
     <row r="847" spans="2:12" x14ac:dyDescent="0.45">
@@ -68145,16 +68145,16 @@
         <v>2016</v>
       </c>
       <c r="F847">
-        <v>1.6400000000000001E-2</v>
+        <v>0.11509999999999998</v>
       </c>
       <c r="G847">
         <v>1</v>
       </c>
       <c r="H847">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I847">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J847">
         <v>0</v>
@@ -68163,7 +68163,7 @@
         <v>39</v>
       </c>
       <c r="L847">
-        <v>0.18550629799122256</v>
+        <v>0.18972426857005978</v>
       </c>
     </row>
     <row r="848" spans="2:12" x14ac:dyDescent="0.45">
@@ -68180,7 +68180,7 @@
         <v>2017</v>
       </c>
       <c r="F848">
-        <v>6.0600000000000001E-2</v>
+        <v>9.0499999999999997E-2</v>
       </c>
       <c r="G848">
         <v>1</v>
@@ -68189,7 +68189,7 @@
         <v>1458</v>
       </c>
       <c r="I848">
-        <v>22.424999999999994</v>
+        <v>22.42499999999999</v>
       </c>
       <c r="J848">
         <v>0</v>
@@ -68198,7 +68198,7 @@
         <v>38</v>
       </c>
       <c r="L848">
-        <v>0.18550629799122262</v>
+        <v>0.18972426857005975</v>
       </c>
     </row>
     <row r="849" spans="2:12" x14ac:dyDescent="0.45">
@@ -68215,16 +68215,16 @@
         <v>2018</v>
       </c>
       <c r="F849">
-        <v>8.8000000000000005E-3</v>
+        <v>0.12670000000000001</v>
       </c>
       <c r="G849">
         <v>1</v>
       </c>
       <c r="H849">
-        <v>1458</v>
+        <v>1294.3378058405683</v>
       </c>
       <c r="I849">
-        <v>22.424999999999994</v>
+        <v>19.810951065509069</v>
       </c>
       <c r="J849">
         <v>0</v>
@@ -68233,7 +68233,7 @@
         <v>37</v>
       </c>
       <c r="L849">
-        <v>0.18550629799122256</v>
+        <v>0.18972426857005972</v>
       </c>
     </row>
     <row r="850" spans="2:12" x14ac:dyDescent="0.45">
@@ -68250,16 +68250,16 @@
         <v>2019</v>
       </c>
       <c r="F850">
-        <v>1.6899999999999998E-2</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="G850">
         <v>1</v>
       </c>
       <c r="H850">
-        <v>1458.0000000000002</v>
+        <v>1458</v>
       </c>
       <c r="I850">
-        <v>22.425000000000004</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J850">
         <v>0</v>
@@ -68268,7 +68268,7 @@
         <v>36</v>
       </c>
       <c r="L850">
-        <v>0.18550629799122259</v>
+        <v>0.18972426857005967</v>
       </c>
     </row>
     <row r="851" spans="2:12" x14ac:dyDescent="0.45">
@@ -68285,7 +68285,7 @@
         <v>2020</v>
       </c>
       <c r="F851">
-        <v>4.6899999999999997E-2</v>
+        <v>6.7600000000000007E-2</v>
       </c>
       <c r="G851">
         <v>1</v>
@@ -68294,7 +68294,7 @@
         <v>1458</v>
       </c>
       <c r="I851">
-        <v>22.425000000000001</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J851">
         <v>0</v>
@@ -68303,7 +68303,7 @@
         <v>35</v>
       </c>
       <c r="L851">
-        <v>0.18550629799122259</v>
+        <v>0.18972426857005961</v>
       </c>
     </row>
     <row r="852" spans="2:12" x14ac:dyDescent="0.45">
@@ -68320,16 +68320,16 @@
         <v>2021</v>
       </c>
       <c r="F852">
-        <v>3.7999999999999999E-2</v>
+        <v>0.15260000000000001</v>
       </c>
       <c r="G852">
         <v>1</v>
       </c>
       <c r="H852">
-        <v>1458</v>
+        <v>1316.453473132372</v>
       </c>
       <c r="I852">
-        <v>22.424999999999997</v>
+        <v>20.164187418086495</v>
       </c>
       <c r="J852">
         <v>0</v>
@@ -68338,7 +68338,7 @@
         <v>34</v>
       </c>
       <c r="L852">
-        <v>0.18550629799122262</v>
+        <v>0.1897242685700597</v>
       </c>
     </row>
     <row r="853" spans="2:12" x14ac:dyDescent="0.45">
@@ -68355,16 +68355,16 @@
         <v>2022</v>
       </c>
       <c r="F853">
-        <v>1.0800000000000001E-2</v>
+        <v>0.12540000000000001</v>
       </c>
       <c r="G853">
         <v>1</v>
       </c>
       <c r="H853">
-        <v>1457.9999999999998</v>
+        <v>1364.9856459330144</v>
       </c>
       <c r="I853">
-        <v>22.424999999999997</v>
+        <v>20.93935406698564</v>
       </c>
       <c r="J853">
         <v>0</v>
@@ -68373,7 +68373,7 @@
         <v>33</v>
       </c>
       <c r="L853">
-        <v>0.18550629799122256</v>
+        <v>0.18972426857005975</v>
       </c>
     </row>
     <row r="854" spans="2:12" x14ac:dyDescent="0.45">
@@ -68390,16 +68390,16 @@
         <v>2023</v>
       </c>
       <c r="F854">
-        <v>1.89E-2</v>
+        <v>3.5700000000000003E-2</v>
       </c>
       <c r="G854">
         <v>1</v>
       </c>
       <c r="H854">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I854">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J854">
         <v>0</v>
@@ -68408,24 +68408,24 @@
         <v>32</v>
       </c>
       <c r="L854">
-        <v>0.18550629799122259</v>
+        <v>0.18972426857005967</v>
       </c>
     </row>
     <row r="855" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B855" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C855" t="s">
         <v>750</v>
       </c>
       <c r="D855" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="E855">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F855">
-        <v>4.5899999999999996E-2</v>
+        <v>5.2700000000000004E-2</v>
       </c>
       <c r="G855">
         <v>1</v>
@@ -68440,10 +68440,10 @@
         <v>0</v>
       </c>
       <c r="K855">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="L855">
-        <v>0.18691405777187248</v>
+        <v>0.18972426857005967</v>
       </c>
     </row>
     <row r="856" spans="2:12" x14ac:dyDescent="0.45">
@@ -68457,10 +68457,10 @@
         <v>771</v>
       </c>
       <c r="E856">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="F856">
-        <v>0.13450000000000001</v>
+        <v>0.1555</v>
       </c>
       <c r="G856">
         <v>1</v>
@@ -68475,10 +68475,10 @@
         <v>0</v>
       </c>
       <c r="K856">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L856">
-        <v>0.1869140577718725</v>
+        <v>0.19067081479710368</v>
       </c>
     </row>
     <row r="857" spans="2:12" x14ac:dyDescent="0.45">
@@ -68492,28 +68492,28 @@
         <v>771</v>
       </c>
       <c r="E857">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="F857">
-        <v>0.10060000000000001</v>
+        <v>0.22669999999999996</v>
       </c>
       <c r="G857">
         <v>1</v>
       </c>
       <c r="H857">
-        <v>1458</v>
+        <v>1379.8703131892373</v>
       </c>
       <c r="I857">
-        <v>22.424999999999997</v>
+        <v>21.177095280105881</v>
       </c>
       <c r="J857">
         <v>0</v>
       </c>
       <c r="K857">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L857">
-        <v>0.18691405777187248</v>
+        <v>0.19067081479710371</v>
       </c>
     </row>
     <row r="858" spans="2:12" x14ac:dyDescent="0.45">
@@ -68527,28 +68527,28 @@
         <v>771</v>
       </c>
       <c r="E858">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F858">
-        <v>8.2200000000000009E-2</v>
+        <v>0.42839999999999995</v>
       </c>
       <c r="G858">
         <v>1</v>
       </c>
       <c r="H858">
-        <v>1457.9999999999998</v>
+        <v>1458.0000000000002</v>
       </c>
       <c r="I858">
-        <v>22.424999999999976</v>
+        <v>22.425000000000033</v>
       </c>
       <c r="J858">
         <v>0</v>
       </c>
       <c r="K858">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L858">
-        <v>0.18691405777187245</v>
+        <v>0.19067081479710346</v>
       </c>
     </row>
     <row r="859" spans="2:12" x14ac:dyDescent="0.45">
@@ -68562,28 +68562,28 @@
         <v>771</v>
       </c>
       <c r="E859">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F859">
-        <v>6.8099999999999994E-2</v>
+        <v>0.19400000000000006</v>
       </c>
       <c r="G859">
         <v>1</v>
       </c>
       <c r="H859">
-        <v>1458</v>
+        <v>1457.9999999999995</v>
       </c>
       <c r="I859">
-        <v>22.424999999999997</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J859">
         <v>0</v>
       </c>
       <c r="K859">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L859">
-        <v>0.18691405777187248</v>
+        <v>0.19067081479710357</v>
       </c>
     </row>
     <row r="860" spans="2:12" x14ac:dyDescent="0.45">
@@ -68597,28 +68597,28 @@
         <v>771</v>
       </c>
       <c r="E860">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F860">
-        <v>7.9199999999999993E-2</v>
+        <v>0.1978</v>
       </c>
       <c r="G860">
         <v>1</v>
       </c>
       <c r="H860">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I860">
-        <v>22.42499999999999</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J860">
         <v>0</v>
       </c>
       <c r="K860">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L860">
-        <v>0.1869140577718725</v>
+        <v>0.19067081479710352</v>
       </c>
     </row>
     <row r="861" spans="2:12" x14ac:dyDescent="0.45">
@@ -68632,16 +68632,16 @@
         <v>771</v>
       </c>
       <c r="E861">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F861">
-        <v>6.1900000000000004E-2</v>
+        <v>0.13719999999999999</v>
       </c>
       <c r="G861">
         <v>1</v>
       </c>
       <c r="H861">
-        <v>1457.9999999999998</v>
+        <v>1458.0000000000002</v>
       </c>
       <c r="I861">
         <v>22.42499999999999</v>
@@ -68650,10 +68650,10 @@
         <v>0</v>
       </c>
       <c r="K861">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L861">
-        <v>0.18691405777187248</v>
+        <v>0.19067081479710354</v>
       </c>
     </row>
     <row r="862" spans="2:12" x14ac:dyDescent="0.45">
@@ -68667,28 +68667,28 @@
         <v>771</v>
       </c>
       <c r="E862">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F862">
-        <v>0.13190000000000004</v>
+        <v>0.31189999999999996</v>
       </c>
       <c r="G862">
         <v>1</v>
       </c>
       <c r="H862">
-        <v>1374.4821834723275</v>
+        <v>1384.5918563642192</v>
       </c>
       <c r="I862">
-        <v>21.091034874905223</v>
+        <v>21.252508816928504</v>
       </c>
       <c r="J862">
         <v>0</v>
       </c>
       <c r="K862">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L862">
-        <v>0.18691405777187242</v>
+        <v>0.19067081479710352</v>
       </c>
     </row>
     <row r="863" spans="2:12" x14ac:dyDescent="0.45">
@@ -68702,28 +68702,28 @@
         <v>771</v>
       </c>
       <c r="E863">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F863">
-        <v>0.12609999999999999</v>
+        <v>0.2712</v>
       </c>
       <c r="G863">
         <v>1</v>
       </c>
       <c r="H863">
-        <v>1458</v>
+        <v>1458.0000000000002</v>
       </c>
       <c r="I863">
-        <v>22.424999999999994</v>
+        <v>22.425000000000011</v>
       </c>
       <c r="J863">
         <v>0</v>
       </c>
       <c r="K863">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L863">
-        <v>0.18691405777187248</v>
+        <v>0.1906708147971036</v>
       </c>
     </row>
     <row r="864" spans="2:12" x14ac:dyDescent="0.45">
@@ -68737,10 +68737,10 @@
         <v>771</v>
       </c>
       <c r="E864">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F864">
-        <v>6.2400000000000004E-2</v>
+        <v>0.16799999999999998</v>
       </c>
       <c r="G864">
         <v>1</v>
@@ -68755,10 +68755,10 @@
         <v>0</v>
       </c>
       <c r="K864">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L864">
-        <v>0.18691405777187248</v>
+        <v>0.19067081479710357</v>
       </c>
     </row>
     <row r="865" spans="2:12" x14ac:dyDescent="0.45">
@@ -68772,28 +68772,28 @@
         <v>771</v>
       </c>
       <c r="E865">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F865">
-        <v>5.7999999999999996E-3</v>
+        <v>0.23450000000000004</v>
       </c>
       <c r="G865">
         <v>1</v>
       </c>
       <c r="H865">
-        <v>1458</v>
+        <v>1399.9701492537308</v>
       </c>
       <c r="I865">
-        <v>22.425000000000001</v>
+        <v>21.498134328358205</v>
       </c>
       <c r="J865">
         <v>0</v>
       </c>
       <c r="K865">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L865">
-        <v>0.18691405777187253</v>
+        <v>0.19067081479710349</v>
       </c>
     </row>
     <row r="866" spans="2:12" x14ac:dyDescent="0.45">
@@ -68807,10 +68807,10 @@
         <v>771</v>
       </c>
       <c r="E866">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F866">
-        <v>2E-3</v>
+        <v>0.1154</v>
       </c>
       <c r="G866">
         <v>1</v>
@@ -68825,45 +68825,45 @@
         <v>0</v>
       </c>
       <c r="K866">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L866">
-        <v>0.1869140577718725</v>
+        <v>0.19067081479710346</v>
       </c>
     </row>
     <row r="867" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B867" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C867" t="s">
         <v>750</v>
       </c>
       <c r="D867" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="E867">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F867">
-        <v>4.5700000000000011E-2</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="G867">
         <v>1</v>
       </c>
       <c r="H867">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I867">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J867">
         <v>0</v>
       </c>
       <c r="K867">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="L867">
-        <v>0.18972426857005958</v>
+        <v>0.19067081479710349</v>
       </c>
     </row>
     <row r="868" spans="2:12" x14ac:dyDescent="0.45">
@@ -68877,10 +68877,10 @@
         <v>773</v>
       </c>
       <c r="E868">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="F868">
-        <v>0.10339999999999999</v>
+        <v>6.9199999999999998E-2</v>
       </c>
       <c r="G868">
         <v>1</v>
@@ -68889,16 +68889,16 @@
         <v>1458</v>
       </c>
       <c r="I868">
-        <v>22.424999999999986</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J868">
         <v>0</v>
       </c>
       <c r="K868">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L868">
-        <v>0.18972426857005975</v>
+        <v>0.18738924720585975</v>
       </c>
     </row>
     <row r="869" spans="2:12" x14ac:dyDescent="0.45">
@@ -68912,28 +68912,28 @@
         <v>773</v>
       </c>
       <c r="E869">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="F869">
-        <v>0.16430000000000006</v>
+        <v>0.1143</v>
       </c>
       <c r="G869">
         <v>1</v>
       </c>
       <c r="H869">
-        <v>1457.9999999999995</v>
+        <v>1458</v>
       </c>
       <c r="I869">
-        <v>22.424999999999986</v>
+        <v>22.42499999999999</v>
       </c>
       <c r="J869">
         <v>0</v>
       </c>
       <c r="K869">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L869">
-        <v>0.18972426857005975</v>
+        <v>0.18738924720585984</v>
       </c>
     </row>
     <row r="870" spans="2:12" x14ac:dyDescent="0.45">
@@ -68947,10 +68947,10 @@
         <v>773</v>
       </c>
       <c r="E870">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F870">
-        <v>0.11509999999999998</v>
+        <v>0.1225</v>
       </c>
       <c r="G870">
         <v>1</v>
@@ -68965,10 +68965,10 @@
         <v>0</v>
       </c>
       <c r="K870">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L870">
-        <v>0.18972426857005978</v>
+        <v>0.18738924720585984</v>
       </c>
     </row>
     <row r="871" spans="2:12" x14ac:dyDescent="0.45">
@@ -68982,28 +68982,28 @@
         <v>773</v>
       </c>
       <c r="E871">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F871">
-        <v>9.0499999999999997E-2</v>
+        <v>0.13639999999999994</v>
       </c>
       <c r="G871">
         <v>1</v>
       </c>
       <c r="H871">
-        <v>1458</v>
+        <v>1458.0000000000002</v>
       </c>
       <c r="I871">
-        <v>22.42499999999999</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J871">
         <v>0</v>
       </c>
       <c r="K871">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L871">
-        <v>0.18972426857005975</v>
+        <v>0.18738924720586</v>
       </c>
     </row>
     <row r="872" spans="2:12" x14ac:dyDescent="0.45">
@@ -69017,28 +69017,28 @@
         <v>773</v>
       </c>
       <c r="E872">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F872">
-        <v>0.12670000000000001</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="G872">
         <v>1</v>
       </c>
       <c r="H872">
-        <v>1294.3378058405683</v>
+        <v>1458</v>
       </c>
       <c r="I872">
-        <v>19.810951065509069</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J872">
         <v>0</v>
       </c>
       <c r="K872">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L872">
-        <v>0.18972426857005972</v>
+        <v>0.18738924720585984</v>
       </c>
     </row>
     <row r="873" spans="2:12" x14ac:dyDescent="0.45">
@@ -69052,16 +69052,16 @@
         <v>773</v>
       </c>
       <c r="E873">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F873">
-        <v>5.3999999999999999E-2</v>
+        <v>3.9800000000000002E-2</v>
       </c>
       <c r="G873">
         <v>1</v>
       </c>
       <c r="H873">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I873">
         <v>22.424999999999997</v>
@@ -69070,10 +69070,10 @@
         <v>0</v>
       </c>
       <c r="K873">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L873">
-        <v>0.18972426857005967</v>
+        <v>0.18738924720585978</v>
       </c>
     </row>
     <row r="874" spans="2:12" x14ac:dyDescent="0.45">
@@ -69087,28 +69087,28 @@
         <v>773</v>
       </c>
       <c r="E874">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F874">
-        <v>6.7600000000000007E-2</v>
+        <v>7.0400000000000004E-2</v>
       </c>
       <c r="G874">
         <v>1</v>
       </c>
       <c r="H874">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I874">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J874">
         <v>0</v>
       </c>
       <c r="K874">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L874">
-        <v>0.18972426857005961</v>
+        <v>0.18738924720585981</v>
       </c>
     </row>
     <row r="875" spans="2:12" x14ac:dyDescent="0.45">
@@ -69122,28 +69122,28 @@
         <v>773</v>
       </c>
       <c r="E875">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F875">
-        <v>0.15260000000000001</v>
+        <v>0.14220000000000002</v>
       </c>
       <c r="G875">
         <v>1</v>
       </c>
       <c r="H875">
-        <v>1316.453473132372</v>
+        <v>1380.5316455696204</v>
       </c>
       <c r="I875">
-        <v>20.164187418086495</v>
+        <v>21.187658227848093</v>
       </c>
       <c r="J875">
         <v>0</v>
       </c>
       <c r="K875">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L875">
-        <v>0.1897242685700597</v>
+        <v>0.18738924720585981</v>
       </c>
     </row>
     <row r="876" spans="2:12" x14ac:dyDescent="0.45">
@@ -69157,28 +69157,28 @@
         <v>773</v>
       </c>
       <c r="E876">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F876">
-        <v>0.12540000000000001</v>
+        <v>0.14990000000000001</v>
       </c>
       <c r="G876">
         <v>1</v>
       </c>
       <c r="H876">
-        <v>1364.9856459330144</v>
+        <v>1458</v>
       </c>
       <c r="I876">
-        <v>20.93935406698564</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J876">
         <v>0</v>
       </c>
       <c r="K876">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L876">
-        <v>0.18972426857005975</v>
+        <v>0.18738924720585978</v>
       </c>
     </row>
     <row r="877" spans="2:12" x14ac:dyDescent="0.45">
@@ -69192,10 +69192,10 @@
         <v>773</v>
       </c>
       <c r="E877">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F877">
-        <v>3.5700000000000003E-2</v>
+        <v>9.8600000000000007E-2</v>
       </c>
       <c r="G877">
         <v>1</v>
@@ -69210,10 +69210,10 @@
         <v>0</v>
       </c>
       <c r="K877">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L877">
-        <v>0.18972426857005967</v>
+        <v>0.18738924720585978</v>
       </c>
     </row>
     <row r="878" spans="2:12" x14ac:dyDescent="0.45">
@@ -69227,10 +69227,10 @@
         <v>773</v>
       </c>
       <c r="E878">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F878">
-        <v>5.2700000000000004E-2</v>
+        <v>1.1800000000000001E-2</v>
       </c>
       <c r="G878">
         <v>1</v>
@@ -69239,51 +69239,51 @@
         <v>1458</v>
       </c>
       <c r="I878">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J878">
         <v>0</v>
       </c>
       <c r="K878">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L878">
-        <v>0.18972426857005967</v>
+        <v>0.18738924720585978</v>
       </c>
     </row>
     <row r="879" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B879" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C879" t="s">
         <v>750</v>
       </c>
       <c r="D879" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="E879">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F879">
-        <v>0.18839999999999998</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="G879">
         <v>1</v>
       </c>
       <c r="H879">
-        <v>1458.0000000000002</v>
+        <v>1458</v>
       </c>
       <c r="I879">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J879">
         <v>0</v>
       </c>
       <c r="K879">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="L879">
-        <v>0.19008013066509072</v>
+        <v>0.18738924720585981</v>
       </c>
     </row>
     <row r="880" spans="2:12" x14ac:dyDescent="0.45">
@@ -69297,28 +69297,28 @@
         <v>775</v>
       </c>
       <c r="E880">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="F880">
-        <v>0.26159999999999994</v>
+        <v>2.0500000000000004E-2</v>
       </c>
       <c r="G880">
         <v>1</v>
       </c>
       <c r="H880">
-        <v>1390.2935779816514</v>
+        <v>1458</v>
       </c>
       <c r="I880">
-        <v>21.343577981651396</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J880">
         <v>0</v>
       </c>
       <c r="K880">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L880">
-        <v>0.19008013066509064</v>
+        <v>0.18539287912319005</v>
       </c>
     </row>
     <row r="881" spans="2:12" x14ac:dyDescent="0.45">
@@ -69332,28 +69332,28 @@
         <v>775</v>
       </c>
       <c r="E881">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="F881">
-        <v>0.49099999999999999</v>
+        <v>7.7799999999999994E-2</v>
       </c>
       <c r="G881">
         <v>1</v>
       </c>
       <c r="H881">
-        <v>1458.0000000000002</v>
+        <v>1457.9999999999995</v>
       </c>
       <c r="I881">
-        <v>22.425000000000033</v>
+        <v>22.42499999999999</v>
       </c>
       <c r="J881">
         <v>0</v>
       </c>
       <c r="K881">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L881">
-        <v>0.1900801306650903</v>
+        <v>0.18539287912319016</v>
       </c>
     </row>
     <row r="882" spans="2:12" x14ac:dyDescent="0.45">
@@ -69367,28 +69367,28 @@
         <v>775</v>
       </c>
       <c r="E882">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F882">
-        <v>0.27680000000000005</v>
+        <v>0.1114</v>
       </c>
       <c r="G882">
         <v>1</v>
       </c>
       <c r="H882">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I882">
-        <v>22.425000000000026</v>
+        <v>22.42499999999999</v>
       </c>
       <c r="J882">
         <v>0</v>
       </c>
       <c r="K882">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L882">
-        <v>0.19008013066509044</v>
+        <v>0.18539287912319011</v>
       </c>
     </row>
     <row r="883" spans="2:12" x14ac:dyDescent="0.45">
@@ -69402,16 +69402,16 @@
         <v>775</v>
       </c>
       <c r="E883">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F883">
-        <v>0.20770000000000002</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="G883">
         <v>1</v>
       </c>
       <c r="H883">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I883">
         <v>22.425000000000001</v>
@@ -69420,10 +69420,10 @@
         <v>0</v>
       </c>
       <c r="K883">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L883">
-        <v>0.19008013066509066</v>
+        <v>0.18539287912319011</v>
       </c>
     </row>
     <row r="884" spans="2:12" x14ac:dyDescent="0.45">
@@ -69437,28 +69437,28 @@
         <v>775</v>
       </c>
       <c r="E884">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F884">
-        <v>0.1421</v>
+        <v>8.5600000000000009E-2</v>
       </c>
       <c r="G884">
         <v>1</v>
       </c>
       <c r="H884">
-        <v>1458.0000000000002</v>
+        <v>1458</v>
       </c>
       <c r="I884">
-        <v>22.424999999999986</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J884">
         <v>0</v>
       </c>
       <c r="K884">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L884">
-        <v>0.19008013066509077</v>
+        <v>0.18539287912319014</v>
       </c>
     </row>
     <row r="885" spans="2:12" x14ac:dyDescent="0.45">
@@ -69472,28 +69472,28 @@
         <v>775</v>
       </c>
       <c r="E885">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="F885">
-        <v>0.32169999999999999</v>
+        <v>5.3100000000000001E-2</v>
       </c>
       <c r="G885">
         <v>1</v>
       </c>
       <c r="H885">
-        <v>1386.8281007149517</v>
+        <v>1458</v>
       </c>
       <c r="I885">
-        <v>21.288226608641597</v>
+        <v>22.42499999999999</v>
       </c>
       <c r="J885">
         <v>0</v>
       </c>
       <c r="K885">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L885">
-        <v>0.19008013066509064</v>
+        <v>0.18539287912319011</v>
       </c>
     </row>
     <row r="886" spans="2:12" x14ac:dyDescent="0.45">
@@ -69507,28 +69507,28 @@
         <v>775</v>
       </c>
       <c r="E886">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F886">
-        <v>0.2883</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="G886">
         <v>1</v>
       </c>
       <c r="H886">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I886">
-        <v>22.425000000000008</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J886">
         <v>0</v>
       </c>
       <c r="K886">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L886">
-        <v>0.19008013066509061</v>
+        <v>0.18539287912319011</v>
       </c>
     </row>
     <row r="887" spans="2:12" x14ac:dyDescent="0.45">
@@ -69542,10 +69542,10 @@
         <v>775</v>
       </c>
       <c r="E887">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F887">
-        <v>0.19179999999999997</v>
+        <v>5.3699999999999998E-2</v>
       </c>
       <c r="G887">
         <v>1</v>
@@ -69554,16 +69554,16 @@
         <v>1458</v>
       </c>
       <c r="I887">
-        <v>22.425000000000001</v>
+        <v>22.425000000000004</v>
       </c>
       <c r="J887">
         <v>0</v>
       </c>
       <c r="K887">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L887">
-        <v>0.19008013066509075</v>
+        <v>0.18539287912319011</v>
       </c>
     </row>
     <row r="888" spans="2:12" x14ac:dyDescent="0.45">
@@ -69577,28 +69577,28 @@
         <v>775</v>
       </c>
       <c r="E888">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F888">
-        <v>0.27520000000000006</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="G888">
         <v>1</v>
       </c>
       <c r="H888">
-        <v>1408.5523255813955</v>
+        <v>1458</v>
       </c>
       <c r="I888">
-        <v>21.635210755813958</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J888">
         <v>0</v>
       </c>
       <c r="K888">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L888">
-        <v>0.19008013066509058</v>
+        <v>0.18539287912319011</v>
       </c>
     </row>
     <row r="889" spans="2:12" x14ac:dyDescent="0.45">
@@ -69612,10 +69612,10 @@
         <v>775</v>
       </c>
       <c r="E889">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F889">
-        <v>0.12320000000000002</v>
+        <v>1.5300000000000001E-2</v>
       </c>
       <c r="G889">
         <v>1</v>
@@ -69630,10 +69630,10 @@
         <v>0</v>
       </c>
       <c r="K889">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L889">
-        <v>0.19008013066509069</v>
+        <v>0.18539287912319011</v>
       </c>
     </row>
     <row r="890" spans="2:12" x14ac:dyDescent="0.45">
@@ -69647,10 +69647,10 @@
         <v>775</v>
       </c>
       <c r="E890">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F890">
-        <v>5.9000000000000007E-3</v>
+        <v>2.07E-2</v>
       </c>
       <c r="G890">
         <v>1</v>
@@ -69659,16 +69659,16 @@
         <v>1458</v>
       </c>
       <c r="I890">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J890">
         <v>0</v>
       </c>
       <c r="K890">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L890">
-        <v>0.19008013066509069</v>
+        <v>0.18539287912319011</v>
       </c>
     </row>
     <row r="891" spans="2:12" x14ac:dyDescent="0.45">
@@ -76049,13 +76049,13 @@
         <v>750</v>
       </c>
       <c r="D1073" t="s">
-        <v>202</v>
+        <v>24</v>
       </c>
       <c r="E1073">
         <v>2013</v>
       </c>
       <c r="F1073">
-        <v>1.9E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G1073">
         <v>1</v>
@@ -76064,7 +76064,7 @@
         <v>1458</v>
       </c>
       <c r="I1073">
-        <v>22.424999999999997</v>
+        <v>22.424999999999994</v>
       </c>
       <c r="J1073">
         <v>0</v>
@@ -76073,7 +76073,7 @@
         <v>42</v>
       </c>
       <c r="L1073">
-        <v>0.18013391841854179</v>
+        <v>0.19855392263260624</v>
       </c>
     </row>
     <row r="1074" spans="2:12" x14ac:dyDescent="0.45">
@@ -76084,13 +76084,13 @@
         <v>750</v>
       </c>
       <c r="D1074" t="s">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="E1074">
         <v>2013</v>
       </c>
       <c r="F1074">
-        <v>3.5000000000000001E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G1074">
         <v>1</v>
@@ -76099,7 +76099,7 @@
         <v>1458</v>
       </c>
       <c r="I1074">
-        <v>22.424999999999994</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1074">
         <v>0</v>
@@ -76108,7 +76108,7 @@
         <v>42</v>
       </c>
       <c r="L1074">
-        <v>0.19855392263260624</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1075" spans="2:12" x14ac:dyDescent="0.45">
@@ -76119,13 +76119,13 @@
         <v>750</v>
       </c>
       <c r="D1075" t="s">
-        <v>289</v>
+        <v>202</v>
       </c>
       <c r="E1075">
         <v>2013</v>
       </c>
       <c r="F1075">
-        <v>1.4E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G1075">
         <v>1</v>
@@ -76143,7 +76143,7 @@
         <v>42</v>
       </c>
       <c r="L1075">
-        <v>0.1885335384832984</v>
+        <v>0.18013391841854179</v>
       </c>
     </row>
     <row r="1076" spans="2:12" x14ac:dyDescent="0.45">
@@ -76154,19 +76154,19 @@
         <v>750</v>
       </c>
       <c r="D1076" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E1076">
         <v>2014</v>
       </c>
       <c r="F1076">
-        <v>2.5000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="G1076">
         <v>1</v>
       </c>
       <c r="H1076">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1076">
         <v>22.424999999999997</v>
@@ -76178,7 +76178,7 @@
         <v>41</v>
       </c>
       <c r="L1076">
-        <v>0.1885335384832984</v>
+        <v>0.19855392263260618</v>
       </c>
     </row>
     <row r="1077" spans="2:12" x14ac:dyDescent="0.45">
@@ -76189,19 +76189,19 @@
         <v>750</v>
       </c>
       <c r="D1077" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="E1077">
         <v>2014</v>
       </c>
       <c r="F1077">
-        <v>2.7000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="G1077">
         <v>1</v>
       </c>
       <c r="H1077">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1077">
         <v>22.424999999999997</v>
@@ -76213,7 +76213,7 @@
         <v>41</v>
       </c>
       <c r="L1077">
-        <v>0.19855392263260618</v>
+        <v>0.18076608822185891</v>
       </c>
     </row>
     <row r="1078" spans="2:12" x14ac:dyDescent="0.45">
@@ -76259,13 +76259,13 @@
         <v>750</v>
       </c>
       <c r="D1079" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="E1079">
         <v>2014</v>
       </c>
       <c r="F1079">
-        <v>2E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G1079">
         <v>1</v>
@@ -76283,7 +76283,7 @@
         <v>41</v>
       </c>
       <c r="L1079">
-        <v>0.18076608822185891</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1080" spans="2:12" x14ac:dyDescent="0.45">
@@ -76434,22 +76434,22 @@
         <v>750</v>
       </c>
       <c r="D1084" t="s">
-        <v>24</v>
+        <v>702</v>
       </c>
       <c r="E1084">
         <v>2015</v>
       </c>
       <c r="F1084">
-        <v>9.6999999999999986E-3</v>
+        <v>4.9000000000000007E-3</v>
       </c>
       <c r="G1084">
         <v>1</v>
       </c>
       <c r="H1084">
-        <v>1458</v>
+        <v>1457.9999999999998</v>
       </c>
       <c r="I1084">
-        <v>22.425000000000001</v>
+        <v>22.424999999999997</v>
       </c>
       <c r="J1084">
         <v>0</v>
@@ -76458,7 +76458,7 @@
         <v>40</v>
       </c>
       <c r="L1084">
-        <v>0.19855392263260621</v>
+        <v>0.18956968490584708</v>
       </c>
     </row>
     <row r="1085" spans="2:12" x14ac:dyDescent="0.45">
@@ -76469,22 +76469,22 @@
         <v>750</v>
       </c>
       <c r="D1085" t="s">
-        <v>702</v>
+        <v>24</v>
       </c>
       <c r="E1085">
         <v>2015</v>
       </c>
       <c r="F1085">
-        <v>4.9000000000000007E-3</v>
+        <v>9.6999999999999986E-3</v>
       </c>
       <c r="G1085">
         <v>1</v>
       </c>
       <c r="H1085">
-        <v>1457.9999999999998</v>
+        <v>1458</v>
       </c>
       <c r="I1085">
-        <v>22.424999999999997</v>
+        <v>22.425000000000001</v>
       </c>
       <c r="J1085">
         <v>0</v>
@@ -76493,7 +76493,7 @@
         <v>40</v>
       </c>
       <c r="L1085">
-        <v>0.18956968490584708</v>
+        <v>0.19855392263260621</v>
       </c>
     </row>
     <row r="1086" spans="2:12" x14ac:dyDescent="0.45">
@@ -76679,19 +76679,19 @@
         <v>750</v>
       </c>
       <c r="D1091" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="E1091">
         <v>2020</v>
       </c>
       <c r="F1091">
-        <v>1.6000000000000001E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="G1091">
         <v>1</v>
       </c>
       <c r="H1091">
-        <v>1458</v>
+        <v>1458.0000000000002</v>
       </c>
       <c r="I1091">
         <v>22.424999999999997</v>
@@ -76703,7 +76703,7 @@
         <v>35</v>
       </c>
       <c r="L1091">
-        <v>0.1885335384832984</v>
+        <v>0.18076608822185894</v>
       </c>
     </row>
     <row r="1092" spans="2:12" x14ac:dyDescent="0.45">
@@ -76714,19 +76714,19 @@
         <v>750</v>
       </c>
       <c r="D1092" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="E1092">
         <v>2020</v>
       </c>
       <c r="F1092">
-        <v>2.8E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="G1092">
         <v>1</v>
       </c>
       <c r="H1092">
-        <v>1458.0000000000002</v>
+        <v>1458</v>
       </c>
       <c r="I1092">
         <v>22.424999999999997</v>
@@ -76738,7 +76738,7 @@
         <v>35</v>
       </c>
       <c r="L1092">
-        <v>0.18076608822185894</v>
+        <v>0.1885335384832984</v>
       </c>
     </row>
     <row r="1093" spans="2:12" x14ac:dyDescent="0.45">
@@ -76866,7 +76866,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1096">
-        <v>0.41074925609602891</v>
+        <v>0.41074925609602886</v>
       </c>
     </row>
     <row r="1097" spans="2:12" x14ac:dyDescent="0.45">
@@ -76889,7 +76889,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L1097">
-        <v>0.41074925609602891</v>
+        <v>0.41074925609602886</v>
       </c>
     </row>
     <row r="1098" spans="2:12" x14ac:dyDescent="0.45">
@@ -76912,7 +76912,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L1098">
-        <v>0.41074925609602891</v>
+        <v>0.41074925609602886</v>
       </c>
     </row>
     <row r="1099" spans="2:12" x14ac:dyDescent="0.45">
@@ -81680,7 +81680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E30F29-F95E-4A6C-8EA6-C053150D0967}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3155DF56-A851-476E-8CD5-8D02BA5CA8B5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
